--- a/examples/ex001.Interpolation.xlsx
+++ b/examples/ex001.Interpolation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr codeName="ЭтаКнига"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\unifloc\unifloc_vba\examples\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unifloc\unifloc_vba\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A662D2CA-6897-4415-9D29-49A5AE126B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E339434E-4F1E-4C9D-B27C-834B0C601E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1095" yWindow="5250" windowWidth="27795" windowHeight="16815" tabRatio="488" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="interpolation" sheetId="1" r:id="rId1"/>
@@ -283,7 +283,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -292,28 +292,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -8815,15 +8814,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>5</xdr:col>
-          <xdr:colOff>30480</xdr:colOff>
+          <xdr:colOff>28575</xdr:colOff>
           <xdr:row>20</xdr:row>
-          <xdr:rowOff>60960</xdr:rowOff>
+          <xdr:rowOff>57150</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>8</xdr:col>
-          <xdr:colOff>213360</xdr:colOff>
+          <xdr:colOff>209550</xdr:colOff>
           <xdr:row>21</xdr:row>
-          <xdr:rowOff>121920</xdr:rowOff>
+          <xdr:rowOff>123825</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -9017,8 +9016,13 @@
         <a:p>
           <a:r>
             <a:rPr lang="ru-RU" sz="1100"/>
-            <a:t>Показаны примеры </a:t>
+            <a:t>Показаны примеры</a:t>
           </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>:</a:t>
+          </a:r>
+          <a:endParaRPr lang="ru-RU" sz="1100"/>
         </a:p>
         <a:p>
           <a:r>
@@ -9110,18 +9114,35 @@
           </a:endParaRPr>
         </a:p>
         <a:p>
+          <a:pPr marL="0" indent="0"/>
           <a:endParaRPr lang="ru-RU" sz="1100">
-            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
-            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
+          <a:pPr marL="0" indent="0"/>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Выполните задания указанные в стрелках</a:t>
+          </a:r>
           <a:r>
             <a:rPr lang="ru-RU" sz="1100">
               <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
               <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
             </a:rPr>
-            <a:t>Выполните задания указанные в стрелках.</a:t>
+            <a:t>.</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -9689,8 +9710,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Info"/>
     </sheetNames>
@@ -9972,14 +9996,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Лист1"/>
   <dimension ref="A1:AI230"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="14" max="14" width="3.6640625" customWidth="1"/>
-    <col min="15" max="15" width="1.5546875" customWidth="1"/>
-    <col min="26" max="26" width="1.6640625" customWidth="1"/>
+    <col min="14" max="14" width="3.7109375" customWidth="1"/>
+    <col min="15" max="15" width="1.5703125" customWidth="1"/>
+    <col min="26" max="26" width="1.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -9988,386 +10012,234 @@
       </c>
       <c r="G1" t="str" cm="1">
         <f t="array" ref="G1">[1]!unf_Version()</f>
-        <v>7.31</v>
-      </c>
-      <c r="AC1" s="14" t="s">
+        <v>7.57</v>
+      </c>
+      <c r="AC1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="AD1" s="14">
+      <c r="AD1" s="13">
         <v>2</v>
       </c>
-      <c r="AE1" s="14"/>
-      <c r="AF1" s="14"/>
-      <c r="AG1" s="14"/>
-      <c r="AH1" s="14"/>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AE1" s="13"/>
+      <c r="AF1" s="13"/>
+      <c r="AG1" s="13"/>
+      <c r="AH1" s="13"/>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="AC2" s="14">
+      <c r="AC2" s="13">
         <v>0</v>
       </c>
-      <c r="AD2" s="14" t="s">
+      <c r="AD2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AE2" s="14"/>
-      <c r="AF2" s="14"/>
-      <c r="AG2" s="14"/>
-      <c r="AH2" s="14"/>
-    </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="AC3" s="14">
+      <c r="AE2" s="13"/>
+      <c r="AF2" s="13"/>
+      <c r="AG2" s="13"/>
+      <c r="AH2" s="13"/>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AC3" s="13">
         <v>1</v>
       </c>
-      <c r="AD3" s="14" t="s">
+      <c r="AD3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AE3" s="14"/>
-      <c r="AF3" s="14"/>
-      <c r="AG3" s="14"/>
-      <c r="AH3" s="14"/>
-    </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="AC4" s="14">
+      <c r="AE3" s="13"/>
+      <c r="AF3" s="13"/>
+      <c r="AG3" s="13"/>
+      <c r="AH3" s="13"/>
+    </row>
+    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AC4" s="13">
         <v>2</v>
       </c>
-      <c r="AD4" s="14" t="s">
+      <c r="AD4" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AE4" s="14"/>
-      <c r="AF4" s="14"/>
-      <c r="AG4" s="14"/>
-      <c r="AH4" s="14"/>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AE4" s="13"/>
+      <c r="AF4" s="13"/>
+      <c r="AG4" s="13"/>
+      <c r="AH4" s="13"/>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
-      <c r="B5" s="6" t="s">
+      <c r="B5" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6" t="s">
+      <c r="E5" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="AC5" s="14">
+      <c r="AC5" s="13">
         <v>3</v>
       </c>
-      <c r="AD5" s="14" t="s">
+      <c r="AD5" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AE5" s="14"/>
-      <c r="AF5" s="14"/>
-      <c r="AG5" s="14"/>
-      <c r="AH5" s="14"/>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AE5" s="13"/>
+      <c r="AF5" s="13"/>
+      <c r="AG5" s="13"/>
+      <c r="AH5" s="13"/>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-    </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
-      <c r="B7" s="8">
+      <c r="B7" s="7">
         <v>1</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="7">
         <v>1</v>
       </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="8">
+      <c r="E7" s="7">
         <v>1</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="7">
         <v>1</v>
       </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
-      <c r="B8" s="8">
+      <c r="B8" s="7">
         <v>4</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="7">
         <v>3</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="8">
+      <c r="E8" s="7">
         <v>3</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="7">
         <v>3</v>
       </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
-      <c r="B9" s="8">
+      <c r="B9" s="7">
         <v>5</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="7">
         <v>5</v>
       </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="8">
+      <c r="E9" s="7">
         <v>8</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="7">
         <v>4.5</v>
       </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
-      <c r="B10" s="8">
+      <c r="B10" s="7">
         <v>15</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="7">
         <v>10</v>
       </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="8">
+      <c r="E10" s="7">
         <v>11</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="7">
         <v>10</v>
       </c>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
-      <c r="B11" s="8">
+      <c r="B11" s="7">
         <v>19</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="7">
         <v>-1</v>
       </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="8">
+      <c r="E11" s="7">
         <v>15</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="7">
         <v>15</v>
       </c>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
-      <c r="B12" s="8">
+      <c r="B12" s="7">
         <v>22</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="7">
         <v>0</v>
       </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="8">
+      <c r="E12" s="7">
         <v>18</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="7">
         <v>20</v>
       </c>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
-      <c r="B13" s="8">
+      <c r="B13" s="7">
         <v>25</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="7">
         <v>4</v>
       </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="8">
+      <c r="E13" s="7">
         <v>25</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="7">
         <v>0</v>
       </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
-      <c r="B14" s="8">
+      <c r="B14" s="7">
         <v>28</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="7">
         <v>5</v>
       </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="8">
+      <c r="E14" s="7">
         <v>28</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="7">
         <v>5</v>
       </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
-      <c r="B15" s="8">
+      <c r="B15" s="7">
         <v>30</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="7">
         <v>5</v>
       </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="8">
+      <c r="E15" s="7">
         <v>30</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="7">
         <v>5</v>
       </c>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="6"/>
-    </row>
-    <row r="17" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
-    </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="3"/>
@@ -10382,7 +10254,7 @@
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="4"/>
-      <c r="P18" s="18" t="str">
+      <c r="P18" s="17" t="str">
         <f>"Часть 2. Поиск решения f(x) = " &amp;f_to_solve_</f>
         <v>Часть 2. Поиск решения f(x) = 4</v>
       </c>
@@ -10395,7 +10267,7 @@
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
       <c r="Y18" s="4"/>
-      <c r="AA18" s="18" t="s">
+      <c r="AA18" s="17" t="s">
         <v>17</v>
       </c>
       <c r="AB18" s="3"/>
@@ -10407,5955 +10279,3554 @@
       <c r="AH18" s="3"/>
       <c r="AI18" s="4"/>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="7"/>
+      <c r="N19" s="6"/>
       <c r="P19" s="5"/>
-      <c r="Q19" s="6"/>
-      <c r="R19" s="6"/>
-      <c r="S19" s="6"/>
-      <c r="T19" s="6"/>
-      <c r="U19" s="6"/>
-      <c r="V19" s="6"/>
-      <c r="W19" s="6"/>
-      <c r="X19" s="6"/>
-      <c r="Y19" s="7"/>
+      <c r="Y19" s="6"/>
       <c r="AA19" s="5"/>
-      <c r="AB19" s="6"/>
-      <c r="AC19" s="6"/>
-      <c r="AD19" s="6"/>
-      <c r="AE19" s="6"/>
-      <c r="AF19" s="6"/>
-      <c r="AG19" s="6"/>
-      <c r="AH19" s="6"/>
-      <c r="AI19" s="7"/>
-    </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI19" s="6"/>
+    </row>
+    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="16" t="s">
+      <c r="G20" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="H20" s="13">
+      <c r="H20" s="12">
         <f>AD1-1</f>
         <v>1</v>
       </c>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="7"/>
+      <c r="N20" s="6"/>
       <c r="P20" s="5"/>
-      <c r="Q20" s="6"/>
-      <c r="R20" s="6"/>
-      <c r="S20" s="6"/>
-      <c r="T20" s="6"/>
-      <c r="U20" s="6"/>
-      <c r="V20" s="6"/>
-      <c r="W20" s="6"/>
-      <c r="X20" s="6"/>
-      <c r="Y20" s="7"/>
+      <c r="Y20" s="6"/>
       <c r="AA20" s="5"/>
-      <c r="AB20" s="6"/>
-      <c r="AC20" s="6"/>
-      <c r="AD20" s="6"/>
-      <c r="AE20" s="6"/>
-      <c r="AF20" s="6"/>
-      <c r="AG20" s="6"/>
-      <c r="AH20" s="6"/>
-      <c r="AI20" s="7"/>
-    </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI20" s="6"/>
+    </row>
+    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
-      <c r="B21" s="20">
+      <c r="B21" s="19">
         <v>1</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B21,тип_интерполяции_)</f>
         <v>1</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B21,тип_интерполяции_)</f>
         <v>1</v>
       </c>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="7"/>
+      <c r="N21" s="6"/>
       <c r="P21" s="5"/>
-      <c r="Q21" s="6"/>
-      <c r="R21" s="6"/>
-      <c r="S21" s="6"/>
-      <c r="T21" s="6"/>
-      <c r="U21" s="6"/>
-      <c r="V21" s="6"/>
-      <c r="W21" s="6"/>
-      <c r="X21" s="6"/>
-      <c r="Y21" s="7"/>
+      <c r="Y21" s="6"/>
       <c r="AA21" s="5"/>
-      <c r="AB21" s="6"/>
-      <c r="AC21" s="6"/>
-      <c r="AD21" s="6"/>
-      <c r="AE21" s="6"/>
-      <c r="AF21" s="6"/>
-      <c r="AG21" s="6"/>
-      <c r="AH21" s="6"/>
-      <c r="AI21" s="7"/>
-    </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI21" s="6"/>
+    </row>
+    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
-      <c r="B22" s="20">
+      <c r="B22" s="19">
         <f>B21+($B$15-$B$7)/200</f>
         <v>1.145</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B22,тип_интерполяции_)</f>
         <v>0.9455290939362081</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B22,тип_интерполяции_)</f>
         <v>1.2168934154046951</v>
       </c>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="7"/>
+      <c r="N22" s="6"/>
       <c r="P22" s="5"/>
-      <c r="Q22" s="6"/>
-      <c r="R22" s="6"/>
-      <c r="S22" s="6"/>
-      <c r="T22" s="6"/>
-      <c r="U22" s="6"/>
-      <c r="V22" s="6"/>
-      <c r="W22" s="6"/>
-      <c r="X22" s="6"/>
-      <c r="Y22" s="7"/>
+      <c r="Y22" s="6"/>
       <c r="AA22" s="5"/>
-      <c r="AB22" s="6"/>
-      <c r="AC22" s="6"/>
-      <c r="AD22" s="6"/>
-      <c r="AE22" s="6"/>
-      <c r="AF22" s="6"/>
-      <c r="AG22" s="6"/>
-      <c r="AH22" s="6"/>
-      <c r="AI22" s="7"/>
-    </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI22" s="6"/>
+    </row>
+    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
-      <c r="B23" s="20">
+      <c r="B23" s="19">
         <f t="shared" ref="B23:B86" si="0">B22+($B$15-$B$7)/200</f>
         <v>1.29</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B23,тип_интерполяции_)</f>
         <v>0.90641016548776931</v>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B23,тип_интерполяции_)</f>
         <v>1.4225474289401925</v>
       </c>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="7"/>
+      <c r="N23" s="6"/>
       <c r="P23" s="5"/>
-      <c r="Q23" s="6"/>
-      <c r="R23" s="6"/>
-      <c r="S23" s="6"/>
-      <c r="T23" s="6"/>
-      <c r="U23" s="6"/>
-      <c r="V23" s="6"/>
-      <c r="W23" s="6"/>
-      <c r="X23" s="6"/>
-      <c r="Y23" s="7"/>
+      <c r="Y23" s="6"/>
       <c r="AA23" s="5"/>
-      <c r="AB23" s="6"/>
-      <c r="AC23" s="6"/>
-      <c r="AD23" s="6"/>
-      <c r="AE23" s="6"/>
-      <c r="AF23" s="6"/>
-      <c r="AG23" s="6"/>
-      <c r="AH23" s="6"/>
-      <c r="AI23" s="7"/>
-    </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI23" s="6"/>
+    </row>
+    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
-      <c r="B24" s="20">
+      <c r="B24" s="19">
         <f t="shared" si="0"/>
         <v>1.4350000000000001</v>
       </c>
-      <c r="C24" s="15">
+      <c r="C24" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B24,тип_интерполяции_)</f>
         <v>0.88264321465468354</v>
       </c>
-      <c r="D24" s="15">
+      <c r="D24" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B24,тип_интерполяции_)</f>
         <v>1.6169620406064924</v>
       </c>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="7"/>
+      <c r="N24" s="6"/>
       <c r="P24" s="5"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="6"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="6"/>
-      <c r="Y24" s="7"/>
+      <c r="Y24" s="6"/>
       <c r="AA24" s="5"/>
-      <c r="AB24" s="6"/>
-      <c r="AC24" s="6"/>
-      <c r="AD24" s="6"/>
-      <c r="AE24" s="6"/>
-      <c r="AF24" s="6"/>
-      <c r="AG24" s="6"/>
-      <c r="AH24" s="6"/>
-      <c r="AI24" s="7"/>
-    </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI24" s="6"/>
+    </row>
+    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
-      <c r="B25" s="20">
+      <c r="B25" s="19">
         <f t="shared" si="0"/>
         <v>1.58</v>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B25,тип_интерполяции_)</f>
         <v>0.87422824143695088</v>
       </c>
-      <c r="D25" s="15">
+      <c r="D25" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B25,тип_интерполяции_)</f>
         <v>1.8001372504035946</v>
       </c>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="6"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="7"/>
+      <c r="N25" s="6"/>
       <c r="P25" s="5"/>
-      <c r="Q25" s="6"/>
-      <c r="R25" s="6"/>
-      <c r="S25" s="6"/>
-      <c r="T25" s="6"/>
-      <c r="U25" s="6"/>
-      <c r="V25" s="6"/>
-      <c r="W25" s="6"/>
-      <c r="X25" s="6"/>
-      <c r="Y25" s="7"/>
+      <c r="Y25" s="6"/>
       <c r="AA25" s="5"/>
-      <c r="AB25" s="6"/>
-      <c r="AC25" s="6"/>
-      <c r="AD25" s="6"/>
-      <c r="AE25" s="6"/>
-      <c r="AF25" s="6"/>
-      <c r="AG25" s="6"/>
-      <c r="AH25" s="6"/>
-      <c r="AI25" s="7"/>
-    </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI25" s="6"/>
+    </row>
+    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
-      <c r="B26" s="20">
+      <c r="B26" s="19">
         <f t="shared" si="0"/>
         <v>1.7250000000000001</v>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B26,тип_интерполяции_)</f>
         <v>0.88116524583457123</v>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B26,тип_интерполяции_)</f>
         <v>1.9720730583314994</v>
       </c>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="6"/>
-      <c r="N26" s="7"/>
+      <c r="N26" s="6"/>
       <c r="P26" s="5"/>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="6"/>
-      <c r="S26" s="6"/>
-      <c r="T26" s="6"/>
-      <c r="U26" s="6"/>
-      <c r="V26" s="6"/>
-      <c r="W26" s="6"/>
-      <c r="X26" s="6"/>
-      <c r="Y26" s="7"/>
+      <c r="Y26" s="6"/>
       <c r="AA26" s="5"/>
-      <c r="AB26" s="6"/>
-      <c r="AC26" s="6"/>
-      <c r="AD26" s="6"/>
-      <c r="AE26" s="6"/>
-      <c r="AF26" s="6"/>
-      <c r="AG26" s="6"/>
-      <c r="AH26" s="6"/>
-      <c r="AI26" s="7"/>
-    </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI26" s="6"/>
+    </row>
+    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
-      <c r="B27" s="20">
+      <c r="B27" s="19">
         <f t="shared" si="0"/>
         <v>1.87</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B27,тип_интерполяции_)</f>
         <v>0.90345422784754459</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B27,тип_интерполяции_)</f>
         <v>2.1327694643902064</v>
       </c>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
-      <c r="N27" s="7"/>
+      <c r="N27" s="6"/>
       <c r="P27" s="5"/>
-      <c r="Q27" s="16" t="s">
+      <c r="Q27" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="R27" s="8">
+      <c r="R27" s="7">
         <v>4</v>
       </c>
-      <c r="S27" s="6"/>
-      <c r="T27" s="6"/>
-      <c r="U27" s="6"/>
-      <c r="V27" s="6"/>
-      <c r="W27" s="6"/>
-      <c r="X27" s="6"/>
-      <c r="Y27" s="7"/>
+      <c r="Y27" s="6"/>
       <c r="AA27" s="5"/>
-      <c r="AB27" s="6"/>
-      <c r="AC27" s="6"/>
-      <c r="AD27" s="6"/>
-      <c r="AE27" s="6"/>
-      <c r="AF27" s="6"/>
-      <c r="AG27" s="6"/>
-      <c r="AH27" s="6"/>
-      <c r="AI27" s="7"/>
-    </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI27" s="6"/>
+    </row>
+    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
-      <c r="B28" s="20">
+      <c r="B28" s="19">
         <f t="shared" si="0"/>
         <v>2.0150000000000001</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B28,тип_интерполяции_)</f>
         <v>0.94109518747587106</v>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B28,тип_интерполяции_)</f>
         <v>2.2822264685797156</v>
       </c>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="6"/>
-      <c r="N28" s="7"/>
+      <c r="N28" s="6"/>
       <c r="P28" s="5"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="6"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="6"/>
-      <c r="U28" s="6"/>
-      <c r="V28" s="6"/>
-      <c r="W28" s="6"/>
-      <c r="X28" s="6"/>
-      <c r="Y28" s="7"/>
+      <c r="Y28" s="6"/>
       <c r="AA28" s="5"/>
-      <c r="AB28" s="6"/>
-      <c r="AC28" s="6"/>
-      <c r="AD28" s="6"/>
-      <c r="AE28" s="6"/>
-      <c r="AF28" s="6"/>
-      <c r="AG28" s="6"/>
-      <c r="AH28" s="6"/>
-      <c r="AI28" s="7"/>
-    </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI28" s="6"/>
+    </row>
+    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
-      <c r="B29" s="20">
+      <c r="B29" s="19">
         <f t="shared" si="0"/>
         <v>2.16</v>
       </c>
-      <c r="C29" s="15">
+      <c r="C29" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B29,тип_интерполяции_)</f>
         <v>0.99408812471955066</v>
       </c>
-      <c r="D29" s="15">
+      <c r="D29" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B29,тип_интерполяции_)</f>
         <v>2.4204440709000274</v>
       </c>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="6"/>
-      <c r="N29" s="7"/>
+      <c r="N29" s="6"/>
       <c r="P29" s="5"/>
-      <c r="Q29" s="6"/>
-      <c r="R29" s="6"/>
-      <c r="S29" s="6"/>
-      <c r="T29" s="6"/>
-      <c r="U29" s="6"/>
-      <c r="V29" s="6"/>
-      <c r="W29" s="6"/>
-      <c r="X29" s="6"/>
-      <c r="Y29" s="7"/>
+      <c r="Y29" s="6"/>
       <c r="AA29" s="5"/>
-      <c r="AB29" s="6"/>
-      <c r="AC29" s="6"/>
-      <c r="AD29" s="6"/>
-      <c r="AE29" s="6"/>
-      <c r="AF29" s="6"/>
-      <c r="AG29" s="6"/>
-      <c r="AH29" s="6"/>
-      <c r="AI29" s="7"/>
-    </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI29" s="6"/>
+    </row>
+    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
-      <c r="B30" s="20">
+      <c r="B30" s="19">
         <f t="shared" si="0"/>
         <v>2.3050000000000002</v>
       </c>
-      <c r="C30" s="15">
+      <c r="C30" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B30,тип_интерполяции_)</f>
         <v>1.0624330395785833</v>
       </c>
-      <c r="D30" s="15">
+      <c r="D30" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B30,тип_интерполяции_)</f>
         <v>2.5474222713511416</v>
       </c>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="6"/>
-      <c r="N30" s="7"/>
+      <c r="N30" s="6"/>
       <c r="P30" s="5"/>
-      <c r="Q30" s="6" t="s">
+      <c r="Q30" t="s">
         <v>9</v>
       </c>
-      <c r="R30" s="17">
+      <c r="R30" s="16">
         <f t="array" ref="R30:V30">[1]!crv_solve(x_,fx_,f_to_solve_)</f>
         <v>4.5</v>
       </c>
-      <c r="S30" s="17">
+      <c r="S30" s="16">
         <v>17.18181818181818</v>
       </c>
-      <c r="T30" s="17">
+      <c r="T30" s="16">
         <v>25</v>
       </c>
-      <c r="U30" s="17" t="e">
+      <c r="U30" s="16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="V30" s="17" t="e">
+      <c r="V30" s="16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="W30" s="6"/>
-      <c r="X30" s="6"/>
-      <c r="Y30" s="7"/>
+      <c r="Y30" s="6"/>
       <c r="AA30" s="5"/>
-      <c r="AB30" s="6" t="s">
+      <c r="AB30" t="s">
         <v>9</v>
       </c>
-      <c r="AC30" s="17">
+      <c r="AC30" s="16">
         <f t="array" ref="AC30:AH30">[1]!crv_intersection(x_,fx_,x2_,gx2_)</f>
         <v>1</v>
       </c>
-      <c r="AD30" s="17">
+      <c r="AD30" s="16">
         <v>4.1764705882352944</v>
       </c>
-      <c r="AE30" s="17">
+      <c r="AE30" s="16">
         <v>9.5</v>
       </c>
-      <c r="AF30" s="17">
+      <c r="AF30" s="16">
         <v>24.045454545454547</v>
       </c>
-      <c r="AG30" s="17">
+      <c r="AG30" s="16">
         <v>28</v>
       </c>
-      <c r="AH30" s="17">
+      <c r="AH30" s="16">
         <v>30</v>
       </c>
-      <c r="AI30" s="7"/>
-    </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI30" s="6"/>
+    </row>
+    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
-      <c r="B31" s="20">
+      <c r="B31" s="19">
         <f t="shared" si="0"/>
         <v>2.4500000000000002</v>
       </c>
-      <c r="C31" s="15">
+      <c r="C31" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B31,тип_интерполяции_)</f>
         <v>1.146129932052969</v>
       </c>
-      <c r="D31" s="15">
+      <c r="D31" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B31,тип_интерполяции_)</f>
         <v>2.6631610699330581</v>
       </c>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="6"/>
-      <c r="N31" s="7"/>
+      <c r="N31" s="6"/>
       <c r="P31" s="5"/>
-      <c r="Q31" s="6"/>
-      <c r="R31" s="17">
+      <c r="R31" s="16">
         <f>[1]!crv_interpolation(x_,fx_,R30,тип_интерполяции_)</f>
         <v>3.9563608090176294</v>
       </c>
-      <c r="S31" s="17">
+      <c r="S31" s="16">
         <f>[1]!crv_interpolation(x_,fx_,S30,тип_интерполяции_)</f>
         <v>3.3109669610188801</v>
       </c>
-      <c r="T31" s="17">
+      <c r="T31" s="16">
         <f>[1]!crv_interpolation(x_,fx_,T30,тип_интерполяции_)</f>
         <v>4</v>
       </c>
-      <c r="U31" s="17" t="str">
+      <c r="U31" s="16" t="str">
         <f>[1]!crv_interpolation(x_,fx_,U30,тип_интерполяции_)</f>
-        <v>error</v>
-      </c>
-      <c r="V31" s="17" t="str">
+        <v xml:space="preserve">Error:crv_interpolation:read_xy_vectors: </v>
+      </c>
+      <c r="V31" s="16" t="str">
         <f>[1]!crv_interpolation(x_,fx_,V30,тип_интерполяции_)</f>
-        <v>error</v>
-      </c>
-      <c r="W31" s="6"/>
-      <c r="X31" s="6"/>
-      <c r="Y31" s="7"/>
+        <v xml:space="preserve">Error:crv_interpolation:read_xy_vectors: </v>
+      </c>
+      <c r="Y31" s="6"/>
       <c r="AA31" s="5"/>
-      <c r="AB31" s="6"/>
-      <c r="AC31" s="17">
+      <c r="AC31" s="16">
         <f>[1]!crv_interpolation(x2_,gx2_,AC30,тип_интерполяции_)</f>
         <v>1</v>
       </c>
-      <c r="AD31" s="17">
+      <c r="AD31" s="16">
         <f>[1]!crv_interpolation(x2_,gx2_,AD30,тип_интерполяции_)</f>
         <v>3.2538855847684771</v>
       </c>
-      <c r="AE31" s="17">
+      <c r="AE31" s="16">
         <f>[1]!crv_interpolation(x2_,gx2_,AE30,тип_интерполяции_)</f>
         <v>7.1460086957131326</v>
       </c>
-      <c r="AF31" s="17">
+      <c r="AF31" s="16">
         <f>[1]!crv_interpolation(x2_,gx2_,AF30,тип_интерполяции_)</f>
         <v>0.99174486076679491</v>
       </c>
-      <c r="AG31" s="17">
+      <c r="AG31" s="16">
         <f>[1]!crv_interpolation(x2_,gx2_,AG30,тип_интерполяции_)</f>
         <v>5</v>
       </c>
-      <c r="AH31" s="17">
+      <c r="AH31" s="16">
         <f>[1]!crv_interpolation(x2_,gx2_,AH30,тип_интерполяции_)</f>
         <v>5</v>
       </c>
-      <c r="AI31" s="7"/>
-    </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI31" s="6"/>
+    </row>
+    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
-      <c r="B32" s="20">
+      <c r="B32" s="19">
         <f t="shared" si="0"/>
         <v>2.5950000000000002</v>
       </c>
-      <c r="C32" s="15">
+      <c r="C32" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B32,тип_интерполяции_)</f>
         <v>1.2451788021427077</v>
       </c>
-      <c r="D32" s="15">
+      <c r="D32" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B32,тип_интерполяции_)</f>
         <v>2.7676604666457774</v>
       </c>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="6"/>
-      <c r="L32" s="6"/>
-      <c r="M32" s="6"/>
-      <c r="N32" s="7"/>
+      <c r="N32" s="6"/>
       <c r="P32" s="5"/>
-      <c r="Q32" s="6"/>
-      <c r="R32" s="6"/>
-      <c r="S32" s="6"/>
-      <c r="T32" s="6"/>
-      <c r="U32" s="6"/>
-      <c r="V32" s="6"/>
-      <c r="W32" s="6"/>
-      <c r="X32" s="6"/>
-      <c r="Y32" s="7"/>
+      <c r="Y32" s="6"/>
       <c r="AA32" s="5"/>
-      <c r="AB32" s="6"/>
-      <c r="AC32" s="6"/>
-      <c r="AD32" s="6"/>
-      <c r="AE32" s="6"/>
-      <c r="AF32" s="6"/>
-      <c r="AG32" s="6"/>
-      <c r="AH32" s="6"/>
-      <c r="AI32" s="7"/>
-    </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI32" s="6"/>
+    </row>
+    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
-      <c r="B33" s="20">
+      <c r="B33" s="19">
         <f t="shared" si="0"/>
         <v>2.74</v>
       </c>
-      <c r="C33" s="15">
+      <c r="C33" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B33,тип_интерполяции_)</f>
         <v>1.3595796498477994</v>
       </c>
-      <c r="D33" s="15">
+      <c r="D33" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B33,тип_интерполяции_)</f>
         <v>2.8609204614892985</v>
       </c>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="6"/>
-      <c r="M33" s="6"/>
-      <c r="N33" s="7"/>
+      <c r="N33" s="6"/>
       <c r="P33" s="5"/>
-      <c r="Q33" s="6"/>
-      <c r="R33" s="6"/>
-      <c r="S33" s="6"/>
-      <c r="T33" s="6"/>
-      <c r="U33" s="6"/>
-      <c r="V33" s="6"/>
-      <c r="W33" s="6"/>
-      <c r="X33" s="6"/>
-      <c r="Y33" s="7"/>
+      <c r="Y33" s="6"/>
       <c r="AA33" s="5"/>
-      <c r="AB33" s="6"/>
-      <c r="AC33" s="6"/>
-      <c r="AD33" s="6"/>
-      <c r="AE33" s="6"/>
-      <c r="AF33" s="6"/>
-      <c r="AG33" s="6"/>
-      <c r="AH33" s="6"/>
-      <c r="AI33" s="7"/>
-    </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI33" s="6"/>
+    </row>
+    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
-      <c r="B34" s="20">
+      <c r="B34" s="19">
         <f t="shared" si="0"/>
         <v>2.8850000000000002</v>
       </c>
-      <c r="C34" s="15">
+      <c r="C34" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B34,тип_интерполяции_)</f>
         <v>1.4893324751682444</v>
       </c>
-      <c r="D34" s="15">
+      <c r="D34" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B34,тип_интерполяции_)</f>
         <v>2.9429410544636223</v>
       </c>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="6"/>
-      <c r="L34" s="6"/>
-      <c r="M34" s="6"/>
-      <c r="N34" s="7"/>
+      <c r="N34" s="6"/>
       <c r="P34" s="5"/>
-      <c r="Q34" s="6"/>
-      <c r="R34" s="6"/>
-      <c r="S34" s="6"/>
-      <c r="T34" s="6"/>
-      <c r="U34" s="6"/>
-      <c r="V34" s="6"/>
-      <c r="W34" s="6"/>
-      <c r="X34" s="6"/>
-      <c r="Y34" s="7"/>
+      <c r="Y34" s="6"/>
       <c r="AA34" s="5"/>
-      <c r="AB34" s="6"/>
-      <c r="AC34" s="6"/>
-      <c r="AD34" s="6"/>
-      <c r="AE34" s="6"/>
-      <c r="AF34" s="6"/>
-      <c r="AG34" s="6"/>
-      <c r="AH34" s="6"/>
-      <c r="AI34" s="7"/>
-    </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI34" s="6"/>
+    </row>
+    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
-      <c r="B35" s="20">
+      <c r="B35" s="19">
         <f t="shared" si="0"/>
         <v>3.0300000000000002</v>
       </c>
-      <c r="C35" s="15">
+      <c r="C35" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B35,тип_интерполяции_)</f>
         <v>1.6344372781040422</v>
       </c>
-      <c r="D35" s="15">
+      <c r="D35" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B35,тип_интерполяции_)</f>
         <v>3.0137235102555056</v>
       </c>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="6"/>
-      <c r="L35" s="6"/>
-      <c r="M35" s="6"/>
-      <c r="N35" s="7"/>
+      <c r="N35" s="6"/>
       <c r="P35" s="5"/>
-      <c r="Q35" s="6"/>
-      <c r="R35" s="6"/>
-      <c r="S35" s="6"/>
-      <c r="T35" s="6"/>
-      <c r="U35" s="6"/>
-      <c r="V35" s="6"/>
-      <c r="W35" s="6"/>
-      <c r="X35" s="6"/>
-      <c r="Y35" s="7"/>
+      <c r="Y35" s="6"/>
       <c r="AA35" s="5"/>
-      <c r="AB35" s="6"/>
-      <c r="AC35" s="6"/>
-      <c r="AD35" s="6"/>
-      <c r="AE35" s="6"/>
-      <c r="AF35" s="6"/>
-      <c r="AG35" s="6"/>
-      <c r="AH35" s="6"/>
-      <c r="AI35" s="7"/>
-    </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI35" s="6"/>
+    </row>
+    <row r="36" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
-      <c r="B36" s="20">
+      <c r="B36" s="19">
         <f t="shared" si="0"/>
         <v>3.1750000000000003</v>
       </c>
-      <c r="C36" s="15">
+      <c r="C36" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B36,тип_интерполяции_)</f>
         <v>1.7948940586551931</v>
       </c>
-      <c r="D36" s="15">
+      <c r="D36" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B36,тип_интерполяции_)</f>
         <v>3.0735150692709068</v>
       </c>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="6"/>
-      <c r="L36" s="6"/>
-      <c r="M36" s="6"/>
-      <c r="N36" s="7"/>
+      <c r="N36" s="6"/>
       <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="6"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="6"/>
-      <c r="Y36" s="7"/>
+      <c r="Y36" s="6"/>
       <c r="AA36" s="5"/>
-      <c r="AB36" s="6"/>
-      <c r="AC36" s="6"/>
-      <c r="AD36" s="6"/>
-      <c r="AE36" s="6"/>
-      <c r="AF36" s="6"/>
-      <c r="AG36" s="6"/>
-      <c r="AH36" s="6"/>
-      <c r="AI36" s="7"/>
-    </row>
-    <row r="37" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI36" s="6"/>
+    </row>
+    <row r="37" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
-      <c r="B37" s="20">
+      <c r="B37" s="19">
         <f t="shared" si="0"/>
         <v>3.3200000000000003</v>
       </c>
-      <c r="C37" s="15">
+      <c r="C37" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B37,тип_интерполяции_)</f>
         <v>1.9707028168216973</v>
       </c>
-      <c r="D37" s="15">
+      <c r="D37" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B37,тип_интерполяции_)</f>
         <v>3.1231012834918825</v>
       </c>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6"/>
-      <c r="L37" s="6"/>
-      <c r="M37" s="6"/>
-      <c r="N37" s="7"/>
+      <c r="N37" s="6"/>
       <c r="P37" s="5"/>
-      <c r="Q37" s="6"/>
-      <c r="R37" s="6"/>
-      <c r="S37" s="6"/>
-      <c r="T37" s="6"/>
-      <c r="U37" s="6"/>
-      <c r="V37" s="6"/>
-      <c r="W37" s="6"/>
-      <c r="X37" s="6"/>
-      <c r="Y37" s="7"/>
+      <c r="Y37" s="6"/>
       <c r="AA37" s="5"/>
-      <c r="AB37" s="6"/>
-      <c r="AC37" s="6"/>
-      <c r="AD37" s="6"/>
-      <c r="AE37" s="6"/>
-      <c r="AF37" s="6"/>
-      <c r="AG37" s="6"/>
-      <c r="AH37" s="6"/>
-      <c r="AI37" s="7"/>
-    </row>
-    <row r="38" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI37" s="6"/>
+    </row>
+    <row r="38" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
-      <c r="B38" s="20">
+      <c r="B38" s="19">
         <f t="shared" si="0"/>
         <v>3.4650000000000003</v>
       </c>
-      <c r="C38" s="15">
+      <c r="C38" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B38,тип_интерполяции_)</f>
         <v>2.1618635526035543</v>
       </c>
-      <c r="D38" s="15">
+      <c r="D38" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B38,тип_интерполяции_)</f>
         <v>3.1633389430661012</v>
       </c>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="6"/>
-      <c r="M38" s="6"/>
-      <c r="N38" s="7"/>
+      <c r="N38" s="6"/>
       <c r="P38" s="5"/>
-      <c r="Q38" s="6"/>
-      <c r="R38" s="6"/>
-      <c r="S38" s="6"/>
-      <c r="T38" s="6"/>
-      <c r="U38" s="6"/>
-      <c r="V38" s="6"/>
-      <c r="W38" s="6"/>
-      <c r="X38" s="6"/>
-      <c r="Y38" s="7"/>
+      <c r="Y38" s="6"/>
       <c r="AA38" s="5"/>
-      <c r="AB38" s="6"/>
-      <c r="AC38" s="6"/>
-      <c r="AD38" s="6"/>
-      <c r="AE38" s="6"/>
-      <c r="AF38" s="6"/>
-      <c r="AG38" s="6"/>
-      <c r="AH38" s="6"/>
-      <c r="AI38" s="7"/>
-    </row>
-    <row r="39" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI38" s="6"/>
+    </row>
+    <row r="39" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
-      <c r="B39" s="20">
+      <c r="B39" s="19">
         <f t="shared" si="0"/>
         <v>3.6100000000000003</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B39,тип_интерполяции_)</f>
         <v>2.3683762660007646</v>
       </c>
-      <c r="D39" s="15">
+      <c r="D39" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B39,тип_интерполяции_)</f>
         <v>3.1950848381412307</v>
       </c>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
-      <c r="L39" s="6"/>
-      <c r="M39" s="6"/>
-      <c r="N39" s="7"/>
+      <c r="N39" s="6"/>
       <c r="P39" s="5"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="6"/>
-      <c r="S39" s="6"/>
-      <c r="T39" s="6"/>
-      <c r="U39" s="6"/>
-      <c r="V39" s="6"/>
-      <c r="W39" s="6"/>
-      <c r="X39" s="6"/>
-      <c r="Y39" s="7"/>
+      <c r="Y39" s="6"/>
       <c r="AA39" s="5"/>
-      <c r="AB39" s="6"/>
-      <c r="AC39" s="6"/>
-      <c r="AD39" s="6"/>
-      <c r="AE39" s="6"/>
-      <c r="AF39" s="6"/>
-      <c r="AG39" s="6"/>
-      <c r="AH39" s="6"/>
-      <c r="AI39" s="7"/>
-    </row>
-    <row r="40" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI39" s="6"/>
+    </row>
+    <row r="40" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
-      <c r="B40" s="20">
+      <c r="B40" s="19">
         <f t="shared" si="0"/>
         <v>3.7550000000000003</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B40,тип_интерполяции_)</f>
         <v>2.5902409570133278</v>
       </c>
-      <c r="D40" s="15">
+      <c r="D40" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B40,тип_интерполяции_)</f>
         <v>3.2191957588649394</v>
       </c>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="6"/>
-      <c r="K40" s="6"/>
-      <c r="L40" s="6"/>
-      <c r="M40" s="6"/>
-      <c r="N40" s="7"/>
+      <c r="N40" s="6"/>
       <c r="P40" s="5"/>
-      <c r="Q40" s="6"/>
-      <c r="R40" s="6"/>
-      <c r="S40" s="6"/>
-      <c r="T40" s="6"/>
-      <c r="U40" s="6"/>
-      <c r="V40" s="6"/>
-      <c r="W40" s="6"/>
-      <c r="X40" s="6"/>
-      <c r="Y40" s="7"/>
+      <c r="Y40" s="6"/>
       <c r="AA40" s="5"/>
-      <c r="AB40" s="6"/>
-      <c r="AC40" s="6"/>
-      <c r="AD40" s="6"/>
-      <c r="AE40" s="6"/>
-      <c r="AF40" s="6"/>
-      <c r="AG40" s="6"/>
-      <c r="AH40" s="6"/>
-      <c r="AI40" s="7"/>
-    </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI40" s="6"/>
+    </row>
+    <row r="41" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
-      <c r="B41" s="20">
+      <c r="B41" s="19">
         <f t="shared" si="0"/>
         <v>3.9000000000000004</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B41,тип_интерполяции_)</f>
         <v>2.827457625641244</v>
       </c>
-      <c r="D41" s="15">
+      <c r="D41" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B41,тип_интерполяции_)</f>
         <v>3.2365284953848956</v>
       </c>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6"/>
-      <c r="J41" s="6"/>
-      <c r="K41" s="6"/>
-      <c r="L41" s="6"/>
-      <c r="M41" s="6"/>
-      <c r="N41" s="7"/>
+      <c r="N41" s="6"/>
       <c r="P41" s="5"/>
-      <c r="Q41" s="6"/>
-      <c r="R41" s="6"/>
-      <c r="S41" s="6"/>
-      <c r="T41" s="6"/>
-      <c r="U41" s="6"/>
-      <c r="V41" s="6"/>
-      <c r="W41" s="6"/>
-      <c r="X41" s="6"/>
-      <c r="Y41" s="7"/>
+      <c r="Y41" s="6"/>
       <c r="AA41" s="5"/>
-      <c r="AB41" s="6"/>
-      <c r="AC41" s="6"/>
-      <c r="AD41" s="6"/>
-      <c r="AE41" s="6"/>
-      <c r="AF41" s="6"/>
-      <c r="AG41" s="6"/>
-      <c r="AH41" s="6"/>
-      <c r="AI41" s="7"/>
-    </row>
-    <row r="42" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI41" s="6"/>
+    </row>
+    <row r="42" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
-      <c r="B42" s="20">
+      <c r="B42" s="19">
         <f t="shared" si="0"/>
         <v>4.0449999999999999</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B42,тип_интерполяции_)</f>
         <v>3.080014697072603</v>
       </c>
-      <c r="D42" s="15">
+      <c r="D42" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B42,тип_интерполяции_)</f>
         <v>3.2479398378487674</v>
       </c>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="6"/>
-      <c r="K42" s="6"/>
-      <c r="L42" s="6"/>
-      <c r="M42" s="6"/>
-      <c r="N42" s="7"/>
+      <c r="N42" s="6"/>
       <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="6"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="6"/>
-      <c r="Y42" s="7"/>
+      <c r="Y42" s="6"/>
       <c r="AA42" s="5"/>
-      <c r="AB42" s="6"/>
-      <c r="AC42" s="6"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="7"/>
-    </row>
-    <row r="43" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI42" s="6"/>
+    </row>
+    <row r="43" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
-      <c r="B43" s="20">
+      <c r="B43" s="19">
         <f t="shared" si="0"/>
         <v>4.1899999999999995</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B43,тип_интерполяции_)</f>
         <v>3.347075656951501</v>
       </c>
-      <c r="D43" s="15">
+      <c r="D43" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B43,тип_интерполяции_)</f>
         <v>3.2542865764042235</v>
       </c>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="6"/>
-      <c r="K43" s="6"/>
-      <c r="L43" s="6"/>
-      <c r="M43" s="6"/>
-      <c r="N43" s="7"/>
+      <c r="N43" s="6"/>
       <c r="P43" s="5"/>
-      <c r="Q43" s="6"/>
-      <c r="R43" s="6"/>
-      <c r="S43" s="6"/>
-      <c r="T43" s="6"/>
-      <c r="U43" s="6"/>
-      <c r="V43" s="6"/>
-      <c r="W43" s="6"/>
-      <c r="X43" s="6"/>
-      <c r="Y43" s="7"/>
+      <c r="Y43" s="6"/>
       <c r="AA43" s="5"/>
-      <c r="AB43" s="6"/>
-      <c r="AC43" s="6"/>
-      <c r="AD43" s="6"/>
-      <c r="AE43" s="6"/>
-      <c r="AF43" s="6"/>
-      <c r="AG43" s="6"/>
-      <c r="AH43" s="6"/>
-      <c r="AI43" s="7"/>
-    </row>
-    <row r="44" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI43" s="6"/>
+    </row>
+    <row r="44" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
-      <c r="B44" s="20">
+      <c r="B44" s="19">
         <f t="shared" si="0"/>
         <v>4.3349999999999991</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B44,тип_интерполяции_)</f>
         <v>3.6264440854827473</v>
       </c>
-      <c r="D44" s="15">
+      <c r="D44" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B44,тип_интерполяции_)</f>
         <v>3.2564255011989318</v>
       </c>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="6"/>
-      <c r="K44" s="6"/>
-      <c r="L44" s="6"/>
-      <c r="M44" s="6"/>
-      <c r="N44" s="7"/>
+      <c r="N44" s="6"/>
       <c r="P44" s="5"/>
-      <c r="Q44" s="6"/>
-      <c r="R44" s="6"/>
-      <c r="S44" s="6"/>
-      <c r="T44" s="6"/>
-      <c r="U44" s="6"/>
-      <c r="V44" s="6"/>
-      <c r="W44" s="6"/>
-      <c r="X44" s="6"/>
-      <c r="Y44" s="7"/>
+      <c r="Y44" s="6"/>
       <c r="AA44" s="5"/>
-      <c r="AB44" s="6"/>
-      <c r="AC44" s="6"/>
-      <c r="AD44" s="6"/>
-      <c r="AE44" s="6"/>
-      <c r="AF44" s="6"/>
-      <c r="AG44" s="6"/>
-      <c r="AH44" s="6"/>
-      <c r="AI44" s="7"/>
-    </row>
-    <row r="45" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI44" s="6"/>
+    </row>
+    <row r="45" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A45" s="5"/>
-      <c r="B45" s="20">
+      <c r="B45" s="19">
         <f t="shared" si="0"/>
         <v>4.4799999999999986</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B45,тип_интерполяции_)</f>
         <v>3.9157965416156273</v>
       </c>
-      <c r="D45" s="15">
+      <c r="D45" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B45,тип_интерполяции_)</f>
         <v>3.2552134023805612</v>
       </c>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="6"/>
-      <c r="K45" s="6"/>
-      <c r="L45" s="6"/>
-      <c r="M45" s="6"/>
-      <c r="N45" s="7"/>
+      <c r="N45" s="6"/>
       <c r="P45" s="5"/>
-      <c r="Q45" s="6"/>
-      <c r="R45" s="6"/>
-      <c r="S45" s="6"/>
-      <c r="T45" s="6"/>
-      <c r="U45" s="6"/>
-      <c r="V45" s="6"/>
-      <c r="W45" s="6"/>
-      <c r="X45" s="6"/>
-      <c r="Y45" s="7"/>
+      <c r="Y45" s="6"/>
       <c r="AA45" s="5"/>
-      <c r="AB45" s="6"/>
-      <c r="AC45" s="6"/>
-      <c r="AD45" s="6"/>
-      <c r="AE45" s="6"/>
-      <c r="AF45" s="6"/>
-      <c r="AG45" s="6"/>
-      <c r="AH45" s="6"/>
-      <c r="AI45" s="7"/>
-    </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI45" s="6"/>
+    </row>
+    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
-      <c r="B46" s="20">
+      <c r="B46" s="19">
         <f t="shared" si="0"/>
         <v>4.6249999999999982</v>
       </c>
-      <c r="C46" s="15">
+      <c r="C46" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B46,тип_интерполяции_)</f>
         <v>4.2128095842994266</v>
       </c>
-      <c r="D46" s="15">
+      <c r="D46" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B46,тип_интерполяции_)</f>
         <v>3.2515070700967788</v>
       </c>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
-      <c r="K46" s="6"/>
-      <c r="L46" s="6"/>
-      <c r="M46" s="6"/>
-      <c r="N46" s="7"/>
+      <c r="N46" s="6"/>
       <c r="P46" s="5"/>
-      <c r="Q46" s="6"/>
-      <c r="R46" s="6"/>
-      <c r="S46" s="6"/>
-      <c r="T46" s="6"/>
-      <c r="U46" s="6"/>
-      <c r="V46" s="6"/>
-      <c r="W46" s="6"/>
-      <c r="X46" s="6"/>
-      <c r="Y46" s="7"/>
+      <c r="Y46" s="6"/>
       <c r="AA46" s="5"/>
-      <c r="AB46" s="6"/>
-      <c r="AC46" s="6"/>
-      <c r="AD46" s="6"/>
-      <c r="AE46" s="6"/>
-      <c r="AF46" s="6"/>
-      <c r="AG46" s="6"/>
-      <c r="AH46" s="6"/>
-      <c r="AI46" s="7"/>
-    </row>
-    <row r="47" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI46" s="6"/>
+    </row>
+    <row r="47" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
-      <c r="B47" s="20">
+      <c r="B47" s="19">
         <f t="shared" si="0"/>
         <v>4.7699999999999978</v>
       </c>
-      <c r="C47" s="15">
+      <c r="C47" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B47,тип_интерполяции_)</f>
         <v>4.5151597724834316</v>
       </c>
-      <c r="D47" s="15">
+      <c r="D47" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B47,тип_интерполяции_)</f>
         <v>3.2461632944952541</v>
       </c>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="6"/>
-      <c r="K47" s="6"/>
-      <c r="L47" s="6"/>
-      <c r="M47" s="6"/>
-      <c r="N47" s="7"/>
+      <c r="N47" s="6"/>
       <c r="P47" s="5"/>
-      <c r="Q47" s="6"/>
-      <c r="R47" s="6"/>
-      <c r="S47" s="6"/>
-      <c r="T47" s="6"/>
-      <c r="U47" s="6"/>
-      <c r="V47" s="6"/>
-      <c r="W47" s="6"/>
-      <c r="X47" s="6"/>
-      <c r="Y47" s="7"/>
+      <c r="Y47" s="6"/>
       <c r="AA47" s="5"/>
-      <c r="AB47" s="6"/>
-      <c r="AC47" s="6"/>
-      <c r="AD47" s="6"/>
-      <c r="AE47" s="6"/>
-      <c r="AF47" s="6"/>
-      <c r="AG47" s="6"/>
-      <c r="AH47" s="6"/>
-      <c r="AI47" s="7"/>
-    </row>
-    <row r="48" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI47" s="6"/>
+    </row>
+    <row r="48" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
-      <c r="B48" s="20">
+      <c r="B48" s="19">
         <f t="shared" si="0"/>
         <v>4.9149999999999974</v>
       </c>
-      <c r="C48" s="15">
+      <c r="C48" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B48,тип_интерполяции_)</f>
         <v>4.8205236651169265</v>
       </c>
-      <c r="D48" s="15">
+      <c r="D48" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B48,тип_интерполяции_)</f>
         <v>3.2400388657236543</v>
       </c>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="6"/>
-      <c r="K48" s="6"/>
-      <c r="L48" s="6"/>
-      <c r="M48" s="6"/>
-      <c r="N48" s="7"/>
+      <c r="N48" s="6"/>
       <c r="P48" s="5"/>
-      <c r="Q48" s="6"/>
-      <c r="R48" s="6"/>
-      <c r="S48" s="6"/>
-      <c r="T48" s="6"/>
-      <c r="U48" s="6"/>
-      <c r="V48" s="6"/>
-      <c r="W48" s="6"/>
-      <c r="X48" s="6"/>
-      <c r="Y48" s="7"/>
+      <c r="Y48" s="6"/>
       <c r="AA48" s="5"/>
-      <c r="AB48" s="6"/>
-      <c r="AC48" s="6"/>
-      <c r="AD48" s="6"/>
-      <c r="AE48" s="6"/>
-      <c r="AF48" s="6"/>
-      <c r="AG48" s="6"/>
-      <c r="AH48" s="6"/>
-      <c r="AI48" s="7"/>
-    </row>
-    <row r="49" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI48" s="6"/>
+    </row>
+    <row r="49" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A49" s="5"/>
-      <c r="B49" s="20">
+      <c r="B49" s="19">
         <f t="shared" si="0"/>
         <v>5.0599999999999969</v>
       </c>
-      <c r="C49" s="15">
+      <c r="C49" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B49,тип_интерполяции_)</f>
         <v>5.1266021229433152</v>
       </c>
-      <c r="D49" s="15">
+      <c r="D49" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B49,тип_интерполяции_)</f>
         <v>3.2339905739296486</v>
       </c>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6"/>
-      <c r="J49" s="6"/>
-      <c r="K49" s="6"/>
-      <c r="L49" s="6"/>
-      <c r="M49" s="6"/>
-      <c r="N49" s="7"/>
+      <c r="N49" s="6"/>
       <c r="P49" s="5"/>
-      <c r="Q49" s="6"/>
-      <c r="R49" s="6"/>
-      <c r="S49" s="6"/>
-      <c r="T49" s="6"/>
-      <c r="U49" s="6"/>
-      <c r="V49" s="6"/>
-      <c r="W49" s="6"/>
-      <c r="X49" s="6"/>
-      <c r="Y49" s="7"/>
+      <c r="Y49" s="6"/>
       <c r="AA49" s="5"/>
-      <c r="AB49" s="6"/>
-      <c r="AC49" s="6"/>
-      <c r="AD49" s="6"/>
-      <c r="AE49" s="6"/>
-      <c r="AF49" s="6"/>
-      <c r="AG49" s="6"/>
-      <c r="AH49" s="6"/>
-      <c r="AI49" s="7"/>
-    </row>
-    <row r="50" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI49" s="6"/>
+    </row>
+    <row r="50" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A50" s="5"/>
-      <c r="B50" s="20">
+      <c r="B50" s="19">
         <f t="shared" si="0"/>
         <v>5.2049999999999965</v>
       </c>
-      <c r="C50" s="15">
+      <c r="C50" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B50,тип_интерполяции_)</f>
         <v>5.4319680726500961</v>
       </c>
-      <c r="D50" s="15">
+      <c r="D50" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B50,тип_интерполяции_)</f>
         <v>3.2288752092609045</v>
       </c>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="6"/>
-      <c r="K50" s="6"/>
-      <c r="L50" s="6"/>
-      <c r="M50" s="6"/>
-      <c r="N50" s="7"/>
+      <c r="N50" s="6"/>
       <c r="P50" s="5"/>
-      <c r="Q50" s="6"/>
-      <c r="R50" s="6"/>
-      <c r="S50" s="6"/>
-      <c r="T50" s="6"/>
-      <c r="U50" s="6"/>
-      <c r="V50" s="6"/>
-      <c r="W50" s="6"/>
-      <c r="X50" s="6"/>
-      <c r="Y50" s="7"/>
+      <c r="Y50" s="6"/>
       <c r="AA50" s="5"/>
-      <c r="AB50" s="6"/>
-      <c r="AC50" s="6"/>
-      <c r="AD50" s="6"/>
-      <c r="AE50" s="6"/>
-      <c r="AF50" s="6"/>
-      <c r="AG50" s="6"/>
-      <c r="AH50" s="6"/>
-      <c r="AI50" s="7"/>
-    </row>
-    <row r="51" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI50" s="6"/>
+    </row>
+    <row r="51" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
-      <c r="B51" s="20">
+      <c r="B51" s="19">
         <f t="shared" si="0"/>
         <v>5.3499999999999961</v>
       </c>
-      <c r="C51" s="15">
+      <c r="C51" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B51,тип_интерполяции_)</f>
         <v>5.7362869528311204</v>
       </c>
-      <c r="D51" s="15">
+      <c r="D51" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B51,тип_интерполяции_)</f>
         <v>3.2255495618650905</v>
       </c>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="6"/>
-      <c r="K51" s="6"/>
-      <c r="L51" s="6"/>
-      <c r="M51" s="6"/>
-      <c r="N51" s="7"/>
+      <c r="N51" s="6"/>
       <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="6"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="6"/>
-      <c r="Y51" s="7"/>
+      <c r="Y51" s="6"/>
       <c r="AA51" s="5"/>
-      <c r="AB51" s="6"/>
-      <c r="AC51" s="6"/>
-      <c r="AD51" s="6"/>
-      <c r="AE51" s="6"/>
-      <c r="AF51" s="6"/>
-      <c r="AG51" s="6"/>
-      <c r="AH51" s="6"/>
-      <c r="AI51" s="7"/>
-    </row>
-    <row r="52" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI51" s="6"/>
+    </row>
+    <row r="52" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
-      <c r="B52" s="20">
+      <c r="B52" s="19">
         <f t="shared" si="0"/>
         <v>5.4949999999999957</v>
       </c>
-      <c r="C52" s="15">
+      <c r="C52" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B52,тип_интерполяции_)</f>
         <v>6.0392932962437218</v>
       </c>
-      <c r="D52" s="15">
+      <c r="D52" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B52,тип_интерполяции_)</f>
         <v>3.2248704218898752</v>
       </c>
-      <c r="E52" s="6"/>
-      <c r="F52" s="6"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="6"/>
-      <c r="K52" s="6"/>
-      <c r="L52" s="6"/>
-      <c r="M52" s="6"/>
-      <c r="N52" s="7"/>
+      <c r="N52" s="6"/>
       <c r="P52" s="5"/>
-      <c r="Q52" s="6"/>
-      <c r="R52" s="6"/>
-      <c r="S52" s="6"/>
-      <c r="T52" s="6"/>
-      <c r="U52" s="6"/>
-      <c r="V52" s="6"/>
-      <c r="W52" s="6"/>
-      <c r="X52" s="6"/>
-      <c r="Y52" s="7"/>
+      <c r="Y52" s="6"/>
       <c r="AA52" s="5"/>
-      <c r="AB52" s="6"/>
-      <c r="AC52" s="6"/>
-      <c r="AD52" s="6"/>
-      <c r="AE52" s="6"/>
-      <c r="AF52" s="6"/>
-      <c r="AG52" s="6"/>
-      <c r="AH52" s="6"/>
-      <c r="AI52" s="7"/>
-    </row>
-    <row r="53" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI52" s="6"/>
+    </row>
+    <row r="53" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
-      <c r="B53" s="20">
+      <c r="B53" s="19">
         <f t="shared" si="0"/>
         <v>5.6399999999999952</v>
       </c>
-      <c r="C53" s="15">
+      <c r="C53" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B53,тип_интерполяции_)</f>
         <v>6.3407216356452354</v>
       </c>
-      <c r="D53" s="15">
+      <c r="D53" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B53,тип_интерполяции_)</f>
         <v>3.2276945794829266</v>
       </c>
-      <c r="E53" s="6"/>
-      <c r="F53" s="6"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="6"/>
-      <c r="K53" s="6"/>
-      <c r="L53" s="6"/>
-      <c r="M53" s="6"/>
-      <c r="N53" s="7"/>
+      <c r="N53" s="6"/>
       <c r="P53" s="5"/>
-      <c r="Q53" s="6"/>
-      <c r="R53" s="6"/>
-      <c r="S53" s="6"/>
-      <c r="T53" s="6"/>
-      <c r="U53" s="6"/>
-      <c r="V53" s="6"/>
-      <c r="W53" s="6"/>
-      <c r="X53" s="6"/>
-      <c r="Y53" s="7"/>
+      <c r="Y53" s="6"/>
       <c r="AA53" s="5"/>
-      <c r="AB53" s="6"/>
-      <c r="AC53" s="6"/>
-      <c r="AD53" s="6"/>
-      <c r="AE53" s="6"/>
-      <c r="AF53" s="6"/>
-      <c r="AG53" s="6"/>
-      <c r="AH53" s="6"/>
-      <c r="AI53" s="7"/>
-    </row>
-    <row r="54" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI53" s="6"/>
+    </row>
+    <row r="54" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A54" s="5"/>
-      <c r="B54" s="20">
+      <c r="B54" s="19">
         <f t="shared" si="0"/>
         <v>5.7849999999999948</v>
       </c>
-      <c r="C54" s="15">
+      <c r="C54" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B54,тип_интерполяции_)</f>
         <v>6.6403065037929947</v>
       </c>
-      <c r="D54" s="15">
+      <c r="D54" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B54,тип_интерполяции_)</f>
         <v>3.2348788247919127</v>
       </c>
-      <c r="E54" s="6"/>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
-      <c r="K54" s="6"/>
-      <c r="L54" s="6"/>
-      <c r="M54" s="6"/>
-      <c r="N54" s="7"/>
+      <c r="N54" s="6"/>
       <c r="P54" s="5"/>
-      <c r="Q54" s="6"/>
-      <c r="R54" s="6"/>
-      <c r="S54" s="6"/>
-      <c r="T54" s="6"/>
-      <c r="U54" s="6"/>
-      <c r="V54" s="6"/>
-      <c r="W54" s="6"/>
-      <c r="X54" s="6"/>
-      <c r="Y54" s="7"/>
+      <c r="Y54" s="6"/>
       <c r="AA54" s="5"/>
-      <c r="AB54" s="6"/>
-      <c r="AC54" s="6"/>
-      <c r="AD54" s="6"/>
-      <c r="AE54" s="6"/>
-      <c r="AF54" s="6"/>
-      <c r="AG54" s="6"/>
-      <c r="AH54" s="6"/>
-      <c r="AI54" s="7"/>
-    </row>
-    <row r="55" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI54" s="6"/>
+    </row>
+    <row r="55" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
-      <c r="B55" s="20">
+      <c r="B55" s="19">
         <f t="shared" si="0"/>
         <v>5.9299999999999944</v>
       </c>
-      <c r="C55" s="15">
+      <c r="C55" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B55,тип_интерполяции_)</f>
         <v>6.9377824334443332</v>
       </c>
-      <c r="D55" s="15">
+      <c r="D55" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B55,тип_интерполяции_)</f>
         <v>3.2472799479645023</v>
       </c>
-      <c r="E55" s="6"/>
-      <c r="F55" s="6"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="6"/>
-      <c r="J55" s="6"/>
-      <c r="K55" s="6"/>
-      <c r="L55" s="6"/>
-      <c r="M55" s="6"/>
-      <c r="N55" s="7"/>
+      <c r="N55" s="6"/>
       <c r="P55" s="5"/>
-      <c r="Q55" s="6"/>
-      <c r="R55" s="6"/>
-      <c r="S55" s="6"/>
-      <c r="T55" s="6"/>
-      <c r="U55" s="6"/>
-      <c r="V55" s="6"/>
-      <c r="W55" s="6"/>
-      <c r="X55" s="6"/>
-      <c r="Y55" s="7"/>
+      <c r="Y55" s="6"/>
       <c r="AA55" s="5"/>
-      <c r="AB55" s="6"/>
-      <c r="AC55" s="6"/>
-      <c r="AD55" s="6"/>
-      <c r="AE55" s="6"/>
-      <c r="AF55" s="6"/>
-      <c r="AG55" s="6"/>
-      <c r="AH55" s="6"/>
-      <c r="AI55" s="7"/>
-    </row>
-    <row r="56" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI55" s="6"/>
+    </row>
+    <row r="56" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
-      <c r="B56" s="20">
+      <c r="B56" s="19">
         <f t="shared" si="0"/>
         <v>6.074999999999994</v>
       </c>
-      <c r="C56" s="15">
+      <c r="C56" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B56,тип_интерполяции_)</f>
         <v>7.2328839573565844</v>
       </c>
-      <c r="D56" s="15">
+      <c r="D56" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B56,тип_интерполяции_)</f>
         <v>3.2657547391483632</v>
       </c>
-      <c r="E56" s="6"/>
-      <c r="F56" s="6"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="6"/>
-      <c r="J56" s="6"/>
-      <c r="K56" s="6"/>
-      <c r="L56" s="6"/>
-      <c r="M56" s="6"/>
-      <c r="N56" s="7"/>
+      <c r="N56" s="6"/>
       <c r="P56" s="5"/>
-      <c r="Q56" s="6"/>
-      <c r="R56" s="6"/>
-      <c r="S56" s="6"/>
-      <c r="T56" s="6"/>
-      <c r="U56" s="6"/>
-      <c r="V56" s="6"/>
-      <c r="W56" s="6"/>
-      <c r="X56" s="6"/>
-      <c r="Y56" s="7"/>
+      <c r="Y56" s="6"/>
       <c r="AA56" s="5"/>
-      <c r="AB56" s="6"/>
-      <c r="AC56" s="6"/>
-      <c r="AD56" s="6"/>
-      <c r="AE56" s="6"/>
-      <c r="AF56" s="6"/>
-      <c r="AG56" s="6"/>
-      <c r="AH56" s="6"/>
-      <c r="AI56" s="7"/>
-    </row>
-    <row r="57" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI56" s="6"/>
+    </row>
+    <row r="57" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
-      <c r="B57" s="20">
+      <c r="B57" s="19">
         <f t="shared" si="0"/>
         <v>6.2199999999999935</v>
       </c>
-      <c r="C57" s="15">
+      <c r="C57" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B57,тип_интерполяции_)</f>
         <v>7.5253456082870835</v>
       </c>
-      <c r="D57" s="15">
+      <c r="D57" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B57,тип_интерполяции_)</f>
         <v>3.291159988491164</v>
       </c>
-      <c r="E57" s="6"/>
-      <c r="F57" s="6"/>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="6"/>
-      <c r="J57" s="6"/>
-      <c r="K57" s="6"/>
-      <c r="L57" s="6"/>
-      <c r="M57" s="6"/>
-      <c r="N57" s="7"/>
+      <c r="N57" s="6"/>
       <c r="P57" s="5"/>
-      <c r="Q57" s="6"/>
-      <c r="R57" s="6"/>
-      <c r="S57" s="6"/>
-      <c r="T57" s="6"/>
-      <c r="U57" s="6"/>
-      <c r="V57" s="6"/>
-      <c r="W57" s="6"/>
-      <c r="X57" s="6"/>
-      <c r="Y57" s="7"/>
+      <c r="Y57" s="6"/>
       <c r="AA57" s="5"/>
-      <c r="AB57" s="6"/>
-      <c r="AC57" s="6"/>
-      <c r="AD57" s="6"/>
-      <c r="AE57" s="6"/>
-      <c r="AF57" s="6"/>
-      <c r="AG57" s="6"/>
-      <c r="AH57" s="6"/>
-      <c r="AI57" s="7"/>
-    </row>
-    <row r="58" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AI57" s="6"/>
+    </row>
+    <row r="58" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A58" s="5"/>
-      <c r="B58" s="20">
+      <c r="B58" s="19">
         <f t="shared" si="0"/>
         <v>6.3649999999999931</v>
       </c>
-      <c r="C58" s="15">
+      <c r="C58" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B58,тип_интерполяции_)</f>
         <v>7.8149019189931641</v>
       </c>
-      <c r="D58" s="15">
+      <c r="D58" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B58,тип_интерполяции_)</f>
         <v>3.3243524861405724</v>
       </c>
-      <c r="E58" s="6"/>
-      <c r="F58" s="6"/>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="6"/>
-      <c r="J58" s="6"/>
-      <c r="K58" s="6"/>
-      <c r="L58" s="6"/>
-      <c r="M58" s="6"/>
-      <c r="N58" s="7"/>
+      <c r="N58" s="6"/>
       <c r="P58" s="5"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="6"/>
-      <c r="S58" s="6"/>
-      <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
-      <c r="V58" s="6"/>
-      <c r="W58" s="6"/>
-      <c r="X58" s="6"/>
-      <c r="Y58" s="7"/>
+      <c r="Y58" s="6"/>
       <c r="AA58" s="5"/>
-      <c r="AB58" s="6"/>
-      <c r="AC58" s="6"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="7"/>
-    </row>
-    <row r="59" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AI58" s="6"/>
+    </row>
+    <row r="59" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5"/>
-      <c r="B59" s="20">
+      <c r="B59" s="19">
         <f t="shared" si="0"/>
         <v>6.5099999999999927</v>
       </c>
-      <c r="C59" s="15">
+      <c r="C59" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B59,тип_интерполяции_)</f>
         <v>8.1012874222321596</v>
       </c>
-      <c r="D59" s="15">
+      <c r="D59" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B59,тип_интерполяции_)</f>
         <v>3.3661890222442574</v>
       </c>
-      <c r="E59" s="6"/>
-      <c r="F59" s="6"/>
-      <c r="G59" s="6"/>
-      <c r="H59" s="6"/>
-      <c r="I59" s="6"/>
-      <c r="J59" s="6"/>
-      <c r="K59" s="6"/>
-      <c r="L59" s="6"/>
-      <c r="M59" s="6"/>
-      <c r="N59" s="7"/>
-      <c r="P59" s="9"/>
-      <c r="Q59" s="10"/>
-      <c r="R59" s="10"/>
-      <c r="S59" s="10"/>
-      <c r="T59" s="10"/>
-      <c r="U59" s="10"/>
-      <c r="V59" s="10"/>
-      <c r="W59" s="10"/>
-      <c r="X59" s="10"/>
-      <c r="Y59" s="11"/>
-      <c r="AA59" s="9"/>
-      <c r="AB59" s="10"/>
-      <c r="AC59" s="10"/>
-      <c r="AD59" s="10"/>
-      <c r="AE59" s="10"/>
-      <c r="AF59" s="10"/>
-      <c r="AG59" s="10"/>
-      <c r="AH59" s="10"/>
-      <c r="AI59" s="11"/>
-    </row>
-    <row r="60" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="N59" s="6"/>
+      <c r="P59" s="8"/>
+      <c r="Q59" s="9"/>
+      <c r="R59" s="9"/>
+      <c r="S59" s="9"/>
+      <c r="T59" s="9"/>
+      <c r="U59" s="9"/>
+      <c r="V59" s="9"/>
+      <c r="W59" s="9"/>
+      <c r="X59" s="9"/>
+      <c r="Y59" s="10"/>
+      <c r="AA59" s="8"/>
+      <c r="AB59" s="9"/>
+      <c r="AC59" s="9"/>
+      <c r="AD59" s="9"/>
+      <c r="AE59" s="9"/>
+      <c r="AF59" s="9"/>
+      <c r="AG59" s="9"/>
+      <c r="AH59" s="9"/>
+      <c r="AI59" s="10"/>
+    </row>
+    <row r="60" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A60" s="5"/>
-      <c r="B60" s="20">
+      <c r="B60" s="19">
         <f t="shared" si="0"/>
         <v>6.6549999999999923</v>
       </c>
-      <c r="C60" s="15">
+      <c r="C60" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B60,тип_интерполяции_)</f>
         <v>8.3842366507614052</v>
       </c>
-      <c r="D60" s="15">
+      <c r="D60" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B60,тип_интерполяции_)</f>
         <v>3.4175263869498869</v>
       </c>
-      <c r="E60" s="6"/>
-      <c r="F60" s="6"/>
-      <c r="G60" s="6"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="6"/>
-      <c r="J60" s="6"/>
-      <c r="K60" s="6"/>
-      <c r="L60" s="6"/>
-      <c r="M60" s="6"/>
-      <c r="N60" s="7"/>
-    </row>
-    <row r="61" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="N60" s="6"/>
+    </row>
+    <row r="61" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
-      <c r="B61" s="20">
+      <c r="B61" s="19">
         <f t="shared" si="0"/>
         <v>6.7999999999999918</v>
       </c>
-      <c r="C61" s="15">
+      <c r="C61" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B61,тип_интерполяции_)</f>
         <v>8.6634841373382336</v>
       </c>
-      <c r="D61" s="15">
+      <c r="D61" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B61,тип_интерполяции_)</f>
         <v>3.4792213704051291</v>
       </c>
-      <c r="E61" s="6"/>
-      <c r="F61" s="6"/>
-      <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
-      <c r="I61" s="6"/>
-      <c r="J61" s="6"/>
-      <c r="K61" s="6"/>
-      <c r="L61" s="6"/>
-      <c r="M61" s="6"/>
-      <c r="N61" s="7"/>
-    </row>
-    <row r="62" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="N61" s="6"/>
+    </row>
+    <row r="62" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A62" s="5"/>
-      <c r="B62" s="20">
+      <c r="B62" s="19">
         <f t="shared" si="0"/>
         <v>6.9449999999999914</v>
       </c>
-      <c r="C62" s="15">
+      <c r="C62" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B62,тип_интерполяции_)</f>
         <v>8.9387644147199783</v>
       </c>
-      <c r="D62" s="15">
+      <c r="D62" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B62,тип_интерполяции_)</f>
         <v>3.5521307627576526</v>
       </c>
-      <c r="E62" s="6"/>
-      <c r="F62" s="6"/>
-      <c r="G62" s="6"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="6"/>
-      <c r="J62" s="6"/>
-      <c r="K62" s="6"/>
-      <c r="L62" s="6"/>
-      <c r="M62" s="6"/>
-      <c r="N62" s="7"/>
-    </row>
-    <row r="63" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="N62" s="6"/>
+    </row>
+    <row r="63" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A63" s="5"/>
-      <c r="B63" s="20">
+      <c r="B63" s="19">
         <f t="shared" si="0"/>
         <v>7.089999999999991</v>
       </c>
-      <c r="C63" s="15">
+      <c r="C63" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B63,тип_интерполяции_)</f>
         <v>9.2098120156639744</v>
       </c>
-      <c r="D63" s="15">
+      <c r="D63" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B63,тип_интерполяции_)</f>
         <v>3.6371113541551252</v>
       </c>
-      <c r="E63" s="6"/>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="6"/>
-      <c r="J63" s="6"/>
-      <c r="K63" s="6"/>
-      <c r="L63" s="6"/>
-      <c r="M63" s="6"/>
-      <c r="N63" s="7"/>
-    </row>
-    <row r="64" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="N63" s="6"/>
+    </row>
+    <row r="64" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A64" s="5"/>
-      <c r="B64" s="20">
+      <c r="B64" s="19">
         <f t="shared" si="0"/>
         <v>7.2349999999999905</v>
       </c>
-      <c r="C64" s="15">
+      <c r="C64" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B64,тип_интерполяции_)</f>
         <v>9.4763614729275556</v>
       </c>
-      <c r="D64" s="15">
+      <c r="D64" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B64,тип_интерполяции_)</f>
         <v>3.7350199347452153</v>
       </c>
-      <c r="E64" s="6"/>
-      <c r="F64" s="6"/>
-      <c r="G64" s="6"/>
-      <c r="H64" s="6"/>
-      <c r="I64" s="6"/>
-      <c r="J64" s="6"/>
-      <c r="K64" s="6"/>
-      <c r="L64" s="6"/>
-      <c r="M64" s="6"/>
-      <c r="N64" s="7"/>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N64" s="6"/>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
-      <c r="B65" s="20">
+      <c r="B65" s="19">
         <f t="shared" si="0"/>
         <v>7.3799999999999901</v>
       </c>
-      <c r="C65" s="15">
+      <c r="C65" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B65,тип_интерполяции_)</f>
         <v>9.7381473192680552</v>
       </c>
-      <c r="D65" s="15">
+      <c r="D65" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B65,тип_интерполяции_)</f>
         <v>3.8467132946755913</v>
       </c>
-      <c r="E65" s="6"/>
-      <c r="F65" s="6"/>
-      <c r="G65" s="6"/>
-      <c r="H65" s="6"/>
-      <c r="I65" s="6"/>
-      <c r="J65" s="6"/>
-      <c r="K65" s="6"/>
-      <c r="L65" s="6"/>
-      <c r="M65" s="6"/>
-      <c r="N65" s="7"/>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N65" s="6"/>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
-      <c r="B66" s="20">
+      <c r="B66" s="19">
         <f t="shared" si="0"/>
         <v>7.5249999999999897</v>
       </c>
-      <c r="C66" s="15">
+      <c r="C66" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B66,тип_интерполяции_)</f>
         <v>9.9949040874428068</v>
       </c>
-      <c r="D66" s="15">
+      <c r="D66" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B66,тип_интерполяции_)</f>
         <v>3.9730482240939216</v>
       </c>
-      <c r="E66" s="6"/>
-      <c r="F66" s="6"/>
-      <c r="G66" s="6"/>
-      <c r="H66" s="6"/>
-      <c r="I66" s="6"/>
-      <c r="J66" s="6"/>
-      <c r="K66" s="6"/>
-      <c r="L66" s="6"/>
-      <c r="M66" s="6"/>
-      <c r="N66" s="7"/>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N66" s="6"/>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="5"/>
-      <c r="B67" s="20">
+      <c r="B67" s="19">
         <f t="shared" si="0"/>
         <v>7.6699999999999893</v>
       </c>
-      <c r="C67" s="15">
+      <c r="C67" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B67,тип_интерполяции_)</f>
         <v>10.246366310209147</v>
       </c>
-      <c r="D67" s="15">
+      <c r="D67" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B67,тип_интерполяции_)</f>
         <v>4.114881513147874</v>
       </c>
-      <c r="E67" s="6"/>
-      <c r="F67" s="6"/>
-      <c r="G67" s="6"/>
-      <c r="H67" s="6"/>
-      <c r="I67" s="6"/>
-      <c r="J67" s="6"/>
-      <c r="K67" s="6"/>
-      <c r="L67" s="6"/>
-      <c r="M67" s="6"/>
-      <c r="N67" s="7"/>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N67" s="6"/>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="5"/>
-      <c r="B68" s="20">
+      <c r="B68" s="19">
         <f t="shared" si="0"/>
         <v>7.8149999999999888</v>
       </c>
-      <c r="C68" s="15">
+      <c r="C68" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B68,тип_интерполяции_)</f>
         <v>10.492268520324407</v>
       </c>
-      <c r="D68" s="15">
+      <c r="D68" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B68,тип_интерполяции_)</f>
         <v>4.273069951985117</v>
       </c>
-      <c r="E68" s="6"/>
-      <c r="F68" s="6"/>
-      <c r="G68" s="6"/>
-      <c r="H68" s="6"/>
-      <c r="I68" s="6"/>
-      <c r="J68" s="6"/>
-      <c r="K68" s="6"/>
-      <c r="L68" s="6"/>
-      <c r="M68" s="6"/>
-      <c r="N68" s="7"/>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N68" s="6"/>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="5"/>
-      <c r="B69" s="20">
+      <c r="B69" s="19">
         <f t="shared" si="0"/>
         <v>7.9599999999999884</v>
       </c>
-      <c r="C69" s="15">
+      <c r="C69" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B69,тип_интерполяции_)</f>
         <v>10.732345250545922</v>
       </c>
-      <c r="D69" s="15">
+      <c r="D69" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B69,тип_интерполяции_)</f>
         <v>4.4484703307533193</v>
       </c>
-      <c r="E69" s="6"/>
-      <c r="F69" s="6"/>
-      <c r="G69" s="6"/>
-      <c r="H69" s="6"/>
-      <c r="I69" s="6"/>
-      <c r="J69" s="6"/>
-      <c r="K69" s="6"/>
-      <c r="L69" s="6"/>
-      <c r="M69" s="6"/>
-      <c r="N69" s="7"/>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N69" s="6"/>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="5"/>
-      <c r="B70" s="20">
+      <c r="B70" s="19">
         <f t="shared" si="0"/>
         <v>8.104999999999988</v>
       </c>
-      <c r="C70" s="15">
+      <c r="C70" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B70,тип_интерполяции_)</f>
         <v>10.966331033631025</v>
       </c>
-      <c r="D70" s="15">
+      <c r="D70" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B70,тип_интерполяции_)</f>
         <v>4.6417851204921385</v>
       </c>
-      <c r="E70" s="6"/>
-      <c r="F70" s="6"/>
-      <c r="G70" s="6"/>
-      <c r="H70" s="6"/>
-      <c r="I70" s="6"/>
-      <c r="J70" s="6"/>
-      <c r="K70" s="6"/>
-      <c r="L70" s="6"/>
-      <c r="M70" s="6"/>
-      <c r="N70" s="7"/>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N70" s="6"/>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="5"/>
-      <c r="B71" s="20">
+      <c r="B71" s="19">
         <f t="shared" si="0"/>
         <v>8.2499999999999876</v>
       </c>
-      <c r="C71" s="15">
+      <c r="C71" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B71,тип_интерполяции_)</f>
         <v>11.193960402337051</v>
       </c>
-      <c r="D71" s="15">
+      <c r="D71" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B71,тип_интерполяции_)</f>
         <v>4.8522511523034257</v>
       </c>
-      <c r="E71" s="6"/>
-      <c r="F71" s="6"/>
-      <c r="G71" s="6"/>
-      <c r="H71" s="6"/>
-      <c r="I71" s="6"/>
-      <c r="J71" s="6"/>
-      <c r="K71" s="6"/>
-      <c r="L71" s="6"/>
-      <c r="M71" s="6"/>
-      <c r="N71" s="7"/>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N71" s="6"/>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="5"/>
-      <c r="B72" s="20">
+      <c r="B72" s="19">
         <f t="shared" si="0"/>
         <v>8.3949999999999871</v>
       </c>
-      <c r="C72" s="15">
+      <c r="C72" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B72,тип_интерполяции_)</f>
         <v>11.414967889421332</v>
       </c>
-      <c r="D72" s="15">
+      <c r="D72" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B72,тип_интерполяции_)</f>
         <v>5.0782953360877778</v>
       </c>
-      <c r="E72" s="6"/>
-      <c r="F72" s="6"/>
-      <c r="G72" s="6"/>
-      <c r="H72" s="6"/>
-      <c r="I72" s="6"/>
-      <c r="J72" s="6"/>
-      <c r="K72" s="6"/>
-      <c r="L72" s="6"/>
-      <c r="M72" s="6"/>
-      <c r="N72" s="7"/>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N72" s="6"/>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="5"/>
-      <c r="B73" s="20">
+      <c r="B73" s="19">
         <f t="shared" si="0"/>
         <v>8.5399999999999867</v>
       </c>
-      <c r="C73" s="15">
+      <c r="C73" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B73,тип_интерполяции_)</f>
         <v>11.629088027641204</v>
       </c>
-      <c r="D73" s="15">
+      <c r="D73" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B73,тип_интерполяции_)</f>
         <v>5.3183360501203412</v>
       </c>
-      <c r="E73" s="6"/>
-      <c r="F73" s="6"/>
-      <c r="G73" s="6"/>
-      <c r="H73" s="6"/>
-      <c r="I73" s="6"/>
-      <c r="J73" s="6"/>
-      <c r="K73" s="6"/>
-      <c r="L73" s="6"/>
-      <c r="M73" s="6"/>
-      <c r="N73" s="7"/>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N73" s="6"/>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="5"/>
-      <c r="B74" s="20">
+      <c r="B74" s="19">
         <f t="shared" si="0"/>
         <v>8.6849999999999863</v>
       </c>
-      <c r="C74" s="15">
+      <c r="C74" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B74,тип_интерполяции_)</f>
         <v>11.836055349754002</v>
       </c>
-      <c r="D74" s="15">
+      <c r="D74" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B74,тип_интерполяции_)</f>
         <v>5.5707916726762647</v>
       </c>
-      <c r="E74" s="6"/>
-      <c r="F74" s="6"/>
-      <c r="G74" s="6"/>
-      <c r="H74" s="6"/>
-      <c r="I74" s="6"/>
-      <c r="J74" s="6"/>
-      <c r="K74" s="6"/>
-      <c r="L74" s="6"/>
-      <c r="M74" s="6"/>
-      <c r="N74" s="7"/>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N74" s="6"/>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="5"/>
-      <c r="B75" s="20">
+      <c r="B75" s="19">
         <f t="shared" si="0"/>
         <v>8.8299999999999859</v>
       </c>
-      <c r="C75" s="15">
+      <c r="C75" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B75,тип_интерполяции_)</f>
         <v>12.035604388517058</v>
       </c>
-      <c r="D75" s="15">
+      <c r="D75" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B75,тип_интерполяции_)</f>
         <v>5.8340805820306931</v>
       </c>
-      <c r="E75" s="6"/>
-      <c r="F75" s="6"/>
-      <c r="G75" s="6"/>
-      <c r="H75" s="6"/>
-      <c r="I75" s="6"/>
-      <c r="J75" s="6"/>
-      <c r="K75" s="6"/>
-      <c r="L75" s="6"/>
-      <c r="M75" s="6"/>
-      <c r="N75" s="7"/>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N75" s="6"/>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="5"/>
-      <c r="B76" s="20">
+      <c r="B76" s="19">
         <f t="shared" si="0"/>
         <v>8.9749999999999854</v>
       </c>
-      <c r="C76" s="15">
+      <c r="C76" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B76,тип_интерполяции_)</f>
         <v>12.227469676687704</v>
       </c>
-      <c r="D76" s="15">
+      <c r="D76" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B76,тип_интерполяции_)</f>
         <v>6.1066211564587745</v>
       </c>
-      <c r="E76" s="6"/>
-      <c r="F76" s="6"/>
-      <c r="G76" s="6"/>
-      <c r="H76" s="6"/>
-      <c r="I76" s="6"/>
-      <c r="J76" s="6"/>
-      <c r="K76" s="6"/>
-      <c r="L76" s="6"/>
-      <c r="M76" s="6"/>
-      <c r="N76" s="7"/>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N76" s="6"/>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="5"/>
-      <c r="B77" s="20">
+      <c r="B77" s="19">
         <f t="shared" si="0"/>
         <v>9.119999999999985</v>
       </c>
-      <c r="C77" s="15">
+      <c r="C77" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B77,тип_интерполяции_)</f>
         <v>12.411385747023278</v>
       </c>
-      <c r="D77" s="15">
+      <c r="D77" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B77,тип_интерполяции_)</f>
         <v>6.3868317742356551</v>
       </c>
-      <c r="E77" s="6"/>
-      <c r="F77" s="6"/>
-      <c r="G77" s="6"/>
-      <c r="H77" s="6"/>
-      <c r="I77" s="6"/>
-      <c r="J77" s="6"/>
-      <c r="K77" s="6"/>
-      <c r="L77" s="6"/>
-      <c r="M77" s="6"/>
-      <c r="N77" s="7"/>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N77" s="6"/>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="5"/>
-      <c r="B78" s="20">
+      <c r="B78" s="19">
         <f t="shared" si="0"/>
         <v>9.2649999999999846</v>
       </c>
-      <c r="C78" s="15">
+      <c r="C78" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B78,тип_интерполяции_)</f>
         <v>12.587087132281111</v>
       </c>
-      <c r="D78" s="15">
+      <c r="D78" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B78,тип_интерполяции_)</f>
         <v>6.6731308136364822</v>
       </c>
-      <c r="E78" s="6"/>
-      <c r="F78" s="6"/>
-      <c r="G78" s="6"/>
-      <c r="H78" s="6"/>
-      <c r="I78" s="6"/>
-      <c r="J78" s="6"/>
-      <c r="K78" s="6"/>
-      <c r="L78" s="6"/>
-      <c r="M78" s="6"/>
-      <c r="N78" s="7"/>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N78" s="6"/>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="5"/>
-      <c r="B79" s="20">
+      <c r="B79" s="19">
         <f t="shared" si="0"/>
         <v>9.4099999999999842</v>
       </c>
-      <c r="C79" s="15">
+      <c r="C79" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B79,тип_интерполяции_)</f>
         <v>12.754308365218538</v>
       </c>
-      <c r="D79" s="15">
+      <c r="D79" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B79,тип_интерполяции_)</f>
         <v>6.9639366529364031</v>
       </c>
-      <c r="E79" s="6"/>
-      <c r="F79" s="6"/>
-      <c r="G79" s="6"/>
-      <c r="H79" s="6"/>
-      <c r="I79" s="6"/>
-      <c r="J79" s="6"/>
-      <c r="K79" s="6"/>
-      <c r="L79" s="6"/>
-      <c r="M79" s="6"/>
-      <c r="N79" s="7"/>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N79" s="6"/>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="5"/>
-      <c r="B80" s="20">
+      <c r="B80" s="19">
         <f t="shared" si="0"/>
         <v>9.5549999999999837</v>
       </c>
-      <c r="C80" s="15">
+      <c r="C80" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B80,тип_интерполяции_)</f>
         <v>12.912783978592895</v>
       </c>
-      <c r="D80" s="15">
+      <c r="D80" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B80,тип_интерполяции_)</f>
         <v>7.257667670410564</v>
       </c>
-      <c r="E80" s="6"/>
-      <c r="F80" s="6"/>
-      <c r="G80" s="6"/>
-      <c r="H80" s="6"/>
-      <c r="I80" s="6"/>
-      <c r="J80" s="6"/>
-      <c r="K80" s="6"/>
-      <c r="L80" s="6"/>
-      <c r="M80" s="6"/>
-      <c r="N80" s="7"/>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N80" s="6"/>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="5"/>
-      <c r="B81" s="20">
+      <c r="B81" s="19">
         <f t="shared" si="0"/>
         <v>9.6999999999999833</v>
       </c>
-      <c r="C81" s="15">
+      <c r="C81" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B81,тип_интерполяции_)</f>
         <v>13.062248505161511</v>
       </c>
-      <c r="D81" s="15">
+      <c r="D81" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B81,тип_интерполяции_)</f>
         <v>7.5527422443341123</v>
       </c>
-      <c r="E81" s="6"/>
-      <c r="F81" s="6"/>
-      <c r="G81" s="6"/>
-      <c r="H81" s="6"/>
-      <c r="I81" s="6"/>
-      <c r="J81" s="6"/>
-      <c r="K81" s="6"/>
-      <c r="L81" s="6"/>
-      <c r="M81" s="6"/>
-      <c r="N81" s="7"/>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N81" s="6"/>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="5"/>
-      <c r="B82" s="20">
+      <c r="B82" s="19">
         <f t="shared" si="0"/>
         <v>9.8449999999999829</v>
       </c>
-      <c r="C82" s="15">
+      <c r="C82" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B82,тип_интерполяции_)</f>
         <v>13.202436477681724</v>
       </c>
-      <c r="D82" s="15">
+      <c r="D82" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B82,тип_интерполяции_)</f>
         <v>7.8475787529821952</v>
       </c>
-      <c r="E82" s="6"/>
-      <c r="F82" s="6"/>
-      <c r="G82" s="6"/>
-      <c r="H82" s="6"/>
-      <c r="I82" s="6"/>
-      <c r="J82" s="6"/>
-      <c r="K82" s="6"/>
-      <c r="L82" s="6"/>
-      <c r="M82" s="6"/>
-      <c r="N82" s="7"/>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N82" s="6"/>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="5"/>
-      <c r="B83" s="20">
+      <c r="B83" s="19">
         <f t="shared" si="0"/>
         <v>9.9899999999999824</v>
       </c>
-      <c r="C83" s="15">
+      <c r="C83" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B83,тип_интерполяции_)</f>
         <v>13.333082428910867</v>
       </c>
-      <c r="D83" s="15">
+      <c r="D83" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B83,тип_интерполяции_)</f>
         <v>8.140595574629959</v>
       </c>
-      <c r="E83" s="6"/>
-      <c r="F83" s="6"/>
-      <c r="G83" s="6"/>
-      <c r="H83" s="6"/>
-      <c r="I83" s="6"/>
-      <c r="J83" s="6"/>
-      <c r="K83" s="6"/>
-      <c r="L83" s="6"/>
-      <c r="M83" s="6"/>
-      <c r="N83" s="7"/>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N83" s="6"/>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="5"/>
-      <c r="B84" s="20">
+      <c r="B84" s="19">
         <f t="shared" si="0"/>
         <v>10.134999999999982</v>
       </c>
-      <c r="C84" s="15">
+      <c r="C84" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B84,тип_интерполяции_)</f>
         <v>13.453920891606273</v>
       </c>
-      <c r="D84" s="15">
+      <c r="D84" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B84,тип_интерполяции_)</f>
         <v>8.43021108755255</v>
       </c>
-      <c r="E84" s="6"/>
-      <c r="F84" s="6"/>
-      <c r="G84" s="6"/>
-      <c r="H84" s="6"/>
-      <c r="I84" s="6"/>
-      <c r="J84" s="6"/>
-      <c r="K84" s="6"/>
-      <c r="L84" s="6"/>
-      <c r="M84" s="6"/>
-      <c r="N84" s="7"/>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N84" s="6"/>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="5"/>
-      <c r="B85" s="20">
+      <c r="B85" s="19">
         <f t="shared" si="0"/>
         <v>10.279999999999982</v>
       </c>
-      <c r="C85" s="15">
+      <c r="C85" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B85,тип_интерполяции_)</f>
         <v>13.564686398525279</v>
       </c>
-      <c r="D85" s="15">
+      <c r="D85" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B85,тип_интерполяции_)</f>
         <v>8.7148436700251164</v>
       </c>
-      <c r="E85" s="6"/>
-      <c r="F85" s="6"/>
-      <c r="G85" s="6"/>
-      <c r="H85" s="6"/>
-      <c r="I85" s="6"/>
-      <c r="J85" s="6"/>
-      <c r="K85" s="6"/>
-      <c r="L85" s="6"/>
-      <c r="M85" s="6"/>
-      <c r="N85" s="7"/>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N85" s="6"/>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="5"/>
-      <c r="B86" s="20">
+      <c r="B86" s="19">
         <f t="shared" si="0"/>
         <v>10.424999999999981</v>
       </c>
-      <c r="C86" s="15">
+      <c r="C86" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B86,тип_интерполяции_)</f>
         <v>13.665113482425214</v>
       </c>
-      <c r="D86" s="15">
+      <c r="D86" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B86,тип_интерполяции_)</f>
         <v>8.9929117003228054</v>
       </c>
-      <c r="E86" s="6"/>
-      <c r="F86" s="6"/>
-      <c r="G86" s="6"/>
-      <c r="H86" s="6"/>
-      <c r="I86" s="6"/>
-      <c r="J86" s="6"/>
-      <c r="K86" s="6"/>
-      <c r="L86" s="6"/>
-      <c r="M86" s="6"/>
-      <c r="N86" s="7"/>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N86" s="6"/>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="5"/>
-      <c r="B87" s="20">
+      <c r="B87" s="19">
         <f t="shared" ref="B87:B150" si="1">B86+($B$15-$B$7)/200</f>
         <v>10.569999999999981</v>
       </c>
-      <c r="C87" s="15">
+      <c r="C87" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B87,тип_интерполяции_)</f>
         <v>13.754936676063414</v>
       </c>
-      <c r="D87" s="15">
+      <c r="D87" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B87,тип_интерполяции_)</f>
         <v>9.2628335567207625</v>
       </c>
-      <c r="E87" s="6"/>
-      <c r="F87" s="6"/>
-      <c r="G87" s="6"/>
-      <c r="H87" s="6"/>
-      <c r="I87" s="6"/>
-      <c r="J87" s="6"/>
-      <c r="K87" s="6"/>
-      <c r="L87" s="6"/>
-      <c r="M87" s="6"/>
-      <c r="N87" s="7"/>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N87" s="6"/>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="5"/>
-      <c r="B88" s="20">
+      <c r="B88" s="19">
         <f t="shared" si="1"/>
         <v>10.71499999999998</v>
       </c>
-      <c r="C88" s="15">
+      <c r="C88" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B88,тип_интерполяции_)</f>
         <v>13.833890512197215</v>
       </c>
-      <c r="D88" s="15">
+      <c r="D88" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B88,тип_интерполяции_)</f>
         <v>9.5230276174941348</v>
       </c>
-      <c r="E88" s="6"/>
-      <c r="F88" s="6"/>
-      <c r="G88" s="6"/>
-      <c r="H88" s="6"/>
-      <c r="I88" s="6"/>
-      <c r="J88" s="6"/>
-      <c r="K88" s="6"/>
-      <c r="L88" s="6"/>
-      <c r="M88" s="6"/>
-      <c r="N88" s="7"/>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N88" s="6"/>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="5"/>
-      <c r="B89" s="20">
+      <c r="B89" s="19">
         <f t="shared" si="1"/>
         <v>10.85999999999998</v>
       </c>
-      <c r="C89" s="15">
+      <c r="C89" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B89,тип_интерполяции_)</f>
         <v>13.90170952358395</v>
       </c>
-      <c r="D89" s="15">
+      <c r="D89" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B89,тип_интерполяции_)</f>
         <v>9.7719122609180697</v>
       </c>
-      <c r="E89" s="6"/>
-      <c r="F89" s="6"/>
-      <c r="G89" s="6"/>
-      <c r="H89" s="6"/>
-      <c r="I89" s="6"/>
-      <c r="J89" s="6"/>
-      <c r="K89" s="6"/>
-      <c r="L89" s="6"/>
-      <c r="M89" s="6"/>
-      <c r="N89" s="7"/>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N89" s="6"/>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="5"/>
-      <c r="B90" s="20">
+      <c r="B90" s="19">
         <f t="shared" si="1"/>
         <v>11.004999999999979</v>
       </c>
-      <c r="C90" s="15">
+      <c r="C90" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B90,тип_интерполяции_)</f>
         <v>13.958128242980951</v>
       </c>
-      <c r="D90" s="15">
+      <c r="D90" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B90,тип_интерполяции_)</f>
         <v>10.007905884190327</v>
       </c>
-      <c r="E90" s="6"/>
-      <c r="F90" s="6"/>
-      <c r="G90" s="6"/>
-      <c r="H90" s="6"/>
-      <c r="I90" s="6"/>
-      <c r="J90" s="6"/>
-      <c r="K90" s="6"/>
-      <c r="L90" s="6"/>
-      <c r="M90" s="6"/>
-      <c r="N90" s="7"/>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N90" s="6"/>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="5"/>
-      <c r="B91" s="20">
+      <c r="B91" s="19">
         <f t="shared" si="1"/>
         <v>11.149999999999979</v>
       </c>
-      <c r="C91" s="15">
+      <c r="C91" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B91,тип_интерполяции_)</f>
         <v>14.002881203145554</v>
       </c>
-      <c r="D91" s="15">
+      <c r="D91" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B91,тип_интерполяции_)</f>
         <v>10.229937719369381</v>
       </c>
-      <c r="E91" s="6"/>
-      <c r="F91" s="6"/>
-      <c r="G91" s="6"/>
-      <c r="H91" s="6"/>
-      <c r="I91" s="6"/>
-      <c r="J91" s="6"/>
-      <c r="K91" s="6"/>
-      <c r="L91" s="6"/>
-      <c r="M91" s="6"/>
-      <c r="N91" s="7"/>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N91" s="6"/>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="5"/>
-      <c r="B92" s="20">
+      <c r="B92" s="19">
         <f t="shared" si="1"/>
         <v>11.294999999999979</v>
       </c>
-      <c r="C92" s="15">
+      <c r="C92" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B92,тип_интерполяции_)</f>
         <v>14.035702936835092</v>
       </c>
-      <c r="D92" s="15">
+      <c r="D92" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B92,тип_интерполяции_)</f>
         <v>10.438779777181308</v>
       </c>
-      <c r="E92" s="6"/>
-      <c r="F92" s="6"/>
-      <c r="G92" s="6"/>
-      <c r="H92" s="6"/>
-      <c r="I92" s="6"/>
-      <c r="J92" s="6"/>
-      <c r="K92" s="6"/>
-      <c r="L92" s="6"/>
-      <c r="M92" s="6"/>
-      <c r="N92" s="7"/>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N92" s="6"/>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
-      <c r="B93" s="20">
+      <c r="B93" s="19">
         <f t="shared" si="1"/>
         <v>11.439999999999978</v>
       </c>
-      <c r="C93" s="15">
+      <c r="C93" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B93,тип_интерполяции_)</f>
         <v>14.056327976806898</v>
       </c>
-      <c r="D93" s="15">
+      <c r="D93" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B93,тип_интерполяции_)</f>
         <v>10.635619457552895</v>
       </c>
-      <c r="E93" s="6"/>
-      <c r="F93" s="6"/>
-      <c r="G93" s="6"/>
-      <c r="H93" s="6"/>
-      <c r="I93" s="6"/>
-      <c r="J93" s="6"/>
-      <c r="K93" s="6"/>
-      <c r="L93" s="6"/>
-      <c r="M93" s="6"/>
-      <c r="N93" s="7"/>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N93" s="6"/>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="5"/>
-      <c r="B94" s="20">
+      <c r="B94" s="19">
         <f t="shared" si="1"/>
         <v>11.584999999999978</v>
       </c>
-      <c r="C94" s="15">
+      <c r="C94" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B94,тип_интерполяции_)</f>
         <v>14.064490855818308</v>
       </c>
-      <c r="D94" s="15">
+      <c r="D94" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B94,тип_интерполяции_)</f>
         <v>10.821644160410932</v>
       </c>
-      <c r="E94" s="6"/>
-      <c r="F94" s="6"/>
-      <c r="G94" s="6"/>
-      <c r="H94" s="6"/>
-      <c r="I94" s="6"/>
-      <c r="J94" s="6"/>
-      <c r="K94" s="6"/>
-      <c r="L94" s="6"/>
-      <c r="M94" s="6"/>
-      <c r="N94" s="7"/>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N94" s="6"/>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="5"/>
-      <c r="B95" s="20">
+      <c r="B95" s="19">
         <f t="shared" si="1"/>
         <v>11.729999999999977</v>
       </c>
-      <c r="C95" s="15">
+      <c r="C95" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B95,тип_интерполяции_)</f>
         <v>14.059926106626655</v>
       </c>
-      <c r="D95" s="15">
+      <c r="D95" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B95,тип_интерполяции_)</f>
         <v>10.998041285682204</v>
       </c>
-      <c r="E95" s="6"/>
-      <c r="F95" s="6"/>
-      <c r="G95" s="6"/>
-      <c r="H95" s="6"/>
-      <c r="I95" s="6"/>
-      <c r="J95" s="6"/>
-      <c r="K95" s="6"/>
-      <c r="L95" s="6"/>
-      <c r="M95" s="6"/>
-      <c r="N95" s="7"/>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N95" s="6"/>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="5"/>
-      <c r="B96" s="20">
+      <c r="B96" s="19">
         <f t="shared" si="1"/>
         <v>11.874999999999977</v>
       </c>
-      <c r="C96" s="15">
+      <c r="C96" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B96,тип_интерполяции_)</f>
         <v>14.042368261989274</v>
       </c>
-      <c r="D96" s="15">
+      <c r="D96" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B96,тип_интерполяции_)</f>
         <v>11.1659982332935</v>
       </c>
-      <c r="E96" s="6"/>
-      <c r="F96" s="6"/>
-      <c r="G96" s="6"/>
-      <c r="H96" s="6"/>
-      <c r="I96" s="6"/>
-      <c r="J96" s="6"/>
-      <c r="K96" s="6"/>
-      <c r="L96" s="6"/>
-      <c r="M96" s="6"/>
-      <c r="N96" s="7"/>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N96" s="6"/>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="5"/>
-      <c r="B97" s="20">
+      <c r="B97" s="19">
         <f t="shared" si="1"/>
         <v>12.019999999999976</v>
       </c>
-      <c r="C97" s="15">
+      <c r="C97" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B97,тип_интерполяции_)</f>
         <v>14.011551854663496</v>
       </c>
-      <c r="D97" s="15">
+      <c r="D97" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B97,тип_интерполяции_)</f>
         <v>11.326702403171609</v>
       </c>
-      <c r="E97" s="6"/>
-      <c r="F97" s="6"/>
-      <c r="G97" s="6"/>
-      <c r="H97" s="6"/>
-      <c r="I97" s="6"/>
-      <c r="J97" s="6"/>
-      <c r="K97" s="6"/>
-      <c r="L97" s="6"/>
-      <c r="M97" s="6"/>
-      <c r="N97" s="7"/>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N97" s="6"/>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="5"/>
-      <c r="B98" s="20">
+      <c r="B98" s="19">
         <f t="shared" si="1"/>
         <v>12.164999999999976</v>
       </c>
-      <c r="C98" s="15">
+      <c r="C98" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B98,тип_интерполяции_)</f>
         <v>13.967211417406659</v>
       </c>
-      <c r="D98" s="15">
+      <c r="D98" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B98,тип_интерполяции_)</f>
         <v>11.481341195243317</v>
       </c>
-      <c r="E98" s="6"/>
-      <c r="F98" s="6"/>
-      <c r="G98" s="6"/>
-      <c r="H98" s="6"/>
-      <c r="I98" s="6"/>
-      <c r="J98" s="6"/>
-      <c r="K98" s="6"/>
-      <c r="L98" s="6"/>
-      <c r="M98" s="6"/>
-      <c r="N98" s="7"/>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N98" s="6"/>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="5"/>
-      <c r="B99" s="20">
+      <c r="B99" s="19">
         <f t="shared" si="1"/>
         <v>12.309999999999976</v>
       </c>
-      <c r="C99" s="15">
+      <c r="C99" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B99,тип_интерполяции_)</f>
         <v>13.909081482976093</v>
       </c>
-      <c r="D99" s="15">
+      <c r="D99" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B99,тип_интерполяции_)</f>
         <v>11.631102009435415</v>
       </c>
-      <c r="E99" s="6"/>
-      <c r="F99" s="6"/>
-      <c r="G99" s="6"/>
-      <c r="H99" s="6"/>
-      <c r="I99" s="6"/>
-      <c r="J99" s="6"/>
-      <c r="K99" s="6"/>
-      <c r="L99" s="6"/>
-      <c r="M99" s="6"/>
-      <c r="N99" s="7"/>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N99" s="6"/>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="5"/>
-      <c r="B100" s="20">
+      <c r="B100" s="19">
         <f t="shared" si="1"/>
         <v>12.454999999999975</v>
       </c>
-      <c r="C100" s="15">
+      <c r="C100" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B100,тип_интерполяции_)</f>
         <v>13.836896584129134</v>
       </c>
-      <c r="D100" s="15">
+      <c r="D100" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B100,тип_интерполяции_)</f>
         <v>11.777172245674686</v>
       </c>
-      <c r="E100" s="6"/>
-      <c r="F100" s="6"/>
-      <c r="G100" s="6"/>
-      <c r="H100" s="6"/>
-      <c r="I100" s="6"/>
-      <c r="J100" s="6"/>
-      <c r="K100" s="6"/>
-      <c r="L100" s="6"/>
-      <c r="M100" s="6"/>
-      <c r="N100" s="7"/>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N100" s="6"/>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="5"/>
-      <c r="B101" s="20">
+      <c r="B101" s="19">
         <f t="shared" si="1"/>
         <v>12.599999999999975</v>
       </c>
-      <c r="C101" s="15">
+      <c r="C101" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B101,тип_интерполяции_)</f>
         <v>13.750391253623116</v>
       </c>
-      <c r="D101" s="15">
+      <c r="D101" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B101,тип_интерполяции_)</f>
         <v>11.920739303887922</v>
       </c>
-      <c r="E101" s="6"/>
-      <c r="F101" s="6"/>
-      <c r="G101" s="6"/>
-      <c r="H101" s="6"/>
-      <c r="I101" s="6"/>
-      <c r="J101" s="6"/>
-      <c r="K101" s="6"/>
-      <c r="L101" s="6"/>
-      <c r="M101" s="6"/>
-      <c r="N101" s="7"/>
-    </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N101" s="6"/>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" s="5"/>
-      <c r="B102" s="20">
+      <c r="B102" s="19">
         <f t="shared" si="1"/>
         <v>12.744999999999974</v>
       </c>
-      <c r="C102" s="15">
+      <c r="C102" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B102,тип_интерполяции_)</f>
         <v>13.649300024215373</v>
       </c>
-      <c r="D102" s="15">
+      <c r="D102" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B102,тип_интерполяции_)</f>
         <v>12.062990584001909</v>
       </c>
-      <c r="E102" s="6"/>
-      <c r="F102" s="6"/>
-      <c r="G102" s="6"/>
-      <c r="H102" s="6"/>
-      <c r="I102" s="6"/>
-      <c r="J102" s="6"/>
-      <c r="K102" s="6"/>
-      <c r="L102" s="6"/>
-      <c r="M102" s="6"/>
-      <c r="N102" s="7"/>
-    </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N102" s="6"/>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="5"/>
-      <c r="B103" s="20">
+      <c r="B103" s="19">
         <f t="shared" si="1"/>
         <v>12.889999999999974</v>
       </c>
-      <c r="C103" s="15">
+      <c r="C103" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B103,тип_интерполяции_)</f>
         <v>13.533357428663237</v>
       </c>
-      <c r="D103" s="15">
+      <c r="D103" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B103,тип_интерполяции_)</f>
         <v>12.205113485943434</v>
       </c>
-      <c r="E103" s="6"/>
-      <c r="F103" s="6"/>
-      <c r="G103" s="6"/>
-      <c r="H103" s="6"/>
-      <c r="I103" s="6"/>
-      <c r="J103" s="6"/>
-      <c r="K103" s="6"/>
-      <c r="L103" s="6"/>
-      <c r="M103" s="6"/>
-      <c r="N103" s="7"/>
-    </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N103" s="6"/>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="5"/>
-      <c r="B104" s="20">
+      <c r="B104" s="19">
         <f t="shared" si="1"/>
         <v>13.034999999999973</v>
       </c>
-      <c r="C104" s="15">
+      <c r="C104" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B104,тип_интерполяции_)</f>
         <v>13.402297999724045</v>
       </c>
-      <c r="D104" s="15">
+      <c r="D104" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B104,тип_интерполяции_)</f>
         <v>12.348295409639288</v>
       </c>
-      <c r="E104" s="6"/>
-      <c r="F104" s="6"/>
-      <c r="G104" s="6"/>
-      <c r="H104" s="6"/>
-      <c r="I104" s="6"/>
-      <c r="J104" s="6"/>
-      <c r="K104" s="6"/>
-      <c r="L104" s="6"/>
-      <c r="M104" s="6"/>
-      <c r="N104" s="7"/>
-    </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N104" s="6"/>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" s="5"/>
-      <c r="B105" s="20">
+      <c r="B105" s="19">
         <f t="shared" si="1"/>
         <v>13.179999999999973</v>
       </c>
-      <c r="C105" s="15">
+      <c r="C105" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B105,тип_интерполяции_)</f>
         <v>13.255856270155128</v>
       </c>
-      <c r="D105" s="15">
+      <c r="D105" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B105,тип_интерполяции_)</f>
         <v>12.493723755016255</v>
       </c>
-      <c r="E105" s="6"/>
-      <c r="F105" s="6"/>
-      <c r="G105" s="6"/>
-      <c r="H105" s="6"/>
-      <c r="I105" s="6"/>
-      <c r="J105" s="6"/>
-      <c r="K105" s="6"/>
-      <c r="L105" s="6"/>
-      <c r="M105" s="6"/>
-      <c r="N105" s="7"/>
-    </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N105" s="6"/>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" s="5"/>
-      <c r="B106" s="20">
+      <c r="B106" s="19">
         <f t="shared" si="1"/>
         <v>13.324999999999973</v>
       </c>
-      <c r="C106" s="15">
+      <c r="C106" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B106,тип_интерполяции_)</f>
         <v>13.093766772713824</v>
       </c>
-      <c r="D106" s="15">
+      <c r="D106" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B106,тип_интерполяции_)</f>
         <v>12.642585922001127</v>
       </c>
-      <c r="E106" s="6"/>
-      <c r="F106" s="6"/>
-      <c r="G106" s="6"/>
-      <c r="H106" s="6"/>
-      <c r="I106" s="6"/>
-      <c r="J106" s="6"/>
-      <c r="K106" s="6"/>
-      <c r="L106" s="6"/>
-      <c r="M106" s="6"/>
-      <c r="N106" s="7"/>
-    </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N106" s="6"/>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" s="5"/>
-      <c r="B107" s="20">
+      <c r="B107" s="19">
         <f t="shared" si="1"/>
         <v>13.469999999999972</v>
       </c>
-      <c r="C107" s="15">
+      <c r="C107" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B107,тип_интерполяции_)</f>
         <v>12.915764040157462</v>
       </c>
-      <c r="D107" s="15">
+      <c r="D107" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B107,тип_интерполяции_)</f>
         <v>12.796069310520688</v>
       </c>
-      <c r="E107" s="6"/>
-      <c r="F107" s="6"/>
-      <c r="G107" s="6"/>
-      <c r="H107" s="6"/>
-      <c r="I107" s="6"/>
-      <c r="J107" s="6"/>
-      <c r="K107" s="6"/>
-      <c r="L107" s="6"/>
-      <c r="M107" s="6"/>
-      <c r="N107" s="7"/>
-    </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N107" s="6"/>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" s="5"/>
-      <c r="B108" s="20">
+      <c r="B108" s="19">
         <f t="shared" si="1"/>
         <v>13.614999999999972</v>
       </c>
-      <c r="C108" s="15">
+      <c r="C108" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B108,тип_интерполяции_)</f>
         <v>12.721582605243379</v>
       </c>
-      <c r="D108" s="15">
+      <c r="D108" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B108,тип_интерполяции_)</f>
         <v>12.955361320501728</v>
       </c>
-      <c r="E108" s="6"/>
-      <c r="F108" s="6"/>
-      <c r="G108" s="6"/>
-      <c r="H108" s="6"/>
-      <c r="I108" s="6"/>
-      <c r="J108" s="6"/>
-      <c r="K108" s="6"/>
-      <c r="L108" s="6"/>
-      <c r="M108" s="6"/>
-      <c r="N108" s="7"/>
-    </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N108" s="6"/>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" s="5"/>
-      <c r="B109" s="20">
+      <c r="B109" s="19">
         <f t="shared" si="1"/>
         <v>13.759999999999971</v>
       </c>
-      <c r="C109" s="15">
+      <c r="C109" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B109,тип_интерполяции_)</f>
         <v>12.510957000728908</v>
       </c>
-      <c r="D109" s="15">
+      <c r="D109" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B109,тип_интерполяции_)</f>
         <v>13.121649351871033</v>
       </c>
-      <c r="E109" s="6"/>
-      <c r="F109" s="6"/>
-      <c r="G109" s="6"/>
-      <c r="H109" s="6"/>
-      <c r="I109" s="6"/>
-      <c r="J109" s="6"/>
-      <c r="K109" s="6"/>
-      <c r="L109" s="6"/>
-      <c r="M109" s="6"/>
-      <c r="N109" s="7"/>
-    </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N109" s="6"/>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" s="5"/>
-      <c r="B110" s="20">
+      <c r="B110" s="19">
         <f t="shared" si="1"/>
         <v>13.904999999999971</v>
       </c>
-      <c r="C110" s="15">
+      <c r="C110" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B110,тип_интерполяции_)</f>
         <v>12.283621759371382</v>
       </c>
-      <c r="D110" s="15">
+      <c r="D110" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B110,тип_интерполяции_)</f>
         <v>13.296120804555393</v>
       </c>
-      <c r="E110" s="6"/>
-      <c r="F110" s="6"/>
-      <c r="G110" s="6"/>
-      <c r="H110" s="6"/>
-      <c r="I110" s="6"/>
-      <c r="J110" s="6"/>
-      <c r="K110" s="6"/>
-      <c r="L110" s="6"/>
-      <c r="M110" s="6"/>
-      <c r="N110" s="7"/>
-    </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N110" s="6"/>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" s="5"/>
-      <c r="B111" s="20">
+      <c r="B111" s="19">
         <f t="shared" si="1"/>
         <v>14.049999999999971</v>
       </c>
-      <c r="C111" s="15">
+      <c r="C111" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B111,тип_интерполяции_)</f>
         <v>12.039311413928138</v>
       </c>
-      <c r="D111" s="15">
+      <c r="D111" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B111,тип_интерполяции_)</f>
         <v>13.479963078481596</v>
       </c>
-      <c r="E111" s="6"/>
-      <c r="F111" s="6"/>
-      <c r="G111" s="6"/>
-      <c r="H111" s="6"/>
-      <c r="I111" s="6"/>
-      <c r="J111" s="6"/>
-      <c r="K111" s="6"/>
-      <c r="L111" s="6"/>
-      <c r="M111" s="6"/>
-      <c r="N111" s="7"/>
-    </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N111" s="6"/>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" s="5"/>
-      <c r="B112" s="20">
+      <c r="B112" s="19">
         <f t="shared" si="1"/>
         <v>14.19499999999997</v>
       </c>
-      <c r="C112" s="15">
+      <c r="C112" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B112,тип_интерполяции_)</f>
         <v>11.777760497156507</v>
       </c>
-      <c r="D112" s="15">
+      <c r="D112" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B112,тип_интерполяции_)</f>
         <v>13.674363573576427</v>
       </c>
-      <c r="E112" s="6"/>
-      <c r="F112" s="6"/>
-      <c r="G112" s="6"/>
-      <c r="H112" s="6"/>
-      <c r="I112" s="6"/>
-      <c r="J112" s="6"/>
-      <c r="K112" s="6"/>
-      <c r="L112" s="6"/>
-      <c r="M112" s="6"/>
-      <c r="N112" s="7"/>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N112" s="6"/>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" s="5"/>
-      <c r="B113" s="20">
+      <c r="B113" s="19">
         <f t="shared" si="1"/>
         <v>14.33999999999997</v>
       </c>
-      <c r="C113" s="15">
+      <c r="C113" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B113,тип_интерполяции_)</f>
         <v>11.498703541813823</v>
       </c>
-      <c r="D113" s="15">
+      <c r="D113" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B113,тип_интерполяции_)</f>
         <v>13.880509689766676</v>
       </c>
-      <c r="E113" s="6"/>
-      <c r="F113" s="6"/>
-      <c r="G113" s="6"/>
-      <c r="H113" s="6"/>
-      <c r="I113" s="6"/>
-      <c r="J113" s="6"/>
-      <c r="K113" s="6"/>
-      <c r="L113" s="6"/>
-      <c r="M113" s="6"/>
-      <c r="N113" s="7"/>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N113" s="6"/>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" s="5"/>
-      <c r="B114" s="20">
+      <c r="B114" s="19">
         <f t="shared" si="1"/>
         <v>14.484999999999969</v>
       </c>
-      <c r="C114" s="15">
+      <c r="C114" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B114,тип_интерполяции_)</f>
         <v>11.201875080657421</v>
       </c>
-      <c r="D114" s="15">
+      <c r="D114" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B114,тип_интерполяции_)</f>
         <v>14.099588826979131</v>
       </c>
-      <c r="E114" s="6"/>
-      <c r="F114" s="6"/>
-      <c r="G114" s="6"/>
-      <c r="H114" s="6"/>
-      <c r="I114" s="6"/>
-      <c r="J114" s="6"/>
-      <c r="K114" s="6"/>
-      <c r="L114" s="6"/>
-      <c r="M114" s="6"/>
-      <c r="N114" s="7"/>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N114" s="6"/>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" s="5"/>
-      <c r="B115" s="20">
+      <c r="B115" s="19">
         <f t="shared" si="1"/>
         <v>14.629999999999969</v>
       </c>
-      <c r="C115" s="15">
+      <c r="C115" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B115,тип_интерполяции_)</f>
         <v>10.887009646444636</v>
       </c>
-      <c r="D115" s="15">
+      <c r="D115" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B115,тип_интерполяции_)</f>
         <v>14.33278838514058</v>
       </c>
-      <c r="E115" s="6"/>
-      <c r="F115" s="6"/>
-      <c r="G115" s="6"/>
-      <c r="H115" s="6"/>
-      <c r="I115" s="6"/>
-      <c r="J115" s="6"/>
-      <c r="K115" s="6"/>
-      <c r="L115" s="6"/>
-      <c r="M115" s="6"/>
-      <c r="N115" s="7"/>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N115" s="6"/>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" s="5"/>
-      <c r="B116" s="20">
+      <c r="B116" s="19">
         <f t="shared" si="1"/>
         <v>14.774999999999968</v>
       </c>
-      <c r="C116" s="15">
+      <c r="C116" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B116,тип_интерполяции_)</f>
         <v>10.553841771932801</v>
       </c>
-      <c r="D116" s="15">
+      <c r="D116" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B116,тип_интерполяции_)</f>
         <v>14.58129576417781</v>
       </c>
-      <c r="E116" s="6"/>
-      <c r="F116" s="6"/>
-      <c r="G116" s="6"/>
-      <c r="H116" s="6"/>
-      <c r="I116" s="6"/>
-      <c r="J116" s="6"/>
-      <c r="K116" s="6"/>
-      <c r="L116" s="6"/>
-      <c r="M116" s="6"/>
-      <c r="N116" s="7"/>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N116" s="6"/>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" s="5"/>
-      <c r="B117" s="20">
+      <c r="B117" s="19">
         <f t="shared" si="1"/>
         <v>14.919999999999968</v>
       </c>
-      <c r="C117" s="15">
+      <c r="C117" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B117,тип_интерполяции_)</f>
         <v>10.202105989879248</v>
       </c>
-      <c r="D117" s="15">
+      <c r="D117" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B117,тип_интерполяции_)</f>
         <v>14.846298364017608</v>
       </c>
-      <c r="E117" s="6"/>
-      <c r="F117" s="6"/>
-      <c r="G117" s="6"/>
-      <c r="H117" s="6"/>
-      <c r="I117" s="6"/>
-      <c r="J117" s="6"/>
-      <c r="K117" s="6"/>
-      <c r="L117" s="6"/>
-      <c r="M117" s="6"/>
-      <c r="N117" s="7"/>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N117" s="6"/>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" s="5"/>
-      <c r="B118" s="20">
+      <c r="B118" s="19">
         <f t="shared" si="1"/>
         <v>15.064999999999968</v>
       </c>
-      <c r="C118" s="15">
+      <c r="C118" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B118,тип_интерполяции_)</f>
         <v>9.8315685866029074</v>
       </c>
-      <c r="D118" s="15">
+      <c r="D118" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B118,тип_интерполяции_)</f>
         <v>15.12891701587343</v>
       </c>
-      <c r="E118" s="6"/>
-      <c r="F118" s="6"/>
-      <c r="G118" s="6"/>
-      <c r="H118" s="6"/>
-      <c r="I118" s="6"/>
-      <c r="J118" s="6"/>
-      <c r="K118" s="6"/>
-      <c r="L118" s="6"/>
-      <c r="M118" s="6"/>
-      <c r="N118" s="7"/>
-    </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N118" s="6"/>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" s="5"/>
-      <c r="B119" s="20">
+      <c r="B119" s="19">
         <f t="shared" si="1"/>
         <v>15.209999999999967</v>
       </c>
-      <c r="C119" s="15">
+      <c r="C119" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B119,тип_интерполяции_)</f>
         <v>9.4429396388514864</v>
       </c>
-      <c r="D119" s="15">
+      <c r="D119" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B119,тип_интерполяции_)</f>
         <v>15.428293972451359</v>
       </c>
-      <c r="E119" s="6"/>
-      <c r="F119" s="6"/>
-      <c r="G119" s="6"/>
-      <c r="H119" s="6"/>
-      <c r="I119" s="6"/>
-      <c r="J119" s="6"/>
-      <c r="K119" s="6"/>
-      <c r="L119" s="6"/>
-      <c r="M119" s="6"/>
-      <c r="N119" s="7"/>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N119" s="6"/>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A120" s="5"/>
-      <c r="B120" s="20">
+      <c r="B120" s="19">
         <f t="shared" si="1"/>
         <v>15.354999999999967</v>
       </c>
-      <c r="C120" s="15">
+      <c r="C120" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B120,тип_интерполяции_)</f>
         <v>9.0380094659521344</v>
       </c>
-      <c r="D120" s="15">
+      <c r="D120" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B120,тип_интерполяции_)</f>
         <v>15.741306847311701</v>
       </c>
-      <c r="E120" s="6"/>
-      <c r="F120" s="6"/>
-      <c r="G120" s="6"/>
-      <c r="H120" s="6"/>
-      <c r="I120" s="6"/>
-      <c r="J120" s="6"/>
-      <c r="K120" s="6"/>
-      <c r="L120" s="6"/>
-      <c r="M120" s="6"/>
-      <c r="N120" s="7"/>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N120" s="6"/>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" s="5"/>
-      <c r="B121" s="20">
+      <c r="B121" s="19">
         <f t="shared" si="1"/>
         <v>15.499999999999966</v>
       </c>
-      <c r="C121" s="15">
+      <c r="C121" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B121,тип_интерполяции_)</f>
         <v>8.6186275873177056</v>
       </c>
-      <c r="D121" s="15">
+      <c r="D121" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B121,тип_интерполяции_)</f>
         <v>16.064709145935645</v>
       </c>
-      <c r="E121" s="6"/>
-      <c r="F121" s="6"/>
-      <c r="G121" s="6"/>
-      <c r="H121" s="6"/>
-      <c r="I121" s="6"/>
-      <c r="J121" s="6"/>
-      <c r="K121" s="6"/>
-      <c r="L121" s="6"/>
-      <c r="M121" s="6"/>
-      <c r="N121" s="7"/>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N121" s="6"/>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" s="5"/>
-      <c r="B122" s="20">
+      <c r="B122" s="19">
         <f t="shared" si="1"/>
         <v>15.644999999999966</v>
       </c>
-      <c r="C122" s="15">
+      <c r="C122" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B122,тип_интерполяции_)</f>
         <v>8.1866435223610541</v>
       </c>
-      <c r="D122" s="15">
+      <c r="D122" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B122,тип_интерполяции_)</f>
         <v>16.395254373804381</v>
       </c>
-      <c r="E122" s="6"/>
-      <c r="F122" s="6"/>
-      <c r="G122" s="6"/>
-      <c r="H122" s="6"/>
-      <c r="I122" s="6"/>
-      <c r="J122" s="6"/>
-      <c r="K122" s="6"/>
-      <c r="L122" s="6"/>
-      <c r="M122" s="6"/>
-      <c r="N122" s="7"/>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N122" s="6"/>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A123" s="5"/>
-      <c r="B123" s="20">
+      <c r="B123" s="19">
         <f t="shared" si="1"/>
         <v>15.789999999999965</v>
       </c>
-      <c r="C123" s="15">
+      <c r="C123" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B123,тип_интерполяции_)</f>
         <v>7.7439067904950294</v>
       </c>
-      <c r="D123" s="15">
+      <c r="D123" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B123,тип_интерполяции_)</f>
         <v>16.729696036399101</v>
       </c>
-      <c r="E123" s="6"/>
-      <c r="F123" s="6"/>
-      <c r="G123" s="6"/>
-      <c r="H123" s="6"/>
-      <c r="I123" s="6"/>
-      <c r="J123" s="6"/>
-      <c r="K123" s="6"/>
-      <c r="L123" s="6"/>
-      <c r="M123" s="6"/>
-      <c r="N123" s="7"/>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N123" s="6"/>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A124" s="5"/>
-      <c r="B124" s="20">
+      <c r="B124" s="19">
         <f t="shared" si="1"/>
         <v>15.934999999999965</v>
       </c>
-      <c r="C124" s="15">
+      <c r="C124" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B124,тип_интерполяции_)</f>
         <v>7.2922669111324865</v>
       </c>
-      <c r="D124" s="15">
+      <c r="D124" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B124,тип_интерполяции_)</f>
         <v>17.064787639200993</v>
       </c>
-      <c r="E124" s="6"/>
-      <c r="F124" s="6"/>
-      <c r="G124" s="6"/>
-      <c r="H124" s="6"/>
-      <c r="I124" s="6"/>
-      <c r="J124" s="6"/>
-      <c r="K124" s="6"/>
-      <c r="L124" s="6"/>
-      <c r="M124" s="6"/>
-      <c r="N124" s="7"/>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N124" s="6"/>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A125" s="5"/>
-      <c r="B125" s="20">
+      <c r="B125" s="19">
         <f t="shared" si="1"/>
         <v>16.079999999999966</v>
       </c>
-      <c r="C125" s="15">
+      <c r="C125" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B125,тип_интерполяции_)</f>
         <v>6.8335734036862714</v>
       </c>
-      <c r="D125" s="15">
+      <c r="D125" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B125,тип_интерполяции_)</f>
         <v>17.397282687691249</v>
       </c>
-      <c r="E125" s="6"/>
-      <c r="F125" s="6"/>
-      <c r="G125" s="6"/>
-      <c r="H125" s="6"/>
-      <c r="I125" s="6"/>
-      <c r="J125" s="6"/>
-      <c r="K125" s="6"/>
-      <c r="L125" s="6"/>
-      <c r="M125" s="6"/>
-      <c r="N125" s="7"/>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N125" s="6"/>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126" s="5"/>
-      <c r="B126" s="20">
+      <c r="B126" s="19">
         <f t="shared" si="1"/>
         <v>16.224999999999966</v>
       </c>
-      <c r="C126" s="15">
+      <c r="C126" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B126,тип_интерполяции_)</f>
         <v>6.3696757875692471</v>
       </c>
-      <c r="D126" s="15">
+      <c r="D126" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B126,тип_интерполяции_)</f>
         <v>17.723934687351054</v>
       </c>
-      <c r="E126" s="6"/>
-      <c r="F126" s="6"/>
-      <c r="G126" s="6"/>
-      <c r="H126" s="6"/>
-      <c r="I126" s="6"/>
-      <c r="J126" s="6"/>
-      <c r="K126" s="6"/>
-      <c r="L126" s="6"/>
-      <c r="M126" s="6"/>
-      <c r="N126" s="7"/>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N126" s="6"/>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A127" s="5"/>
-      <c r="B127" s="20">
+      <c r="B127" s="19">
         <f t="shared" si="1"/>
         <v>16.369999999999965</v>
       </c>
-      <c r="C127" s="15">
+      <c r="C127" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B127,тип_интерполяции_)</f>
         <v>5.9024235821942623</v>
       </c>
-      <c r="D127" s="15">
+      <c r="D127" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B127,тип_интерполяции_)</f>
         <v>18.041497143661601</v>
       </c>
-      <c r="E127" s="6"/>
-      <c r="F127" s="6"/>
-      <c r="G127" s="6"/>
-      <c r="H127" s="6"/>
-      <c r="I127" s="6"/>
-      <c r="J127" s="6"/>
-      <c r="K127" s="6"/>
-      <c r="L127" s="6"/>
-      <c r="M127" s="6"/>
-      <c r="N127" s="7"/>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N127" s="6"/>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A128" s="5"/>
-      <c r="B128" s="20">
+      <c r="B128" s="19">
         <f t="shared" si="1"/>
         <v>16.514999999999965</v>
       </c>
-      <c r="C128" s="15">
+      <c r="C128" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B128,тип_интерполяции_)</f>
         <v>5.4336663069741684</v>
       </c>
-      <c r="D128" s="15">
+      <c r="D128" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B128,тип_интерполяции_)</f>
         <v>18.346723562104081</v>
       </c>
-      <c r="E128" s="6"/>
-      <c r="F128" s="6"/>
-      <c r="G128" s="6"/>
-      <c r="H128" s="6"/>
-      <c r="I128" s="6"/>
-      <c r="J128" s="6"/>
-      <c r="K128" s="6"/>
-      <c r="L128" s="6"/>
-      <c r="M128" s="6"/>
-      <c r="N128" s="7"/>
-    </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N128" s="6"/>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A129" s="5"/>
-      <c r="B129" s="20">
+      <c r="B129" s="19">
         <f t="shared" si="1"/>
         <v>16.659999999999965</v>
       </c>
-      <c r="C129" s="15">
+      <c r="C129" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B129,тип_интерполяции_)</f>
         <v>4.9652534813218185</v>
       </c>
-      <c r="D129" s="15">
+      <c r="D129" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B129,тип_интерполяции_)</f>
         <v>18.636367448159685</v>
       </c>
-      <c r="E129" s="6"/>
-      <c r="F129" s="6"/>
-      <c r="G129" s="6"/>
-      <c r="H129" s="6"/>
-      <c r="I129" s="6"/>
-      <c r="J129" s="6"/>
-      <c r="K129" s="6"/>
-      <c r="L129" s="6"/>
-      <c r="M129" s="6"/>
-      <c r="N129" s="7"/>
-    </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N129" s="6"/>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A130" s="5"/>
-      <c r="B130" s="20">
+      <c r="B130" s="19">
         <f t="shared" si="1"/>
         <v>16.804999999999964</v>
       </c>
-      <c r="C130" s="15">
+      <c r="C130" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B130,тип_интерполяции_)</f>
         <v>4.499034624650065</v>
       </c>
-      <c r="D130" s="15">
+      <c r="D130" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B130,тип_интерполяции_)</f>
         <v>18.907182307309597</v>
       </c>
-      <c r="E130" s="6"/>
-      <c r="F130" s="6"/>
-      <c r="G130" s="6"/>
-      <c r="H130" s="6"/>
-      <c r="I130" s="6"/>
-      <c r="J130" s="6"/>
-      <c r="K130" s="6"/>
-      <c r="L130" s="6"/>
-      <c r="M130" s="6"/>
-      <c r="N130" s="7"/>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N130" s="6"/>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A131" s="5"/>
-      <c r="B131" s="20">
+      <c r="B131" s="19">
         <f t="shared" si="1"/>
         <v>16.949999999999964</v>
       </c>
-      <c r="C131" s="15">
+      <c r="C131" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B131,тип_интерполяции_)</f>
         <v>4.03685925637176</v>
       </c>
-      <c r="D131" s="15">
+      <c r="D131" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B131,тип_интерполяции_)</f>
         <v>19.155921645035011</v>
       </c>
-      <c r="E131" s="6"/>
-      <c r="F131" s="6"/>
-      <c r="G131" s="6"/>
-      <c r="H131" s="6"/>
-      <c r="I131" s="6"/>
-      <c r="J131" s="6"/>
-      <c r="K131" s="6"/>
-      <c r="L131" s="6"/>
-      <c r="M131" s="6"/>
-      <c r="N131" s="7"/>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N131" s="6"/>
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A132" s="5"/>
-      <c r="B132" s="20">
+      <c r="B132" s="19">
         <f t="shared" si="1"/>
         <v>17.094999999999963</v>
       </c>
-      <c r="C132" s="15">
+      <c r="C132" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B132,тип_интерполяции_)</f>
         <v>3.5805768958997568</v>
       </c>
-      <c r="D132" s="15">
+      <c r="D132" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B132,тип_интерполяции_)</f>
         <v>19.379338966817119</v>
       </c>
-      <c r="E132" s="6"/>
-      <c r="F132" s="6"/>
-      <c r="G132" s="6"/>
-      <c r="H132" s="6"/>
-      <c r="I132" s="6"/>
-      <c r="J132" s="6"/>
-      <c r="K132" s="6"/>
-      <c r="L132" s="6"/>
-      <c r="M132" s="6"/>
-      <c r="N132" s="7"/>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N132" s="6"/>
+    </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A133" s="5"/>
-      <c r="B133" s="20">
+      <c r="B133" s="19">
         <f t="shared" si="1"/>
         <v>17.239999999999963</v>
       </c>
-      <c r="C133" s="15">
+      <c r="C133" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B133,тип_интерполяции_)</f>
         <v>3.1320370626469076</v>
       </c>
-      <c r="D133" s="15">
+      <c r="D133" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B133,тип_интерполяции_)</f>
         <v>19.574187778137109</v>
       </c>
-      <c r="E133" s="6"/>
-      <c r="F133" s="6"/>
-      <c r="G133" s="6"/>
-      <c r="H133" s="6"/>
-      <c r="I133" s="6"/>
-      <c r="J133" s="6"/>
-      <c r="K133" s="6"/>
-      <c r="L133" s="6"/>
-      <c r="M133" s="6"/>
-      <c r="N133" s="7"/>
-    </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N133" s="6"/>
+    </row>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A134" s="5"/>
-      <c r="B134" s="20">
+      <c r="B134" s="19">
         <f t="shared" si="1"/>
         <v>17.384999999999962</v>
       </c>
-      <c r="C134" s="15">
+      <c r="C134" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B134,тип_интерполяции_)</f>
         <v>2.6930892760260647</v>
       </c>
-      <c r="D134" s="15">
+      <c r="D134" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B134,тип_интерполяции_)</f>
         <v>19.73722158447617</v>
       </c>
-      <c r="E134" s="6"/>
-      <c r="F134" s="6"/>
-      <c r="G134" s="6"/>
-      <c r="H134" s="6"/>
-      <c r="I134" s="6"/>
-      <c r="J134" s="6"/>
-      <c r="K134" s="6"/>
-      <c r="L134" s="6"/>
-      <c r="M134" s="6"/>
-      <c r="N134" s="7"/>
-    </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N134" s="6"/>
+    </row>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A135" s="5"/>
-      <c r="B135" s="20">
+      <c r="B135" s="19">
         <f t="shared" si="1"/>
         <v>17.529999999999962</v>
       </c>
-      <c r="C135" s="15">
+      <c r="C135" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B135,тип_интерполяции_)</f>
         <v>2.2655830554500818</v>
       </c>
-      <c r="D135" s="15">
+      <c r="D135" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B135,тип_интерполяции_)</f>
         <v>19.865193891315492</v>
       </c>
-      <c r="E135" s="6"/>
-      <c r="F135" s="6"/>
-      <c r="G135" s="6"/>
-      <c r="H135" s="6"/>
-      <c r="I135" s="6"/>
-      <c r="J135" s="6"/>
-      <c r="K135" s="6"/>
-      <c r="L135" s="6"/>
-      <c r="M135" s="6"/>
-      <c r="N135" s="7"/>
-    </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N135" s="6"/>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A136" s="5"/>
-      <c r="B136" s="20">
+      <c r="B136" s="19">
         <f t="shared" si="1"/>
         <v>17.674999999999962</v>
       </c>
-      <c r="C136" s="15">
+      <c r="C136" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B136,тип_интерполяции_)</f>
         <v>1.8513679203318101</v>
       </c>
-      <c r="D136" s="15">
+      <c r="D136" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B136,тип_интерполяции_)</f>
         <v>19.954858204136269</v>
       </c>
-      <c r="E136" s="6"/>
-      <c r="F136" s="6"/>
-      <c r="G136" s="6"/>
-      <c r="H136" s="6"/>
-      <c r="I136" s="6"/>
-      <c r="J136" s="6"/>
-      <c r="K136" s="6"/>
-      <c r="L136" s="6"/>
-      <c r="M136" s="6"/>
-      <c r="N136" s="7"/>
-    </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N136" s="6"/>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A137" s="5"/>
-      <c r="B137" s="20">
+      <c r="B137" s="19">
         <f t="shared" si="1"/>
         <v>17.819999999999961</v>
       </c>
-      <c r="C137" s="15">
+      <c r="C137" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B137,тип_интерполяции_)</f>
         <v>1.4522933900841031</v>
       </c>
-      <c r="D137" s="15">
+      <c r="D137" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B137,тип_интерполяции_)</f>
         <v>20.002968028419684</v>
       </c>
-      <c r="E137" s="6"/>
-      <c r="F137" s="6"/>
-      <c r="G137" s="6"/>
-      <c r="H137" s="6"/>
-      <c r="I137" s="6"/>
-      <c r="J137" s="6"/>
-      <c r="K137" s="6"/>
-      <c r="L137" s="6"/>
-      <c r="M137" s="6"/>
-      <c r="N137" s="7"/>
-    </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N137" s="6"/>
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A138" s="5"/>
-      <c r="B138" s="20">
+      <c r="B138" s="19">
         <f t="shared" si="1"/>
         <v>17.964999999999961</v>
       </c>
-      <c r="C138" s="15">
+      <c r="C138" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B138,тип_интерполяции_)</f>
         <v>1.070208984119813</v>
       </c>
-      <c r="D138" s="15">
+      <c r="D138" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B138,тип_интерполяции_)</f>
         <v>20.006276869646932</v>
       </c>
-      <c r="E138" s="6"/>
-      <c r="F138" s="6"/>
-      <c r="G138" s="6"/>
-      <c r="H138" s="6"/>
-      <c r="I138" s="6"/>
-      <c r="J138" s="6"/>
-      <c r="K138" s="6"/>
-      <c r="L138" s="6"/>
-      <c r="M138" s="6"/>
-      <c r="N138" s="7"/>
-    </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N138" s="6"/>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A139" s="5"/>
-      <c r="B139" s="20">
+      <c r="B139" s="19">
         <f t="shared" si="1"/>
         <v>18.10999999999996</v>
       </c>
-      <c r="C139" s="15">
+      <c r="C139" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B139,тип_интерполяции_)</f>
         <v>0.70696422185179231</v>
       </c>
-      <c r="D139" s="15">
+      <c r="D139" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B139,тип_интерполяции_)</f>
         <v>19.961923630734969</v>
       </c>
-      <c r="E139" s="6"/>
-      <c r="F139" s="6"/>
-      <c r="G139" s="6"/>
-      <c r="H139" s="6"/>
-      <c r="I139" s="6"/>
-      <c r="J139" s="6"/>
-      <c r="K139" s="6"/>
-      <c r="L139" s="6"/>
-      <c r="M139" s="6"/>
-      <c r="N139" s="7"/>
-    </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N139" s="6"/>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A140" s="5"/>
-      <c r="B140" s="20">
+      <c r="B140" s="19">
         <f t="shared" si="1"/>
         <v>18.25499999999996</v>
       </c>
-      <c r="C140" s="15">
+      <c r="C140" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B140,тип_интерполяции_)</f>
         <v>0.3644086226928937</v>
       </c>
-      <c r="D140" s="15">
+      <c r="D140" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B140,тип_интерполяции_)</f>
         <v>19.870306841541773</v>
       </c>
-      <c r="E140" s="6"/>
-      <c r="F140" s="6"/>
-      <c r="G140" s="6"/>
-      <c r="H140" s="6"/>
-      <c r="I140" s="6"/>
-      <c r="J140" s="6"/>
-      <c r="K140" s="6"/>
-      <c r="L140" s="6"/>
-      <c r="M140" s="6"/>
-      <c r="N140" s="7"/>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N140" s="6"/>
+    </row>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A141" s="5"/>
-      <c r="B141" s="20">
+      <c r="B141" s="19">
         <f t="shared" si="1"/>
         <v>18.399999999999959</v>
       </c>
-      <c r="C141" s="15">
+      <c r="C141" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B141,тип_интерполяции_)</f>
         <v>4.4391706055969843E-2</v>
       </c>
-      <c r="D141" s="15">
+      <c r="D141" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B141,тип_интерполяции_)</f>
         <v>19.733464056857823</v>
       </c>
-      <c r="E141" s="6"/>
-      <c r="F141" s="6"/>
-      <c r="G141" s="6"/>
-      <c r="H141" s="6"/>
-      <c r="I141" s="6"/>
-      <c r="J141" s="6"/>
-      <c r="K141" s="6"/>
-      <c r="L141" s="6"/>
-      <c r="M141" s="6"/>
-      <c r="N141" s="7"/>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N141" s="6"/>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A142" s="5"/>
-      <c r="B142" s="20">
+      <c r="B142" s="19">
         <f t="shared" si="1"/>
         <v>18.544999999999959</v>
       </c>
-      <c r="C142" s="15">
+      <c r="C142" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B142,тип_интерполяции_)</f>
         <v>-0.2512370086461268</v>
       </c>
-      <c r="D142" s="15">
+      <c r="D142" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B142,тип_интерполяции_)</f>
         <v>19.553445246135567</v>
       </c>
-      <c r="E142" s="6"/>
-      <c r="F142" s="6"/>
-      <c r="G142" s="6"/>
-      <c r="H142" s="6"/>
-      <c r="I142" s="6"/>
-      <c r="J142" s="6"/>
-      <c r="K142" s="6"/>
-      <c r="L142" s="6"/>
-      <c r="M142" s="6"/>
-      <c r="N142" s="7"/>
-    </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N142" s="6"/>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A143" s="5"/>
-      <c r="B143" s="20">
+      <c r="B143" s="19">
         <f t="shared" si="1"/>
         <v>18.689999999999959</v>
       </c>
-      <c r="C143" s="15">
+      <c r="C143" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B143,тип_интерполяции_)</f>
         <v>-0.5206280020005436</v>
       </c>
-      <c r="D143" s="15">
+      <c r="D143" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B143,тип_интерполяции_)</f>
         <v>19.332300378827433</v>
       </c>
-      <c r="E143" s="6"/>
-      <c r="F143" s="6"/>
-      <c r="G143" s="6"/>
-      <c r="H143" s="6"/>
-      <c r="I143" s="6"/>
-      <c r="J143" s="6"/>
-      <c r="K143" s="6"/>
-      <c r="L143" s="6"/>
-      <c r="M143" s="6"/>
-      <c r="N143" s="7"/>
-    </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N143" s="6"/>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A144" s="5"/>
-      <c r="B144" s="20">
+      <c r="B144" s="19">
         <f t="shared" si="1"/>
         <v>18.834999999999958</v>
       </c>
-      <c r="C144" s="15">
+      <c r="C144" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B144,тип_интерполяции_)</f>
         <v>-0.76193175459442808</v>
       </c>
-      <c r="D144" s="15">
+      <c r="D144" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B144,тип_интерполяции_)</f>
         <v>19.072079424385869</v>
       </c>
-      <c r="E144" s="6"/>
-      <c r="F144" s="6"/>
-      <c r="G144" s="6"/>
-      <c r="H144" s="6"/>
-      <c r="I144" s="6"/>
-      <c r="J144" s="6"/>
-      <c r="K144" s="6"/>
-      <c r="L144" s="6"/>
-      <c r="M144" s="6"/>
-      <c r="N144" s="7"/>
-    </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N144" s="6"/>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A145" s="5"/>
-      <c r="B145" s="20">
+      <c r="B145" s="19">
         <f t="shared" si="1"/>
         <v>18.979999999999958</v>
       </c>
-      <c r="C145" s="15">
+      <c r="C145" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B145,тип_интерполяции_)</f>
         <v>-0.97329874701492758</v>
       </c>
-      <c r="D145" s="15">
+      <c r="D145" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B145,тип_интерполяции_)</f>
         <v>18.774832352263306</v>
       </c>
-      <c r="E145" s="6"/>
-      <c r="F145" s="6"/>
-      <c r="G145" s="6"/>
-      <c r="H145" s="6"/>
-      <c r="I145" s="6"/>
-      <c r="J145" s="6"/>
-      <c r="K145" s="6"/>
-      <c r="L145" s="6"/>
-      <c r="M145" s="6"/>
-      <c r="N145" s="7"/>
-    </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N145" s="6"/>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A146" s="5"/>
-      <c r="B146" s="20">
+      <c r="B146" s="19">
         <f t="shared" si="1"/>
         <v>19.124999999999957</v>
       </c>
-      <c r="C146" s="15">
+      <c r="C146" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B146,тип_интерполяции_)</f>
         <v>-1.1532142606813363</v>
       </c>
-      <c r="D146" s="15">
+      <c r="D146" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B146,тип_интерполяции_)</f>
         <v>18.442609131912189</v>
       </c>
-      <c r="E146" s="6"/>
-      <c r="F146" s="6"/>
-      <c r="G146" s="6"/>
-      <c r="H146" s="6"/>
-      <c r="I146" s="6"/>
-      <c r="J146" s="6"/>
-      <c r="K146" s="6"/>
-      <c r="L146" s="6"/>
-      <c r="M146" s="6"/>
-      <c r="N146" s="7"/>
-    </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N146" s="6"/>
+    </row>
+    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A147" s="5"/>
-      <c r="B147" s="20">
+      <c r="B147" s="19">
         <f t="shared" si="1"/>
         <v>19.269999999999957</v>
       </c>
-      <c r="C147" s="15">
+      <c r="C147" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B147,тип_интерполяции_)</f>
         <v>-1.3021983946912843</v>
       </c>
-      <c r="D147" s="15">
+      <c r="D147" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B147,тип_интерполяции_)</f>
         <v>18.077459732784948</v>
       </c>
-      <c r="E147" s="6"/>
-      <c r="F147" s="6"/>
-      <c r="G147" s="6"/>
-      <c r="H147" s="6"/>
-      <c r="I147" s="6"/>
-      <c r="J147" s="6"/>
-      <c r="K147" s="6"/>
-      <c r="L147" s="6"/>
-      <c r="M147" s="6"/>
-      <c r="N147" s="7"/>
-    </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N147" s="6"/>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A148" s="5"/>
-      <c r="B148" s="20">
+      <c r="B148" s="19">
         <f t="shared" si="1"/>
         <v>19.414999999999957</v>
       </c>
-      <c r="C148" s="15">
+      <c r="C148" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B148,тип_интерполяции_)</f>
         <v>-1.4215357939658801</v>
       </c>
-      <c r="D148" s="15">
+      <c r="D148" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B148,тип_интерполяции_)</f>
         <v>17.681434124334029</v>
       </c>
-      <c r="E148" s="6"/>
-      <c r="F148" s="6"/>
-      <c r="G148" s="6"/>
-      <c r="H148" s="6"/>
-      <c r="I148" s="6"/>
-      <c r="J148" s="6"/>
-      <c r="K148" s="6"/>
-      <c r="L148" s="6"/>
-      <c r="M148" s="6"/>
-      <c r="N148" s="7"/>
-    </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N148" s="6"/>
+    </row>
+    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A149" s="5"/>
-      <c r="B149" s="20">
+      <c r="B149" s="19">
         <f t="shared" si="1"/>
         <v>19.559999999999956</v>
       </c>
-      <c r="C149" s="15">
+      <c r="C149" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B149,тип_интерполяции_)</f>
         <v>-1.5125124747704406</v>
       </c>
-      <c r="D149" s="15">
+      <c r="D149" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B149,тип_интерполяции_)</f>
         <v>17.256582276011866</v>
       </c>
-      <c r="E149" s="6"/>
-      <c r="F149" s="6"/>
-      <c r="G149" s="6"/>
-      <c r="H149" s="6"/>
-      <c r="I149" s="6"/>
-      <c r="J149" s="6"/>
-      <c r="K149" s="6"/>
-      <c r="L149" s="6"/>
-      <c r="M149" s="6"/>
-      <c r="N149" s="7"/>
-    </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N149" s="6"/>
+    </row>
+    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A150" s="5"/>
-      <c r="B150" s="20">
+      <c r="B150" s="19">
         <f t="shared" si="1"/>
         <v>19.704999999999956</v>
       </c>
-      <c r="C150" s="15">
+      <c r="C150" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B150,тип_интерполяции_)</f>
         <v>-1.5764144533702829</v>
       </c>
-      <c r="D150" s="15">
+      <c r="D150" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B150,тип_интерполяции_)</f>
         <v>16.804954157270899</v>
       </c>
-      <c r="E150" s="6"/>
-      <c r="F150" s="6"/>
-      <c r="G150" s="6"/>
-      <c r="H150" s="6"/>
-      <c r="I150" s="6"/>
-      <c r="J150" s="6"/>
-      <c r="K150" s="6"/>
-      <c r="L150" s="6"/>
-      <c r="M150" s="6"/>
-      <c r="N150" s="7"/>
-    </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N150" s="6"/>
+    </row>
+    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A151" s="5"/>
-      <c r="B151" s="20">
+      <c r="B151" s="19">
         <f t="shared" ref="B151:B196" si="2">B150+($B$15-$B$7)/200</f>
         <v>19.849999999999955</v>
       </c>
-      <c r="C151" s="15">
+      <c r="C151" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B151,тип_интерполяции_)</f>
         <v>-1.6145277460307235</v>
       </c>
-      <c r="D151" s="15">
+      <c r="D151" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B151,тип_интерполяции_)</f>
         <v>16.328599737563565</v>
       </c>
-      <c r="E151" s="6"/>
-      <c r="F151" s="6"/>
-      <c r="G151" s="6"/>
-      <c r="H151" s="6"/>
-      <c r="I151" s="6"/>
-      <c r="J151" s="6"/>
-      <c r="K151" s="6"/>
-      <c r="L151" s="6"/>
-      <c r="M151" s="6"/>
-      <c r="N151" s="7"/>
-    </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N151" s="6"/>
+    </row>
+    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A152" s="5"/>
-      <c r="B152" s="20">
+      <c r="B152" s="19">
         <f t="shared" si="2"/>
         <v>19.994999999999955</v>
       </c>
-      <c r="C152" s="15">
+      <c r="C152" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B152,тип_интерполяции_)</f>
         <v>-1.6281383690170796</v>
       </c>
-      <c r="D152" s="15">
+      <c r="D152" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B152,тип_интерполяции_)</f>
         <v>15.829568986342302</v>
       </c>
-      <c r="E152" s="6"/>
-      <c r="F152" s="6"/>
-      <c r="G152" s="6"/>
-      <c r="H152" s="6"/>
-      <c r="I152" s="6"/>
-      <c r="J152" s="6"/>
-      <c r="K152" s="6"/>
-      <c r="L152" s="6"/>
-      <c r="M152" s="6"/>
-      <c r="N152" s="7"/>
-    </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N152" s="6"/>
+    </row>
+    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A153" s="5"/>
-      <c r="B153" s="20">
+      <c r="B153" s="19">
         <f t="shared" si="2"/>
         <v>20.139999999999954</v>
       </c>
-      <c r="C153" s="15">
+      <c r="C153" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B153,тип_интерполяции_)</f>
         <v>-1.6185323385946679</v>
       </c>
-      <c r="D153" s="15">
+      <c r="D153" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B153,тип_интерполяции_)</f>
         <v>15.309911873059551</v>
       </c>
-      <c r="E153" s="6"/>
-      <c r="F153" s="6"/>
-      <c r="G153" s="6"/>
-      <c r="H153" s="6"/>
-      <c r="I153" s="6"/>
-      <c r="J153" s="6"/>
-      <c r="K153" s="6"/>
-      <c r="L153" s="6"/>
-      <c r="M153" s="6"/>
-      <c r="N153" s="7"/>
-    </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N153" s="6"/>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A154" s="5"/>
-      <c r="B154" s="20">
+      <c r="B154" s="19">
         <f t="shared" si="2"/>
         <v>20.284999999999954</v>
       </c>
-      <c r="C154" s="15">
+      <c r="C154" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B154,тип_интерполяции_)</f>
         <v>-1.5869956710288056</v>
       </c>
-      <c r="D154" s="15">
+      <c r="D154" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B154,тип_интерполяции_)</f>
         <v>14.771678367167748</v>
       </c>
-      <c r="E154" s="6"/>
-      <c r="F154" s="6"/>
-      <c r="G154" s="6"/>
-      <c r="H154" s="6"/>
-      <c r="I154" s="6"/>
-      <c r="J154" s="6"/>
-      <c r="K154" s="6"/>
-      <c r="L154" s="6"/>
-      <c r="M154" s="6"/>
-      <c r="N154" s="7"/>
-    </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N154" s="6"/>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A155" s="5"/>
-      <c r="B155" s="20">
+      <c r="B155" s="19">
         <f t="shared" si="2"/>
         <v>20.429999999999954</v>
       </c>
-      <c r="C155" s="15">
+      <c r="C155" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B155,тип_интерполяции_)</f>
         <v>-1.5348143825848093</v>
       </c>
-      <c r="D155" s="15">
+      <c r="D155" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B155,тип_интерполяции_)</f>
         <v>14.216918438119333</v>
       </c>
-      <c r="E155" s="6"/>
-      <c r="F155" s="6"/>
-      <c r="G155" s="6"/>
-      <c r="H155" s="6"/>
-      <c r="I155" s="6"/>
-      <c r="J155" s="6"/>
-      <c r="K155" s="6"/>
-      <c r="L155" s="6"/>
-      <c r="M155" s="6"/>
-      <c r="N155" s="7"/>
-    </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N155" s="6"/>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A156" s="5"/>
-      <c r="B156" s="20">
+      <c r="B156" s="19">
         <f t="shared" si="2"/>
         <v>20.574999999999953</v>
       </c>
-      <c r="C156" s="15">
+      <c r="C156" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B156,тип_интерполяции_)</f>
         <v>-1.4632744895279961</v>
       </c>
-      <c r="D156" s="15">
+      <c r="D156" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B156,тип_интерполяции_)</f>
         <v>13.647682055366742</v>
       </c>
-      <c r="E156" s="6"/>
-      <c r="F156" s="6"/>
-      <c r="G156" s="6"/>
-      <c r="H156" s="6"/>
-      <c r="I156" s="6"/>
-      <c r="J156" s="6"/>
-      <c r="K156" s="6"/>
-      <c r="L156" s="6"/>
-      <c r="M156" s="6"/>
-      <c r="N156" s="7"/>
-    </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N156" s="6"/>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A157" s="5"/>
-      <c r="B157" s="20">
+      <c r="B157" s="19">
         <f t="shared" si="2"/>
         <v>20.719999999999953</v>
       </c>
-      <c r="C157" s="15">
+      <c r="C157" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B157,тип_интерполяции_)</f>
         <v>-1.3736620081236826</v>
       </c>
-      <c r="D157" s="15">
+      <c r="D157" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B157,тип_интерполяции_)</f>
         <v>13.066019188362414</v>
       </c>
-      <c r="E157" s="6"/>
-      <c r="F157" s="6"/>
-      <c r="G157" s="6"/>
-      <c r="H157" s="6"/>
-      <c r="I157" s="6"/>
-      <c r="J157" s="6"/>
-      <c r="K157" s="6"/>
-      <c r="L157" s="6"/>
-      <c r="M157" s="6"/>
-      <c r="N157" s="7"/>
-    </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N157" s="6"/>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A158" s="5"/>
-      <c r="B158" s="20">
+      <c r="B158" s="19">
         <f t="shared" si="2"/>
         <v>20.864999999999952</v>
       </c>
-      <c r="C158" s="15">
+      <c r="C158" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B158,тип_интерполяции_)</f>
         <v>-1.2672629546371859</v>
       </c>
-      <c r="D158" s="15">
+      <c r="D158" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B158,тип_интерполяции_)</f>
         <v>12.473979806558789</v>
       </c>
-      <c r="E158" s="6"/>
-      <c r="F158" s="6"/>
-      <c r="G158" s="6"/>
-      <c r="H158" s="6"/>
-      <c r="I158" s="6"/>
-      <c r="J158" s="6"/>
-      <c r="K158" s="6"/>
-      <c r="L158" s="6"/>
-      <c r="M158" s="6"/>
-      <c r="N158" s="7"/>
-    </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N158" s="6"/>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A159" s="5"/>
-      <c r="B159" s="20">
+      <c r="B159" s="19">
         <f t="shared" si="2"/>
         <v>21.009999999999952</v>
       </c>
-      <c r="C159" s="15">
+      <c r="C159" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B159,тип_интерполяции_)</f>
         <v>-1.1453633453338228</v>
       </c>
-      <c r="D159" s="15">
+      <c r="D159" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B159,тип_интерполяции_)</f>
         <v>11.873613879408305</v>
       </c>
-      <c r="E159" s="6"/>
-      <c r="F159" s="6"/>
-      <c r="G159" s="6"/>
-      <c r="H159" s="6"/>
-      <c r="I159" s="6"/>
-      <c r="J159" s="6"/>
-      <c r="K159" s="6"/>
-      <c r="L159" s="6"/>
-      <c r="M159" s="6"/>
-      <c r="N159" s="7"/>
-    </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N159" s="6"/>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A160" s="5"/>
-      <c r="B160" s="20">
+      <c r="B160" s="19">
         <f t="shared" si="2"/>
         <v>21.154999999999951</v>
       </c>
-      <c r="C160" s="15">
+      <c r="C160" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B160,тип_интерполяции_)</f>
         <v>-1.0092491964789105</v>
       </c>
-      <c r="D160" s="15">
+      <c r="D160" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B160,тип_интерполяции_)</f>
         <v>11.266971376363399</v>
       </c>
-      <c r="E160" s="6"/>
-      <c r="F160" s="6"/>
-      <c r="G160" s="6"/>
-      <c r="H160" s="6"/>
-      <c r="I160" s="6"/>
-      <c r="J160" s="6"/>
-      <c r="K160" s="6"/>
-      <c r="L160" s="6"/>
-      <c r="M160" s="6"/>
-      <c r="N160" s="7"/>
-    </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N160" s="6"/>
+    </row>
+    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A161" s="5"/>
-      <c r="B161" s="20">
+      <c r="B161" s="19">
         <f t="shared" si="2"/>
         <v>21.299999999999951</v>
       </c>
-      <c r="C161" s="15">
+      <c r="C161" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B161,тип_интерполяции_)</f>
         <v>-0.86020652433776545</v>
       </c>
-      <c r="D161" s="15">
+      <c r="D161" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B161,тип_интерполяции_)</f>
         <v>10.656102266876511</v>
       </c>
-      <c r="E161" s="6"/>
-      <c r="F161" s="6"/>
-      <c r="G161" s="6"/>
-      <c r="H161" s="6"/>
-      <c r="I161" s="6"/>
-      <c r="J161" s="6"/>
-      <c r="K161" s="6"/>
-      <c r="L161" s="6"/>
-      <c r="M161" s="6"/>
-      <c r="N161" s="7"/>
-    </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N161" s="6"/>
+    </row>
+    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A162" s="5"/>
-      <c r="B162" s="20">
+      <c r="B162" s="19">
         <f t="shared" si="2"/>
         <v>21.444999999999951</v>
       </c>
-      <c r="C162" s="15">
+      <c r="C162" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B162,тип_интерполяции_)</f>
         <v>-0.69952134517570486</v>
       </c>
-      <c r="D162" s="15">
+      <c r="D162" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B162,тип_интерполяции_)</f>
         <v>10.043056520400077</v>
       </c>
-      <c r="E162" s="6"/>
-      <c r="F162" s="6"/>
-      <c r="G162" s="6"/>
-      <c r="H162" s="6"/>
-      <c r="I162" s="6"/>
-      <c r="J162" s="6"/>
-      <c r="K162" s="6"/>
-      <c r="L162" s="6"/>
-      <c r="M162" s="6"/>
-      <c r="N162" s="7"/>
-    </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N162" s="6"/>
+    </row>
+    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A163" s="5"/>
-      <c r="B163" s="20">
+      <c r="B163" s="19">
         <f t="shared" si="2"/>
         <v>21.58999999999995</v>
       </c>
-      <c r="C163" s="15">
+      <c r="C163" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B163,тип_интерполяции_)</f>
         <v>-0.52847967525804551</v>
       </c>
-      <c r="D163" s="15">
+      <c r="D163" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B163,тип_интерполяции_)</f>
         <v>9.4298841063865364</v>
       </c>
-      <c r="E163" s="6"/>
-      <c r="F163" s="6"/>
-      <c r="G163" s="6"/>
-      <c r="H163" s="6"/>
-      <c r="I163" s="6"/>
-      <c r="J163" s="6"/>
-      <c r="K163" s="6"/>
-      <c r="L163" s="6"/>
-      <c r="M163" s="6"/>
-      <c r="N163" s="7"/>
-    </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N163" s="6"/>
+    </row>
+    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A164" s="5"/>
-      <c r="B164" s="20">
+      <c r="B164" s="19">
         <f t="shared" si="2"/>
         <v>21.73499999999995</v>
       </c>
-      <c r="C164" s="15">
+      <c r="C164" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B164,тип_интерполяции_)</f>
         <v>-0.34836753085010425</v>
       </c>
-      <c r="D164" s="15">
+      <c r="D164" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B164,тип_интерполяции_)</f>
         <v>8.8186349942883275</v>
       </c>
-      <c r="E164" s="6"/>
-      <c r="F164" s="6"/>
-      <c r="G164" s="6"/>
-      <c r="H164" s="6"/>
-      <c r="I164" s="6"/>
-      <c r="J164" s="6"/>
-      <c r="K164" s="6"/>
-      <c r="L164" s="6"/>
-      <c r="M164" s="6"/>
-      <c r="N164" s="7"/>
-    </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N164" s="6"/>
+    </row>
+    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A165" s="5"/>
-      <c r="B165" s="20">
+      <c r="B165" s="19">
         <f t="shared" si="2"/>
         <v>21.879999999999949</v>
       </c>
-      <c r="C165" s="15">
+      <c r="C165" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B165,тип_интерполяции_)</f>
         <v>-0.16047092821719808</v>
       </c>
-      <c r="D165" s="15">
+      <c r="D165" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B165,тип_интерполяции_)</f>
         <v>8.2113591535578898</v>
       </c>
-      <c r="E165" s="6"/>
-      <c r="F165" s="6"/>
-      <c r="G165" s="6"/>
-      <c r="H165" s="6"/>
-      <c r="I165" s="6"/>
-      <c r="J165" s="6"/>
-      <c r="K165" s="6"/>
-      <c r="L165" s="6"/>
-      <c r="M165" s="6"/>
-      <c r="N165" s="7"/>
-    </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N165" s="6"/>
+    </row>
+    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A166" s="5"/>
-      <c r="B166" s="20">
+      <c r="B166" s="19">
         <f t="shared" si="2"/>
         <v>22.024999999999949</v>
       </c>
-      <c r="C166" s="15">
+      <c r="C166" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B166,тип_интерполяции_)</f>
         <v>3.3924506332920497E-2</v>
       </c>
-      <c r="D166" s="15">
+      <c r="D166" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B166,тип_интерполяции_)</f>
         <v>7.6101065536476602</v>
       </c>
-      <c r="E166" s="6"/>
-      <c r="F166" s="6"/>
-      <c r="G166" s="6"/>
-      <c r="H166" s="6"/>
-      <c r="I166" s="6"/>
-      <c r="J166" s="6"/>
-      <c r="K166" s="6"/>
-      <c r="L166" s="6"/>
-      <c r="M166" s="6"/>
-      <c r="N166" s="7"/>
-    </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N166" s="6"/>
+    </row>
+    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A167" s="5"/>
-      <c r="B167" s="20">
+      <c r="B167" s="19">
         <f t="shared" si="2"/>
         <v>22.169999999999948</v>
       </c>
-      <c r="C167" s="15">
+      <c r="C167" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B167,тип_интерполяции_)</f>
         <v>0.233654201799188</v>
       </c>
-      <c r="D167" s="15">
+      <c r="D167" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B167,тип_интерполяции_)</f>
         <v>7.0169271640100774</v>
       </c>
-      <c r="E167" s="6"/>
-      <c r="F167" s="6"/>
-      <c r="G167" s="6"/>
-      <c r="H167" s="6"/>
-      <c r="I167" s="6"/>
-      <c r="J167" s="6"/>
-      <c r="K167" s="6"/>
-      <c r="L167" s="6"/>
-      <c r="M167" s="6"/>
-      <c r="N167" s="7"/>
-    </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N167" s="6"/>
+    </row>
+    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A168" s="5"/>
-      <c r="B168" s="20">
+      <c r="B168" s="19">
         <f t="shared" si="2"/>
         <v>22.314999999999948</v>
       </c>
-      <c r="C168" s="15">
+      <c r="C168" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B168,тип_интерполяции_)</f>
         <v>0.43784552813134986</v>
       </c>
-      <c r="D168" s="15">
+      <c r="D168" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B168,тип_интерполяции_)</f>
         <v>6.4338709540975794</v>
       </c>
-      <c r="E168" s="6"/>
-      <c r="F168" s="6"/>
-      <c r="G168" s="6"/>
-      <c r="H168" s="6"/>
-      <c r="I168" s="6"/>
-      <c r="J168" s="6"/>
-      <c r="K168" s="6"/>
-      <c r="L168" s="6"/>
-      <c r="M168" s="6"/>
-      <c r="N168" s="7"/>
-    </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N168" s="6"/>
+    </row>
+    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A169" s="5"/>
-      <c r="B169" s="20">
+      <c r="B169" s="19">
         <f t="shared" si="2"/>
         <v>22.459999999999948</v>
       </c>
-      <c r="C169" s="15">
+      <c r="C169" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B169,тип_интерполяции_)</f>
         <v>0.64566898146613405</v>
       </c>
-      <c r="D169" s="15">
+      <c r="D169" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B169,тип_интерполяции_)</f>
         <v>5.8629878933626056</v>
       </c>
-      <c r="E169" s="6"/>
-      <c r="F169" s="6"/>
-      <c r="G169" s="6"/>
-      <c r="H169" s="6"/>
-      <c r="I169" s="6"/>
-      <c r="J169" s="6"/>
-      <c r="K169" s="6"/>
-      <c r="L169" s="6"/>
-      <c r="M169" s="6"/>
-      <c r="N169" s="7"/>
-    </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N169" s="6"/>
+    </row>
+    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A170" s="5"/>
-      <c r="B170" s="20">
+      <c r="B170" s="19">
         <f t="shared" si="2"/>
         <v>22.604999999999947</v>
       </c>
-      <c r="C170" s="15">
+      <c r="C170" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B170,тип_интерполяции_)</f>
         <v>0.85629505794026861</v>
       </c>
-      <c r="D170" s="15">
+      <c r="D170" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B170,тип_интерполяции_)</f>
         <v>5.3063279512575932</v>
       </c>
-      <c r="E170" s="6"/>
-      <c r="F170" s="6"/>
-      <c r="G170" s="6"/>
-      <c r="H170" s="6"/>
-      <c r="I170" s="6"/>
-      <c r="J170" s="6"/>
-      <c r="K170" s="6"/>
-      <c r="L170" s="6"/>
-      <c r="M170" s="6"/>
-      <c r="N170" s="7"/>
-    </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N170" s="6"/>
+    </row>
+    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A171" s="5"/>
-      <c r="B171" s="20">
+      <c r="B171" s="19">
         <f t="shared" si="2"/>
         <v>22.749999999999947</v>
       </c>
-      <c r="C171" s="15">
+      <c r="C171" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B171,тип_интерполяции_)</f>
         <v>1.0688942536904815</v>
       </c>
-      <c r="D171" s="15">
+      <c r="D171" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B171,тип_интерполяции_)</f>
         <v>4.7659410972349807</v>
       </c>
-      <c r="E171" s="6"/>
-      <c r="F171" s="6"/>
-      <c r="G171" s="6"/>
-      <c r="H171" s="6"/>
-      <c r="I171" s="6"/>
-      <c r="J171" s="6"/>
-      <c r="K171" s="6"/>
-      <c r="L171" s="6"/>
-      <c r="M171" s="6"/>
-      <c r="N171" s="7"/>
-    </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N171" s="6"/>
+    </row>
+    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A172" s="5"/>
-      <c r="B172" s="20">
+      <c r="B172" s="19">
         <f t="shared" si="2"/>
         <v>22.894999999999946</v>
       </c>
-      <c r="C172" s="15">
+      <c r="C172" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B172,тип_интерполяции_)</f>
         <v>1.2826370648535008</v>
       </c>
-      <c r="D172" s="15">
+      <c r="D172" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B172,тип_интерполяции_)</f>
         <v>4.243877300747207</v>
       </c>
-      <c r="E172" s="6"/>
-      <c r="F172" s="6"/>
-      <c r="G172" s="6"/>
-      <c r="H172" s="6"/>
-      <c r="I172" s="6"/>
-      <c r="J172" s="6"/>
-      <c r="K172" s="6"/>
-      <c r="L172" s="6"/>
-      <c r="M172" s="6"/>
-      <c r="N172" s="7"/>
-    </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N172" s="6"/>
+    </row>
+    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A173" s="5"/>
-      <c r="B173" s="20">
+      <c r="B173" s="19">
         <f t="shared" si="2"/>
         <v>23.039999999999946</v>
       </c>
-      <c r="C173" s="15">
+      <c r="C173" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B173,тип_интерполяции_)</f>
         <v>1.4966939875660545</v>
       </c>
-      <c r="D173" s="15">
+      <c r="D173" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B173,тип_интерполяции_)</f>
         <v>3.7421865312467104</v>
       </c>
-      <c r="E173" s="6"/>
-      <c r="F173" s="6"/>
-      <c r="G173" s="6"/>
-      <c r="H173" s="6"/>
-      <c r="I173" s="6"/>
-      <c r="J173" s="6"/>
-      <c r="K173" s="6"/>
-      <c r="L173" s="6"/>
-      <c r="M173" s="6"/>
-      <c r="N173" s="7"/>
-    </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N173" s="6"/>
+    </row>
+    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A174" s="5"/>
-      <c r="B174" s="20">
+      <c r="B174" s="19">
         <f t="shared" si="2"/>
         <v>23.184999999999945</v>
       </c>
-      <c r="C174" s="15">
+      <c r="C174" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B174,тип_интерполяции_)</f>
         <v>1.7102355179648705</v>
       </c>
-      <c r="D174" s="15">
+      <c r="D174" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B174,тип_интерполяции_)</f>
         <v>3.2629187581859282</v>
       </c>
-      <c r="E174" s="6"/>
-      <c r="F174" s="6"/>
-      <c r="G174" s="6"/>
-      <c r="H174" s="6"/>
-      <c r="I174" s="6"/>
-      <c r="J174" s="6"/>
-      <c r="K174" s="6"/>
-      <c r="L174" s="6"/>
-      <c r="M174" s="6"/>
-      <c r="N174" s="7"/>
-    </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N174" s="6"/>
+    </row>
+    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A175" s="5"/>
-      <c r="B175" s="20">
+      <c r="B175" s="19">
         <f t="shared" si="2"/>
         <v>23.329999999999945</v>
       </c>
-      <c r="C175" s="15">
+      <c r="C175" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B175,тип_интерполяции_)</f>
         <v>1.922432152186677</v>
       </c>
-      <c r="D175" s="15">
+      <c r="D175" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B175,тип_интерполяции_)</f>
         <v>2.8081239510172997</v>
       </c>
-      <c r="E175" s="6"/>
-      <c r="F175" s="6"/>
-      <c r="G175" s="6"/>
-      <c r="H175" s="6"/>
-      <c r="I175" s="6"/>
-      <c r="J175" s="6"/>
-      <c r="K175" s="6"/>
-      <c r="L175" s="6"/>
-      <c r="M175" s="6"/>
-      <c r="N175" s="7"/>
-    </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N175" s="6"/>
+    </row>
+    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A176" s="5"/>
-      <c r="B176" s="20">
+      <c r="B176" s="19">
         <f t="shared" si="2"/>
         <v>23.474999999999945</v>
       </c>
-      <c r="C176" s="15">
+      <c r="C176" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B176,тип_интерполяции_)</f>
         <v>2.1324543863682015</v>
       </c>
-      <c r="D176" s="15">
+      <c r="D176" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B176,тип_интерполяции_)</f>
         <v>2.3798520791932631</v>
       </c>
-      <c r="E176" s="6"/>
-      <c r="F176" s="6"/>
-      <c r="G176" s="6"/>
-      <c r="H176" s="6"/>
-      <c r="I176" s="6"/>
-      <c r="J176" s="6"/>
-      <c r="K176" s="6"/>
-      <c r="L176" s="6"/>
-      <c r="M176" s="6"/>
-      <c r="N176" s="7"/>
-    </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N176" s="6"/>
+    </row>
+    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A177" s="5"/>
-      <c r="B177" s="20">
+      <c r="B177" s="19">
         <f t="shared" si="2"/>
         <v>23.619999999999944</v>
       </c>
-      <c r="C177" s="15">
+      <c r="C177" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B177,тип_интерполяции_)</f>
         <v>2.3394727166461728</v>
       </c>
-      <c r="D177" s="15">
+      <c r="D177" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B177,тип_интерполяции_)</f>
         <v>1.9801531121662563</v>
       </c>
-      <c r="E177" s="6"/>
-      <c r="F177" s="6"/>
-      <c r="G177" s="6"/>
-      <c r="H177" s="6"/>
-      <c r="I177" s="6"/>
-      <c r="J177" s="6"/>
-      <c r="K177" s="6"/>
-      <c r="L177" s="6"/>
-      <c r="M177" s="6"/>
-      <c r="N177" s="7"/>
-    </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N177" s="6"/>
+    </row>
+    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A178" s="5"/>
-      <c r="B178" s="20">
+      <c r="B178" s="19">
         <f t="shared" si="2"/>
         <v>23.764999999999944</v>
       </c>
-      <c r="C178" s="15">
+      <c r="C178" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B178,тип_интерполяции_)</f>
         <v>2.5426576391573183</v>
       </c>
-      <c r="D178" s="15">
+      <c r="D178" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B178,тип_интерполяции_)</f>
         <v>1.6110770193887178</v>
       </c>
-      <c r="E178" s="6"/>
-      <c r="F178" s="6"/>
-      <c r="G178" s="6"/>
-      <c r="H178" s="6"/>
-      <c r="I178" s="6"/>
-      <c r="J178" s="6"/>
-      <c r="K178" s="6"/>
-      <c r="L178" s="6"/>
-      <c r="M178" s="6"/>
-      <c r="N178" s="7"/>
-    </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N178" s="6"/>
+    </row>
+    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A179" s="5"/>
-      <c r="B179" s="20">
+      <c r="B179" s="19">
         <f t="shared" si="2"/>
         <v>23.909999999999943</v>
       </c>
-      <c r="C179" s="15">
+      <c r="C179" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B179,тип_интерполяции_)</f>
         <v>2.7411796500383665</v>
       </c>
-      <c r="D179" s="15">
+      <c r="D179" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B179,тип_интерполяции_)</f>
         <v>1.2746737703130862</v>
       </c>
-      <c r="E179" s="6"/>
-      <c r="F179" s="6"/>
-      <c r="G179" s="6"/>
-      <c r="H179" s="6"/>
-      <c r="I179" s="6"/>
-      <c r="J179" s="6"/>
-      <c r="K179" s="6"/>
-      <c r="L179" s="6"/>
-      <c r="M179" s="6"/>
-      <c r="N179" s="7"/>
-    </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N179" s="6"/>
+    </row>
+    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A180" s="5"/>
-      <c r="B180" s="20">
+      <c r="B180" s="19">
         <f t="shared" si="2"/>
         <v>24.054999999999943</v>
       </c>
-      <c r="C180" s="15">
+      <c r="C180" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B180,тип_интерполяции_)</f>
         <v>2.9342092454260449</v>
       </c>
-      <c r="D180" s="15">
+      <c r="D180" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B180,тип_интерполяции_)</f>
         <v>0.97299333439179936</v>
       </c>
-      <c r="E180" s="6"/>
-      <c r="F180" s="6"/>
-      <c r="G180" s="6"/>
-      <c r="H180" s="6"/>
-      <c r="I180" s="6"/>
-      <c r="J180" s="6"/>
-      <c r="K180" s="6"/>
-      <c r="L180" s="6"/>
-      <c r="M180" s="6"/>
-      <c r="N180" s="7"/>
-    </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N180" s="6"/>
+    </row>
+    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A181" s="5"/>
-      <c r="B181" s="20">
+      <c r="B181" s="19">
         <f t="shared" si="2"/>
         <v>24.199999999999942</v>
       </c>
-      <c r="C181" s="15">
+      <c r="C181" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B181,тип_интерполяции_)</f>
         <v>3.1209169214570815</v>
       </c>
-      <c r="D181" s="15">
+      <c r="D181" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B181,тип_интерполяции_)</f>
         <v>0.70808568107729597</v>
       </c>
-      <c r="E181" s="6"/>
-      <c r="F181" s="6"/>
-      <c r="G181" s="6"/>
-      <c r="H181" s="6"/>
-      <c r="I181" s="6"/>
-      <c r="J181" s="6"/>
-      <c r="K181" s="6"/>
-      <c r="L181" s="6"/>
-      <c r="M181" s="6"/>
-      <c r="N181" s="7"/>
-    </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N181" s="6"/>
+    </row>
+    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A182" s="5"/>
-      <c r="B182" s="20">
+      <c r="B182" s="19">
         <f t="shared" si="2"/>
         <v>24.344999999999942</v>
       </c>
-      <c r="C182" s="15">
+      <c r="C182" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B182,тип_интерполяции_)</f>
         <v>3.300473174268205</v>
       </c>
-      <c r="D182" s="15">
+      <c r="D182" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B182,тип_интерполяции_)</f>
         <v>0.48200077982201417</v>
       </c>
-      <c r="E182" s="6"/>
-      <c r="F182" s="6"/>
-      <c r="G182" s="6"/>
-      <c r="H182" s="6"/>
-      <c r="I182" s="6"/>
-      <c r="J182" s="6"/>
-      <c r="K182" s="6"/>
-      <c r="L182" s="6"/>
-      <c r="M182" s="6"/>
-      <c r="N182" s="7"/>
-    </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N182" s="6"/>
+    </row>
+    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A183" s="5"/>
-      <c r="B183" s="20">
+      <c r="B183" s="19">
         <f t="shared" si="2"/>
         <v>24.489999999999942</v>
       </c>
-      <c r="C183" s="15">
+      <c r="C183" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B183,тип_интерполяции_)</f>
         <v>3.4720484999961427</v>
       </c>
-      <c r="D183" s="15">
+      <c r="D183" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B183,тип_интерполяции_)</f>
         <v>0.29678860007839225</v>
       </c>
-      <c r="E183" s="6"/>
-      <c r="F183" s="6"/>
-      <c r="G183" s="6"/>
-      <c r="H183" s="6"/>
-      <c r="I183" s="6"/>
-      <c r="J183" s="6"/>
-      <c r="K183" s="6"/>
-      <c r="L183" s="6"/>
-      <c r="M183" s="6"/>
-      <c r="N183" s="7"/>
-    </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N183" s="6"/>
+    </row>
+    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A184" s="5"/>
-      <c r="B184" s="20">
+      <c r="B184" s="19">
         <f t="shared" si="2"/>
         <v>24.634999999999941</v>
       </c>
-      <c r="C184" s="15">
+      <c r="C184" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B184,тип_интерполяции_)</f>
         <v>3.6348133947776229</v>
       </c>
-      <c r="D184" s="15">
+      <c r="D184" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B184,тип_интерполяции_)</f>
         <v>0.15449911129886867</v>
       </c>
-      <c r="E184" s="6"/>
-      <c r="F184" s="6"/>
-      <c r="G184" s="6"/>
-      <c r="H184" s="6"/>
-      <c r="I184" s="6"/>
-      <c r="J184" s="6"/>
-      <c r="K184" s="6"/>
-      <c r="L184" s="6"/>
-      <c r="M184" s="6"/>
-      <c r="N184" s="7"/>
-    </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N184" s="6"/>
+    </row>
+    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A185" s="5"/>
-      <c r="B185" s="20">
+      <c r="B185" s="19">
         <f t="shared" si="2"/>
         <v>24.779999999999941</v>
       </c>
-      <c r="C185" s="15">
+      <c r="C185" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B185,тип_интерполяции_)</f>
         <v>3.7879383547493735</v>
       </c>
-      <c r="D185" s="15">
+      <c r="D185" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B185,тип_интерполяции_)</f>
         <v>5.7182282935881651E-2</v>
       </c>
-      <c r="E185" s="6"/>
-      <c r="F185" s="6"/>
-      <c r="G185" s="6"/>
-      <c r="H185" s="6"/>
-      <c r="I185" s="6"/>
-      <c r="J185" s="6"/>
-      <c r="K185" s="6"/>
-      <c r="L185" s="6"/>
-      <c r="M185" s="6"/>
-      <c r="N185" s="7"/>
-    </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N185" s="6"/>
+    </row>
+    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A186" s="5"/>
-      <c r="B186" s="20">
+      <c r="B186" s="19">
         <f t="shared" si="2"/>
         <v>24.92499999999994</v>
       </c>
-      <c r="C186" s="15">
+      <c r="C186" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B186,тип_интерполяции_)</f>
         <v>3.9305938760481225</v>
       </c>
-      <c r="D186" s="15">
+      <c r="D186" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B186,тип_интерполяции_)</f>
         <v>6.8880844418695367E-3</v>
       </c>
-      <c r="E186" s="6"/>
-      <c r="F186" s="6"/>
-      <c r="G186" s="6"/>
-      <c r="H186" s="6"/>
-      <c r="I186" s="6"/>
-      <c r="J186" s="6"/>
-      <c r="K186" s="6"/>
-      <c r="L186" s="6"/>
-      <c r="M186" s="6"/>
-      <c r="N186" s="7"/>
-    </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N186" s="6"/>
+    </row>
+    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A187" s="5"/>
-      <c r="B187" s="20">
+      <c r="B187" s="19">
         <f t="shared" si="2"/>
         <v>25.06999999999994</v>
       </c>
-      <c r="C187" s="15">
+      <c r="C187" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B187,тип_интерполяции_)</f>
         <v>4.0619761201991569</v>
       </c>
-      <c r="D187" s="15">
+      <c r="D187" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B187,тип_интерполяции_)</f>
         <v>5.5553692615704642E-3</v>
       </c>
-      <c r="E187" s="6"/>
-      <c r="F187" s="6"/>
-      <c r="G187" s="6"/>
-      <c r="H187" s="6"/>
-      <c r="I187" s="6"/>
-      <c r="J187" s="6"/>
-      <c r="K187" s="6"/>
-      <c r="L187" s="6"/>
-      <c r="M187" s="6"/>
-      <c r="N187" s="7"/>
-    </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N187" s="6"/>
+    </row>
+    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A188" s="5"/>
-      <c r="B188" s="20">
+      <c r="B188" s="19">
         <f t="shared" si="2"/>
         <v>25.214999999999939</v>
       </c>
-      <c r="C188" s="15">
+      <c r="C188" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B188,тип_интерполяции_)</f>
         <v>4.1819222380657264</v>
       </c>
-      <c r="D188" s="15">
+      <c r="D188" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B188,тип_интерполяции_)</f>
         <v>5.2347884745025143E-2</v>
       </c>
-      <c r="E188" s="6"/>
-      <c r="F188" s="6"/>
-      <c r="G188" s="6"/>
-      <c r="H188" s="6"/>
-      <c r="I188" s="6"/>
-      <c r="J188" s="6"/>
-      <c r="K188" s="6"/>
-      <c r="L188" s="6"/>
-      <c r="M188" s="6"/>
-      <c r="N188" s="7"/>
-    </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N188" s="6"/>
+    </row>
+    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A189" s="5"/>
-      <c r="B189" s="20">
+      <c r="B189" s="19">
         <f t="shared" si="2"/>
         <v>25.359999999999939</v>
       </c>
-      <c r="C189" s="15">
+      <c r="C189" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B189,тип_интерполяции_)</f>
         <v>4.2909398607273657</v>
       </c>
-      <c r="D189" s="15">
+      <c r="D189" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B189,тип_интерполяции_)</f>
         <v>0.14352659402357343</v>
       </c>
-      <c r="E189" s="6"/>
-      <c r="F189" s="6"/>
-      <c r="G189" s="6"/>
-      <c r="H189" s="6"/>
-      <c r="I189" s="6"/>
-      <c r="J189" s="6"/>
-      <c r="K189" s="6"/>
-      <c r="L189" s="6"/>
-      <c r="M189" s="6"/>
-      <c r="N189" s="7"/>
-    </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N189" s="6"/>
+    </row>
+    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A190" s="5"/>
-      <c r="B190" s="20">
+      <c r="B190" s="19">
         <f t="shared" si="2"/>
         <v>25.504999999999939</v>
       </c>
-      <c r="C190" s="15">
+      <c r="C190" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B190,тип_интерполяции_)</f>
         <v>4.3895681865691474</v>
       </c>
-      <c r="D190" s="15">
+      <c r="D190" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B190,тип_интерполяции_)</f>
         <v>0.27521579239838007</v>
       </c>
-      <c r="E190" s="6"/>
-      <c r="F190" s="6"/>
-      <c r="G190" s="6"/>
-      <c r="H190" s="6"/>
-      <c r="I190" s="6"/>
-      <c r="J190" s="6"/>
-      <c r="K190" s="6"/>
-      <c r="L190" s="6"/>
-      <c r="M190" s="6"/>
-      <c r="N190" s="7"/>
-    </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N190" s="6"/>
+    </row>
+    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A191" s="5"/>
-      <c r="B191" s="20">
+      <c r="B191" s="19">
         <f t="shared" si="2"/>
         <v>25.649999999999938</v>
       </c>
-      <c r="C191" s="15">
+      <c r="C191" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B191,тип_интерполяции_)</f>
         <v>4.4783464139761433</v>
       </c>
-      <c r="D191" s="15">
+      <c r="D191" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B191,тип_интерполяции_)</f>
         <v>0.44353977517060988</v>
       </c>
-      <c r="E191" s="6"/>
-      <c r="F191" s="6"/>
-      <c r="G191" s="6"/>
-      <c r="H191" s="6"/>
-      <c r="I191" s="6"/>
-      <c r="J191" s="6"/>
-      <c r="K191" s="6"/>
-      <c r="L191" s="6"/>
-      <c r="M191" s="6"/>
-      <c r="N191" s="7"/>
-    </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N191" s="6"/>
+    </row>
+    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A192" s="5"/>
-      <c r="B192" s="20">
+      <c r="B192" s="19">
         <f t="shared" si="2"/>
         <v>25.794999999999938</v>
       </c>
-      <c r="C192" s="15">
+      <c r="C192" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B192,тип_интерполяции_)</f>
         <v>4.5578137413334243</v>
       </c>
-      <c r="D192" s="15">
+      <c r="D192" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B192,тип_интерполяции_)</f>
         <v>0.64462283764142769</v>
       </c>
-      <c r="E192" s="6"/>
-      <c r="F192" s="6"/>
-      <c r="G192" s="6"/>
-      <c r="H192" s="6"/>
-      <c r="I192" s="6"/>
-      <c r="J192" s="6"/>
-      <c r="K192" s="6"/>
-      <c r="L192" s="6"/>
-      <c r="M192" s="6"/>
-      <c r="N192" s="7"/>
-    </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N192" s="6"/>
+    </row>
+    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A193" s="5"/>
-      <c r="B193" s="20">
+      <c r="B193" s="19">
         <f t="shared" si="2"/>
         <v>25.939999999999937</v>
       </c>
-      <c r="C193" s="15">
+      <c r="C193" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B193,тип_интерполяции_)</f>
         <v>4.6285093670260622</v>
       </c>
-      <c r="D193" s="15">
+      <c r="D193" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B193,тип_интерполяции_)</f>
         <v>0.87458927511199813</v>
       </c>
-      <c r="E193" s="6"/>
-      <c r="F193" s="6"/>
-      <c r="G193" s="6"/>
-      <c r="H193" s="6"/>
-      <c r="I193" s="6"/>
-      <c r="J193" s="6"/>
-      <c r="K193" s="6"/>
-      <c r="L193" s="6"/>
-      <c r="M193" s="6"/>
-      <c r="N193" s="7"/>
-    </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N193" s="6"/>
+    </row>
+    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A194" s="5"/>
-      <c r="B194" s="20">
+      <c r="B194" s="19">
         <f t="shared" si="2"/>
         <v>26.084999999999937</v>
       </c>
-      <c r="C194" s="15">
+      <c r="C194" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B194,тип_интерполяции_)</f>
         <v>4.6909724894391287</v>
       </c>
-      <c r="D194" s="15">
+      <c r="D194" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B194,тип_интерполяции_)</f>
         <v>1.1295633828834861</v>
       </c>
-      <c r="E194" s="6"/>
-      <c r="F194" s="6"/>
-      <c r="G194" s="6"/>
-      <c r="H194" s="6"/>
-      <c r="I194" s="6"/>
-      <c r="J194" s="6"/>
-      <c r="K194" s="6"/>
-      <c r="L194" s="6"/>
-      <c r="M194" s="6"/>
-      <c r="N194" s="7"/>
-    </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N194" s="6"/>
+    </row>
+    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A195" s="5"/>
-      <c r="B195" s="20">
+      <c r="B195" s="19">
         <f t="shared" si="2"/>
         <v>26.229999999999936</v>
       </c>
-      <c r="C195" s="15">
+      <c r="C195" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B195,тип_интерполяции_)</f>
         <v>4.7457423069576947</v>
       </c>
-      <c r="D195" s="15">
+      <c r="D195" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B195,тип_интерполяции_)</f>
         <v>1.4056694562570562</v>
       </c>
-      <c r="E195" s="6"/>
-      <c r="F195" s="6"/>
-      <c r="G195" s="6"/>
-      <c r="H195" s="6"/>
-      <c r="I195" s="6"/>
-      <c r="J195" s="6"/>
-      <c r="K195" s="6"/>
-      <c r="L195" s="6"/>
-      <c r="M195" s="6"/>
-      <c r="N195" s="7"/>
-    </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N195" s="6"/>
+    </row>
+    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A196" s="5"/>
-      <c r="B196" s="20">
+      <c r="B196" s="19">
         <f t="shared" si="2"/>
         <v>26.374999999999936</v>
       </c>
-      <c r="C196" s="15">
+      <c r="C196" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B196,тип_интерполяции_)</f>
         <v>4.7933580179668329</v>
       </c>
-      <c r="D196" s="15">
+      <c r="D196" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B196,тип_интерполяции_)</f>
         <v>1.6990317905338734</v>
       </c>
-      <c r="E196" s="6"/>
-      <c r="F196" s="6"/>
-      <c r="G196" s="6"/>
-      <c r="H196" s="6"/>
-      <c r="I196" s="6"/>
-      <c r="J196" s="6"/>
-      <c r="K196" s="6"/>
-      <c r="L196" s="6"/>
-      <c r="M196" s="6"/>
-      <c r="N196" s="7"/>
-    </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N196" s="6"/>
+    </row>
+    <row r="197" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A197" s="5"/>
-      <c r="B197" s="20">
+      <c r="B197" s="19">
         <f>B196+($B$15-$B$7)/200</f>
         <v>26.519999999999936</v>
       </c>
-      <c r="C197" s="15">
+      <c r="C197" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B197,тип_интерполяции_)</f>
         <v>4.8343588208516142</v>
       </c>
-      <c r="D197" s="15">
+      <c r="D197" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B197,тип_интерполяции_)</f>
         <v>2.0057746810151027</v>
       </c>
-      <c r="E197" s="6"/>
-      <c r="F197" s="6"/>
-      <c r="G197" s="6"/>
-      <c r="H197" s="6"/>
-      <c r="I197" s="6"/>
-      <c r="J197" s="6"/>
-      <c r="K197" s="6"/>
-      <c r="L197" s="6"/>
-      <c r="M197" s="6"/>
-      <c r="N197" s="7"/>
-    </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N197" s="6"/>
+    </row>
+    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A198" s="5"/>
-      <c r="B198" s="20">
+      <c r="B198" s="19">
         <f t="shared" ref="B198:B213" si="3">B197+($B$15-$B$7)/200</f>
         <v>26.664999999999935</v>
       </c>
-      <c r="C198" s="15">
+      <c r="C198" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B198,тип_интерполяции_)</f>
         <v>4.8692839139971111</v>
       </c>
-      <c r="D198" s="15">
+      <c r="D198" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B198,тип_интерполяции_)</f>
         <v>2.3220224230019082</v>
       </c>
-      <c r="E198" s="6"/>
-      <c r="F198" s="6"/>
-      <c r="G198" s="6"/>
-      <c r="H198" s="6"/>
-      <c r="I198" s="6"/>
-      <c r="J198" s="6"/>
-      <c r="K198" s="6"/>
-      <c r="L198" s="6"/>
-      <c r="M198" s="6"/>
-      <c r="N198" s="7"/>
-    </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N198" s="6"/>
+    </row>
+    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A199" s="5"/>
-      <c r="B199" s="20">
+      <c r="B199" s="19">
         <f t="shared" si="3"/>
         <v>26.809999999999935</v>
       </c>
-      <c r="C199" s="15">
+      <c r="C199" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B199,тип_интерполяции_)</f>
         <v>4.8986724957883929</v>
       </c>
-      <c r="D199" s="15">
+      <c r="D199" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B199,тип_интерполяции_)</f>
         <v>2.643899311795455</v>
       </c>
-      <c r="E199" s="6"/>
-      <c r="F199" s="6"/>
-      <c r="G199" s="6"/>
-      <c r="H199" s="6"/>
-      <c r="I199" s="6"/>
-      <c r="J199" s="6"/>
-      <c r="K199" s="6"/>
-      <c r="L199" s="6"/>
-      <c r="M199" s="6"/>
-      <c r="N199" s="7"/>
-    </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N199" s="6"/>
+    </row>
+    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A200" s="5"/>
-      <c r="B200" s="20">
+      <c r="B200" s="19">
         <f t="shared" si="3"/>
         <v>26.954999999999934</v>
       </c>
-      <c r="C200" s="15">
+      <c r="C200" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B200,тип_интерполяции_)</f>
         <v>4.923063764610534</v>
       </c>
-      <c r="D200" s="15">
+      <c r="D200" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B200,тип_интерполяции_)</f>
         <v>2.967529642696908</v>
       </c>
-      <c r="E200" s="6"/>
-      <c r="F200" s="6"/>
-      <c r="G200" s="6"/>
-      <c r="H200" s="6"/>
-      <c r="I200" s="6"/>
-      <c r="J200" s="6"/>
-      <c r="K200" s="6"/>
-      <c r="L200" s="6"/>
-      <c r="M200" s="6"/>
-      <c r="N200" s="7"/>
-    </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N200" s="6"/>
+    </row>
+    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A201" s="5"/>
-      <c r="B201" s="20">
+      <c r="B201" s="19">
         <f t="shared" si="3"/>
         <v>27.099999999999934</v>
       </c>
-      <c r="C201" s="15">
+      <c r="C201" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B201,тип_интерполяции_)</f>
         <v>4.9429969188486043</v>
       </c>
-      <c r="D201" s="15">
+      <c r="D201" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B201,тип_интерполяции_)</f>
         <v>3.289037711007432</v>
       </c>
-      <c r="E201" s="6"/>
-      <c r="F201" s="6"/>
-      <c r="G201" s="6"/>
-      <c r="H201" s="6"/>
-      <c r="I201" s="6"/>
-      <c r="J201" s="6"/>
-      <c r="K201" s="6"/>
-      <c r="L201" s="6"/>
-      <c r="M201" s="6"/>
-      <c r="N201" s="7"/>
-    </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N201" s="6"/>
+    </row>
+    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A202" s="5"/>
-      <c r="B202" s="20">
+      <c r="B202" s="19">
         <f t="shared" si="3"/>
         <v>27.244999999999933</v>
       </c>
-      <c r="C202" s="15">
+      <c r="C202" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B202,тип_интерполяции_)</f>
         <v>4.9590111568876756</v>
       </c>
-      <c r="D202" s="15">
+      <c r="D202" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B202,тип_интерполяции_)</f>
         <v>3.6045478120281915</v>
       </c>
-      <c r="E202" s="6"/>
-      <c r="F202" s="6"/>
-      <c r="G202" s="6"/>
-      <c r="H202" s="6"/>
-      <c r="I202" s="6"/>
-      <c r="J202" s="6"/>
-      <c r="K202" s="6"/>
-      <c r="L202" s="6"/>
-      <c r="M202" s="6"/>
-      <c r="N202" s="7"/>
-    </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N202" s="6"/>
+    </row>
+    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A203" s="5"/>
-      <c r="B203" s="20">
+      <c r="B203" s="19">
         <f t="shared" si="3"/>
         <v>27.389999999999933</v>
       </c>
-      <c r="C203" s="15">
+      <c r="C203" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B203,тип_интерполяции_)</f>
         <v>4.9716456771128188</v>
       </c>
-      <c r="D203" s="15">
+      <c r="D203" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B203,тип_интерполяции_)</f>
         <v>3.9101842410603518</v>
       </c>
-      <c r="E203" s="6"/>
-      <c r="F203" s="6"/>
-      <c r="G203" s="6"/>
-      <c r="H203" s="6"/>
-      <c r="I203" s="6"/>
-      <c r="J203" s="6"/>
-      <c r="K203" s="6"/>
-      <c r="L203" s="6"/>
-      <c r="M203" s="6"/>
-      <c r="N203" s="7"/>
-    </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N203" s="6"/>
+    </row>
+    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A204" s="5"/>
-      <c r="B204" s="20">
+      <c r="B204" s="19">
         <f t="shared" si="3"/>
         <v>27.534999999999933</v>
       </c>
-      <c r="C204" s="15">
+      <c r="C204" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B204,тип_интерполяции_)</f>
         <v>4.9814396779091075</v>
       </c>
-      <c r="D204" s="15">
+      <c r="D204" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B204,тип_интерполяции_)</f>
         <v>4.2020712934050772</v>
       </c>
-      <c r="E204" s="6"/>
-      <c r="F204" s="6"/>
-      <c r="G204" s="6"/>
-      <c r="H204" s="6"/>
-      <c r="I204" s="6"/>
-      <c r="J204" s="6"/>
-      <c r="K204" s="6"/>
-      <c r="L204" s="6"/>
-      <c r="M204" s="6"/>
-      <c r="N204" s="7"/>
-    </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N204" s="6"/>
+    </row>
+    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A205" s="5"/>
-      <c r="B205" s="20">
+      <c r="B205" s="19">
         <f t="shared" si="3"/>
         <v>27.679999999999932</v>
       </c>
-      <c r="C205" s="15">
+      <c r="C205" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B205,тип_интерполяции_)</f>
         <v>4.9889323576616107</v>
       </c>
-      <c r="D205" s="15">
+      <c r="D205" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B205,тип_интерполяции_)</f>
         <v>4.4763332643635323</v>
       </c>
-      <c r="E205" s="6"/>
-      <c r="F205" s="6"/>
-      <c r="G205" s="6"/>
-      <c r="H205" s="6"/>
-      <c r="I205" s="6"/>
-      <c r="J205" s="6"/>
-      <c r="K205" s="6"/>
-      <c r="L205" s="6"/>
-      <c r="M205" s="6"/>
-      <c r="N205" s="7"/>
-    </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N205" s="6"/>
+    </row>
+    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A206" s="5"/>
-      <c r="B206" s="20">
+      <c r="B206" s="19">
         <f t="shared" si="3"/>
         <v>27.824999999999932</v>
       </c>
-      <c r="C206" s="15">
+      <c r="C206" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B206,тип_интерполяции_)</f>
         <v>4.994662914755402</v>
       </c>
-      <c r="D206" s="15">
+      <c r="D206" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B206,тип_интерполяции_)</f>
         <v>4.7290944492368823</v>
       </c>
-      <c r="E206" s="6"/>
-      <c r="F206" s="6"/>
-      <c r="G206" s="6"/>
-      <c r="H206" s="6"/>
-      <c r="I206" s="6"/>
-      <c r="J206" s="6"/>
-      <c r="K206" s="6"/>
-      <c r="L206" s="6"/>
-      <c r="M206" s="6"/>
-      <c r="N206" s="7"/>
-    </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N206" s="6"/>
+    </row>
+    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A207" s="5"/>
-      <c r="B207" s="20">
+      <c r="B207" s="19">
         <f t="shared" si="3"/>
         <v>27.969999999999931</v>
       </c>
-      <c r="C207" s="15">
+      <c r="C207" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B207,тип_интерполяции_)</f>
         <v>4.9991705475755523</v>
       </c>
-      <c r="D207" s="15">
+      <c r="D207" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B207,тип_интерполяции_)</f>
         <v>4.956479143326292</v>
       </c>
-      <c r="E207" s="6"/>
-      <c r="F207" s="6"/>
-      <c r="G207" s="6"/>
-      <c r="H207" s="6"/>
-      <c r="I207" s="6"/>
-      <c r="J207" s="6"/>
-      <c r="K207" s="6"/>
-      <c r="L207" s="6"/>
-      <c r="M207" s="6"/>
-      <c r="N207" s="7"/>
-    </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N207" s="6"/>
+    </row>
+    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A208" s="5"/>
-      <c r="B208" s="20">
+      <c r="B208" s="19">
         <f t="shared" si="3"/>
         <v>28.114999999999931</v>
       </c>
-      <c r="C208" s="15">
+      <c r="C208" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B208,тип_интерполяции_)</f>
         <v>5.0029496226379084</v>
       </c>
-      <c r="D208" s="15">
+      <c r="D208" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B208,тип_интерполяции_)</f>
         <v>5.1549338889778413</v>
       </c>
-      <c r="E208" s="6"/>
-      <c r="F208" s="6"/>
-      <c r="G208" s="6"/>
-      <c r="H208" s="6"/>
-      <c r="I208" s="6"/>
-      <c r="J208" s="6"/>
-      <c r="K208" s="6"/>
-      <c r="L208" s="6"/>
-      <c r="M208" s="6"/>
-      <c r="N208" s="7"/>
-    </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N208" s="6"/>
+    </row>
+    <row r="209" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A209" s="5"/>
-      <c r="B209" s="20">
+      <c r="B209" s="19">
         <f t="shared" si="3"/>
         <v>28.259999999999931</v>
       </c>
-      <c r="C209" s="15">
+      <c r="C209" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B209,тип_интерполяции_)</f>
         <v>5.0061557342008545</v>
       </c>
-      <c r="D209" s="15">
+      <c r="D209" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B209,тип_интерполяции_)</f>
         <v>5.3233402900408207</v>
       </c>
-      <c r="E209" s="6"/>
-      <c r="F209" s="6"/>
-      <c r="G209" s="6"/>
-      <c r="H209" s="6"/>
-      <c r="I209" s="6"/>
-      <c r="J209" s="6"/>
-      <c r="K209" s="6"/>
-      <c r="L209" s="6"/>
-      <c r="M209" s="6"/>
-      <c r="N209" s="7"/>
-    </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N209" s="6"/>
+    </row>
+    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A210" s="5"/>
-      <c r="B210" s="20">
+      <c r="B210" s="19">
         <f t="shared" si="3"/>
         <v>28.40499999999993</v>
       </c>
-      <c r="C210" s="15">
+      <c r="C210" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B210,тип_интерполяции_)</f>
         <v>5.008789678161798</v>
       </c>
-      <c r="D210" s="15">
+      <c r="D210" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B210,тип_интерполяции_)</f>
         <v>5.4616926256833329</v>
       </c>
-      <c r="E210" s="6"/>
-      <c r="F210" s="6"/>
-      <c r="G210" s="6"/>
-      <c r="H210" s="6"/>
-      <c r="I210" s="6"/>
-      <c r="J210" s="6"/>
-      <c r="K210" s="6"/>
-      <c r="L210" s="6"/>
-      <c r="M210" s="6"/>
-      <c r="N210" s="7"/>
-    </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N210" s="6"/>
+    </row>
+    <row r="211" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A211" s="5"/>
-      <c r="B211" s="20">
+      <c r="B211" s="19">
         <f t="shared" si="3"/>
         <v>28.54999999999993</v>
       </c>
-      <c r="C211" s="15">
+      <c r="C211" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B211,тип_интерполяции_)</f>
         <v>5.010851454520739</v>
       </c>
-      <c r="D211" s="15">
+      <c r="D211" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B211,тип_интерполяции_)</f>
         <v>5.5699908959053772</v>
       </c>
-      <c r="E211" s="6"/>
-      <c r="F211" s="6"/>
-      <c r="G211" s="6"/>
-      <c r="H211" s="6"/>
-      <c r="I211" s="6"/>
-      <c r="J211" s="6"/>
-      <c r="K211" s="6"/>
-      <c r="L211" s="6"/>
-      <c r="M211" s="6"/>
-      <c r="N211" s="7"/>
-    </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N211" s="6"/>
+    </row>
+    <row r="212" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A212" s="5"/>
-      <c r="B212" s="20">
+      <c r="B212" s="19">
         <f t="shared" si="3"/>
         <v>28.694999999999929</v>
       </c>
-      <c r="C212" s="15">
+      <c r="C212" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B212,тип_интерполяции_)</f>
         <v>5.0123410632776775</v>
       </c>
-      <c r="D212" s="15">
+      <c r="D212" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B212,тип_интерполяции_)</f>
         <v>5.6482351007069544</v>
       </c>
-      <c r="E212" s="6"/>
-      <c r="F212" s="6"/>
-      <c r="G212" s="6"/>
-      <c r="H212" s="6"/>
-      <c r="I212" s="6"/>
-      <c r="J212" s="6"/>
-      <c r="K212" s="6"/>
-      <c r="L212" s="6"/>
-      <c r="M212" s="6"/>
-      <c r="N212" s="7"/>
-    </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N212" s="6"/>
+    </row>
+    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A213" s="5"/>
-      <c r="B213" s="20">
+      <c r="B213" s="19">
         <f t="shared" si="3"/>
         <v>28.839999999999929</v>
       </c>
-      <c r="C213" s="15">
+      <c r="C213" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B213,тип_интерполяции_)</f>
         <v>5.0132585044326134</v>
       </c>
-      <c r="D213" s="15">
+      <c r="D213" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B213,тип_интерполяции_)</f>
         <v>5.6964252400880637</v>
       </c>
-      <c r="E213" s="6"/>
-      <c r="F213" s="6"/>
-      <c r="G213" s="6"/>
-      <c r="H213" s="6"/>
-      <c r="I213" s="6"/>
-      <c r="J213" s="6"/>
-      <c r="K213" s="6"/>
-      <c r="L213" s="6"/>
-      <c r="M213" s="6"/>
-      <c r="N213" s="7"/>
-    </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N213" s="6"/>
+    </row>
+    <row r="214" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A214" s="5"/>
-      <c r="B214" s="20">
+      <c r="B214" s="19">
         <f>B213+($B$15-$B$7)/200</f>
         <v>28.984999999999928</v>
       </c>
-      <c r="C214" s="15">
+      <c r="C214" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B214,тип_интерполяции_)</f>
         <v>5.013603777985546</v>
       </c>
-      <c r="D214" s="15">
+      <c r="D214" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B214,тип_интерполяции_)</f>
         <v>5.7145613140487059</v>
       </c>
-      <c r="E214" s="6"/>
-      <c r="F214" s="6"/>
-      <c r="G214" s="6"/>
-      <c r="H214" s="6"/>
-      <c r="I214" s="6"/>
-      <c r="J214" s="6"/>
-      <c r="K214" s="6"/>
-      <c r="L214" s="6"/>
-      <c r="M214" s="6"/>
-      <c r="N214" s="7"/>
-    </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N214" s="6"/>
+    </row>
+    <row r="215" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A215" s="5"/>
-      <c r="B215" s="20">
+      <c r="B215" s="19">
         <f t="shared" ref="B215:B221" si="4">B214+($B$15-$B$7)/200</f>
         <v>29.129999999999928</v>
       </c>
-      <c r="C215" s="15">
+      <c r="C215" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B215,тип_интерполяции_)</f>
         <v>5.0133768839364761</v>
       </c>
-      <c r="D215" s="15">
+      <c r="D215" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B215,тип_интерполяции_)</f>
         <v>5.7026433225888802</v>
       </c>
-      <c r="E215" s="6"/>
-      <c r="F215" s="6"/>
-      <c r="G215" s="6"/>
-      <c r="H215" s="6"/>
-      <c r="I215" s="6"/>
-      <c r="J215" s="6"/>
-      <c r="K215" s="6"/>
-      <c r="L215" s="6"/>
-      <c r="M215" s="6"/>
-      <c r="N215" s="7"/>
-    </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N215" s="6"/>
+    </row>
+    <row r="216" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A216" s="5"/>
-      <c r="B216" s="20">
+      <c r="B216" s="19">
         <f t="shared" si="4"/>
         <v>29.274999999999928</v>
       </c>
-      <c r="C216" s="15">
+      <c r="C216" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B216,тип_интерполяции_)</f>
         <v>5.0125778222854036</v>
       </c>
-      <c r="D216" s="15">
+      <c r="D216" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B216,тип_интерполяции_)</f>
         <v>5.6606712657085865</v>
       </c>
-      <c r="E216" s="6"/>
-      <c r="F216" s="6"/>
-      <c r="G216" s="6"/>
-      <c r="H216" s="6"/>
-      <c r="I216" s="6"/>
-      <c r="J216" s="6"/>
-      <c r="K216" s="6"/>
-      <c r="L216" s="6"/>
-      <c r="M216" s="6"/>
-      <c r="N216" s="7"/>
-    </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N216" s="6"/>
+    </row>
+    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A217" s="5"/>
-      <c r="B217" s="20">
+      <c r="B217" s="19">
         <f t="shared" si="4"/>
         <v>29.419999999999927</v>
       </c>
-      <c r="C217" s="15">
+      <c r="C217" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B217,тип_интерполяции_)</f>
         <v>5.0112065930323286</v>
       </c>
-      <c r="D217" s="15">
+      <c r="D217" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B217,тип_интерполяции_)</f>
         <v>5.5886451434078257</v>
       </c>
-      <c r="E217" s="6"/>
-      <c r="F217" s="6"/>
-      <c r="G217" s="6"/>
-      <c r="H217" s="6"/>
-      <c r="I217" s="6"/>
-      <c r="J217" s="6"/>
-      <c r="K217" s="6"/>
-      <c r="L217" s="6"/>
-      <c r="M217" s="6"/>
-      <c r="N217" s="7"/>
-    </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N217" s="6"/>
+    </row>
+    <row r="218" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A218" s="5"/>
-      <c r="B218" s="20">
+      <c r="B218" s="19">
         <f t="shared" si="4"/>
         <v>29.564999999999927</v>
       </c>
-      <c r="C218" s="15">
+      <c r="C218" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B218,тип_интерполяции_)</f>
         <v>5.0092631961772511</v>
       </c>
-      <c r="D218" s="15">
+      <c r="D218" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B218,тип_интерполяции_)</f>
         <v>5.486564955686597</v>
       </c>
-      <c r="E218" s="6"/>
-      <c r="F218" s="6"/>
-      <c r="G218" s="6"/>
-      <c r="H218" s="6"/>
-      <c r="I218" s="6"/>
-      <c r="J218" s="6"/>
-      <c r="K218" s="6"/>
-      <c r="L218" s="6"/>
-      <c r="M218" s="6"/>
-      <c r="N218" s="7"/>
-    </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N218" s="6"/>
+    </row>
+    <row r="219" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A219" s="5"/>
-      <c r="B219" s="20">
+      <c r="B219" s="19">
         <f t="shared" si="4"/>
         <v>29.709999999999926</v>
       </c>
-      <c r="C219" s="15">
+      <c r="C219" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B219,тип_интерполяции_)</f>
         <v>5.0067476317201711</v>
       </c>
-      <c r="D219" s="15">
+      <c r="D219" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B219,тип_интерполяции_)</f>
         <v>5.3544307025449012</v>
       </c>
-      <c r="E219" s="6"/>
-      <c r="F219" s="6"/>
-      <c r="G219" s="6"/>
-      <c r="H219" s="6"/>
-      <c r="I219" s="6"/>
-      <c r="J219" s="6"/>
-      <c r="K219" s="6"/>
-      <c r="L219" s="6"/>
-      <c r="M219" s="6"/>
-      <c r="N219" s="7"/>
-    </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N219" s="6"/>
+    </row>
+    <row r="220" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A220" s="5"/>
-      <c r="B220" s="20">
+      <c r="B220" s="19">
         <f t="shared" si="4"/>
         <v>29.854999999999926</v>
       </c>
-      <c r="C220" s="15">
+      <c r="C220" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B220,тип_интерполяции_)</f>
         <v>5.0036598996610877</v>
       </c>
-      <c r="D220" s="15">
+      <c r="D220" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B220,тип_интерполяции_)</f>
         <v>5.1922423839827374</v>
       </c>
-      <c r="E220" s="6"/>
-      <c r="F220" s="6"/>
-      <c r="G220" s="6"/>
-      <c r="H220" s="6"/>
-      <c r="I220" s="6"/>
-      <c r="J220" s="6"/>
-      <c r="K220" s="6"/>
-      <c r="L220" s="6"/>
-      <c r="M220" s="6"/>
-      <c r="N220" s="7"/>
-    </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N220" s="6"/>
+    </row>
+    <row r="221" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A221" s="5"/>
-      <c r="B221" s="20">
+      <c r="B221" s="19">
         <f t="shared" si="4"/>
         <v>29.999999999999925</v>
       </c>
-      <c r="C221" s="15">
+      <c r="C221" s="14">
         <f>[1]!crv_interpolation(x_,fx_,B221,тип_интерполяции_)</f>
         <v>5.0000000000000018</v>
       </c>
-      <c r="D221" s="15">
+      <c r="D221" s="14">
         <f>[1]!crv_interpolation(x2_,gx2_,B221,тип_интерполяции_)</f>
         <v>5.0000000000001066</v>
       </c>
-      <c r="E221" s="6"/>
-      <c r="F221" s="6"/>
-      <c r="G221" s="6"/>
-      <c r="H221" s="6"/>
-      <c r="I221" s="6"/>
-      <c r="J221" s="6"/>
-      <c r="K221" s="6"/>
-      <c r="L221" s="6"/>
-      <c r="M221" s="6"/>
-      <c r="N221" s="7"/>
-    </row>
-    <row r="222" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A222" s="9"/>
-      <c r="B222" s="21"/>
-      <c r="C222" s="10"/>
-      <c r="D222" s="10"/>
-      <c r="E222" s="10"/>
-      <c r="F222" s="10"/>
-      <c r="G222" s="10"/>
-      <c r="H222" s="10"/>
-      <c r="I222" s="10"/>
-      <c r="J222" s="10"/>
-      <c r="K222" s="10"/>
-      <c r="L222" s="10"/>
-      <c r="M222" s="10"/>
-      <c r="N222" s="11"/>
-    </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N221" s="6"/>
+    </row>
+    <row r="222" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A222" s="8"/>
+      <c r="B222" s="20"/>
+      <c r="C222" s="9"/>
+      <c r="D222" s="9"/>
+      <c r="E222" s="9"/>
+      <c r="F222" s="9"/>
+      <c r="G222" s="9"/>
+      <c r="H222" s="9"/>
+      <c r="I222" s="9"/>
+      <c r="J222" s="9"/>
+      <c r="K222" s="9"/>
+      <c r="L222" s="9"/>
+      <c r="M222" s="9"/>
+      <c r="N222" s="10"/>
+    </row>
+    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B223" s="2"/>
     </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B224" s="2"/>
     </row>
-    <row r="225" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="225" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B225" s="2"/>
     </row>
-    <row r="226" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="226" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B226" s="2"/>
     </row>
-    <row r="227" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="227" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B227" s="2"/>
     </row>
-    <row r="228" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="228" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B228" s="2"/>
     </row>
-    <row r="229" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="229" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B229" s="2"/>
     </row>
-    <row r="230" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="230" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B230" s="2"/>
     </row>
   </sheetData>
@@ -16372,15 +13843,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>5</xdr:col>
-                    <xdr:colOff>30480</xdr:colOff>
+                    <xdr:colOff>28575</xdr:colOff>
                     <xdr:row>20</xdr:row>
-                    <xdr:rowOff>60960</xdr:rowOff>
+                    <xdr:rowOff>57150</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>8</xdr:col>
-                    <xdr:colOff>213360</xdr:colOff>
+                    <xdr:colOff>209550</xdr:colOff>
                     <xdr:row>21</xdr:row>
-                    <xdr:rowOff>121920</xdr:rowOff>
+                    <xdr:rowOff>123825</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
